--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -17596,7 +17596,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -24956,7 +24956,7 @@
       </c>
       <c r="G529" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H529" s="5" t="n">
@@ -36656,7 +36656,7 @@
       </c>
       <c r="G783" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H783" s="5" t="n">
@@ -40152,7 +40152,7 @@
       </c>
       <c r="G859" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="H859" s="5" t="n">
@@ -48355,7 +48355,7 @@
           <t>B6 | 236呎 (开放式)
 $525万
 $22,263/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O34" s="18" t="inlineStr">
@@ -51066,7 +51066,7 @@
           <t>A6 | 469呎 (2房)
 $1,170万
 $24,949/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H27" s="16" t="inlineStr"/>
@@ -51824,7 +51824,7 @@
           <t>B1 | 467呎 (2房)
 $912万
 $19,530/呎
-(已售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J34" s="18" t="inlineStr">

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -647,7 +647,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -2177,7 +2177,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1985</v>
+        <v>1914</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>77550000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>39068</v>
+        <v>40517</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>77550000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>39068</v>
+        <v>40517</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -7455,7 +7455,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7471,7 +7471,7 @@
         <v>6757200</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>22449</v>
+        <v>22524</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7482,7 +7482,7 @@
         <v>6757200</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>22449</v>
+        <v>22524</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
       </c>
       <c r="J536" s="3" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="K536" s="5" t="n">
@@ -50315,7 +50315,7 @@
         </is>
       </c>
       <c r="E800" s="4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F800" s="3" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>5347900</v>
       </c>
       <c r="I800" s="5" t="n">
-        <v>22661</v>
+        <v>22565</v>
       </c>
       <c r="J800" s="3" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>5347900</v>
       </c>
       <c r="L800" s="5" t="n">
-        <v>22661</v>
+        <v>22565</v>
       </c>
       <c r="M800" s="3" t="inlineStr">
         <is>
@@ -57339,7 +57339,7 @@
           <t>A | 1993呎 (4+房)
 $8305万
 $41,672/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -57351,7 +57351,7 @@
           <t>B | 1991呎 (4+房)
 $9103万
 $45,722/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
@@ -57364,7 +57364,7 @@
           <t>C | 1367呎 (4+房)
 $3989万
 $29,180/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N7" s="22" t="inlineStr">
@@ -57372,7 +57372,7 @@
           <t>D | 1227呎 (4+房)
 $3336万
 $27,184/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr"/>
@@ -57416,7 +57416,7 @@
           <t>C | 1367呎 (4+房)
 $4078万
 $29,832/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
@@ -57424,7 +57424,7 @@
           <t>D | 1227呎 (4+房)
 $3452万
 $28,134/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr"/>
@@ -57443,7 +57443,7 @@
           <t>A | 1993呎 (4+房)
 $8098万
 $40,631/呎
-(25年-01月-16日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -57468,7 +57468,7 @@
           <t>C | 1367呎 (4+房)
 $3862万
 $28,255/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N9" s="22" t="inlineStr">
@@ -57476,7 +57476,7 @@
           <t>D | 1227呎 (4+房)
 $3258万
 $26,553/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr"/>
@@ -57495,7 +57495,7 @@
           <t>A | 1921呎 (4+房)
 $8015万
 $41,721/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -57507,7 +57507,7 @@
           <t>B | 1985呎 (4+房)
 $7810万
 $39,345/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -57520,7 +57520,7 @@
           <t>C | 1365呎 (4+房)
 $4069万
 $29,812/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N10" s="22" t="inlineStr">
@@ -57528,7 +57528,7 @@
           <t>D | 1227呎 (4+房)
 $3260万
 $26,571/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr"/>
@@ -57547,7 +57547,7 @@
           <t>A | 1993呎 (4+房)
 $7994万
 $40,109/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -57556,10 +57556,10 @@
       <c r="F11" s="20" t="inlineStr"/>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t>B | 1985呎 (4+房)
+          <t>B | 1914呎 (4+房)
 $7755万
-$39,068/呎
-(24年-12月-08日)</t>
+$40,517/呎
+(24年-12月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
@@ -57572,7 +57572,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,802/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N11" s="22" t="inlineStr">
@@ -57580,7 +57580,7 @@
           <t>D | 1227呎 (4+房)
 $3299万
 $26,887/呎
-(24年-12月-03日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr"/>
@@ -57599,7 +57599,7 @@
           <t>A | 1993呎 (4+房)
 $7952万
 $39,901/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -57611,7 +57611,7 @@
           <t>B | 1985呎 (4+房)
 $7652万
 $38,547/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
@@ -57624,7 +57624,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,800/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
@@ -57632,7 +57632,7 @@
           <t>D | 1227呎 (4+房)
 $3113万
 $25,370/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr"/>
@@ -57651,7 +57651,7 @@
           <t>A | 1993呎 (4+房)
 $7288万
 $36,568/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -57676,7 +57676,7 @@
           <t>C | 1365呎 (4+房)
 $4038万
 $29,579/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N13" s="22" t="inlineStr">
@@ -57684,7 +57684,7 @@
           <t>D | 1227呎 (4+房)
 $3068万
 $25,008/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr"/>
@@ -57703,7 +57703,7 @@
           <t>A | 1993呎 (4+房)
 $7268万
 $36,467/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr"/>
@@ -57715,7 +57715,7 @@
           <t>B | 1985呎 (4+房)
 $7500万
 $37,783/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
@@ -57728,7 +57728,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,800/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N14" s="22" t="inlineStr">
@@ -57736,7 +57736,7 @@
           <t>D | 1227呎 (4+房)
 $3262万
 $26,584/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr"/>
@@ -57755,7 +57755,7 @@
           <t>A | 1993呎 (4+房)
 $6989万
 $35,067/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -57767,7 +57767,7 @@
           <t>B | 1985呎 (4+房)
 $7344万
 $36,997/呎
-(24年-12月-18日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -57780,7 +57780,7 @@
           <t>C | 1365呎 (4+房)
 $3699万
 $27,099/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -57788,7 +57788,7 @@
           <t>D | 1227呎 (4+房)
 $3279万
 $26,727/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr"/>
@@ -57807,7 +57807,7 @@
           <t>A | 1993呎 (4+房)
 $7036万
 $35,305/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -57819,7 +57819,7 @@
           <t>B | 1985呎 (4+房)
 $7238万
 $36,463/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -57832,7 +57832,7 @@
           <t>C | 1365呎 (4+房)
 $4069万
 $29,810/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -57840,7 +57840,7 @@
           <t>D | 1227呎 (4+房)
 $3261万
 $26,575/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr"/>
@@ -57859,7 +57859,7 @@
           <t>A | 1993呎 (4+房)
 $6852万
 $34,380/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -57871,7 +57871,7 @@
           <t>B | 1985呎 (4+房)
 $7197万
 $36,255/呎
-(25年-01月-20日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -57884,7 +57884,7 @@
           <t>C | 1365呎 (4+房)
 $3982万
 $29,174/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -57892,7 +57892,7 @@
           <t>D | 1227呎 (4+房)
 $3017万
 $24,592/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr"/>
@@ -57911,7 +57911,7 @@
           <t>A | 1993呎 (4+房)
 $6894万
 $34,589/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr"/>
@@ -57923,7 +57923,7 @@
           <t>B | 1985呎 (4+房)
 $7093万
 $35,735/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -57936,7 +57936,7 @@
           <t>C | 1365呎 (4+房)
 $3456万
 $25,320/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -57944,7 +57944,7 @@
           <t>D | 1227呎 (4+房)
 $3222万
 $26,259/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr"/>
@@ -57963,7 +57963,7 @@
           <t>A | 1993呎 (4+房)
 $6644万
 $33,339/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -57975,7 +57975,7 @@
           <t>B | 1985呎 (4+房)
 $7031万
 $35,422/呎
-(24年-12月-08日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -57988,7 +57988,7 @@
           <t>C | 1365呎 (4+房)
 $3600万
 $26,374/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -57996,7 +57996,7 @@
           <t>D | 1227呎 (4+房)
 $3132万
 $25,530/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr"/>
@@ -58015,7 +58015,7 @@
           <t>A | 1993呎 (4+房)
 $7018万
 $35,214/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -58027,7 +58027,7 @@
           <t>B | 1985呎 (4+房)
 $6990万
 $35,214/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -58040,7 +58040,7 @@
           <t>C | 1365呎 (4+房)
 $3793万
 $27,785/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -58048,7 +58048,7 @@
           <t>D | 1227呎 (4+房)
 $3324万
 $27,092/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr"/>
@@ -58068,7 +58068,7 @@
           <t>A1 | 559呎 (2房)
 $1277万
 $22,851/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -58076,7 +58076,7 @@
           <t>A2 | 443呎 (2房)
 $1094万
 $24,697/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -58084,7 +58084,7 @@
           <t>A3 | 443呎 (2房)
 $1052万
 $23,736/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -58092,7 +58092,7 @@
           <t>A5 | 887呎 (4+房)
 $2525万
 $28,464/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
@@ -58101,7 +58101,7 @@
           <t>B1 | 458呎 (2房)
 $987万
 $21,554/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -58109,7 +58109,7 @@
           <t>B2 | 298呎 (1房)
 $678万
 $22,765/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -58117,7 +58117,7 @@
           <t>B3 | 301呎 (1房)
 $685万
 $22,765/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -58125,7 +58125,7 @@
           <t>B5 | 298呎 (1房)
 $678万
 $22,765/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -58133,7 +58133,7 @@
           <t>B6 | 437呎 (2房)
 $973万
 $22,261/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr"/>
@@ -58155,7 +58155,7 @@
           <t>A1 | 559呎 (2房)
 $1254万
 $22,431/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -58163,7 +58163,7 @@
           <t>A2 | 443呎 (2房)
 $1089万
 $24,590/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -58171,7 +58171,7 @@
           <t>A3 | 443呎 (2房)
 $1089万
 $24,590/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -58179,7 +58179,7 @@
           <t>A5 | 887呎 (4+房)
 $2600万
 $29,308/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -58188,7 +58188,7 @@
           <t>B1 | 458呎 (2房)
 $979万
 $21,383/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -58196,7 +58196,7 @@
           <t>B2 | 298呎 (1房)
 $676万
 $22,675/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -58204,7 +58204,7 @@
           <t>B3 | 301呎 (1房)
 $683万
 $22,675/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -58212,7 +58212,7 @@
           <t>B5 | 298呎 (1房)
 $676万
 $22,675/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -58220,7 +58220,7 @@
           <t>B6 | 437呎 (2房)
 $965万
 $22,084/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr"/>
@@ -58242,7 +58242,7 @@
           <t>A1 | 559呎 (2房)
 $1289万
 $23,054/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -58250,7 +58250,7 @@
           <t>A2 | 443呎 (2房)
 $1076万
 $24,284/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -58258,7 +58258,7 @@
           <t>A3 | 443呎 (2房)
 $1076万
 $24,284/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -58266,7 +58266,7 @@
           <t>A5 | 887呎 (4+房)
 $2422万
 $27,303/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
@@ -58275,7 +58275,7 @@
           <t>B1 | 458呎 (2房)
 $973万
 $21,255/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -58283,7 +58283,7 @@
           <t>B2 | 298呎 (1房)
 $674万
 $22,630/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -58291,7 +58291,7 @@
           <t>B3 | 301呎 (1房)
 $681万
 $22,630/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -58299,7 +58299,7 @@
           <t>B5 | 298呎 (1房)
 $674万
 $22,630/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -58307,7 +58307,7 @@
           <t>B6 | 437呎 (2房)
 $959万
 $21,953/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr"/>
@@ -58329,7 +58329,7 @@
           <t>A1 | 559呎 (2房)
 $1287万
 $23,022/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -58337,7 +58337,7 @@
           <t>A2 | 443呎 (2房)
 $1067万
 $24,083/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -58345,7 +58345,7 @@
           <t>A3 | 443呎 (2房)
 $1067万
 $24,083/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -58353,7 +58353,7 @@
           <t>A5 | 887呎 (4+房)
 $2361万
 $26,617/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
@@ -58362,7 +58362,7 @@
           <t>B1 | 459呎 (2房)
 $968万
 $21,082/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -58370,7 +58370,7 @@
           <t>B2 | 298呎 (1房)
 $673万
 $22,585/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -58378,7 +58378,7 @@
           <t>B3 | 301呎 (1房)
 $680万
 $22,584/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -58386,7 +58386,7 @@
           <t>B5 | 298呎 (1房)
 $673万
 $22,585/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -58394,7 +58394,7 @@
           <t>B6 | 437呎 (2房)
 $954万
 $21,822/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr"/>
@@ -58416,7 +58416,7 @@
           <t>A1 | 559呎 (2房)
 $1285万
 $22,990/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -58424,7 +58424,7 @@
           <t>A2 | 443呎 (2房)
 $1023万
 $23,103/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -58432,7 +58432,7 @@
           <t>A3 | 443呎 (2房)
 $1023万
 $23,103/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -58440,7 +58440,7 @@
           <t>A5 | 887呎 (4+房)
 $2536万
 $28,591/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
@@ -58449,7 +58449,7 @@
           <t>B1 | 458呎 (2房)
 $963万
 $21,023/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -58457,7 +58457,7 @@
           <t>B2 | 298呎 (1房)
 $671万
 $22,517/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -58465,7 +58465,7 @@
           <t>B3 | 301呎 (1房)
 $677万
 $22,484/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -58473,7 +58473,7 @@
           <t>B5 | 298呎 (1房)
 $671万
 $22,517/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -58481,7 +58481,7 @@
           <t>B6 | 437呎 (2房)
 $949万
 $21,713/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr"/>
@@ -58503,7 +58503,7 @@
           <t>A1 | 559呎 (2房)
 $1308万
 $23,406/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -58511,7 +58511,7 @@
           <t>A2 | 443呎 (2房)
 $1020万
 $23,033/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -58519,7 +58519,7 @@
           <t>A3 | 443呎 (2房)
 $1062万
 $23,965/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -58527,7 +58527,7 @@
           <t>A5 | 887呎 (4+房)
 $2302万
 $25,950/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
@@ -58536,7 +58536,7 @@
           <t>B1 | 458呎 (2房)
 $960万
 $20,960/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -58544,15 +58544,15 @@
           <t>B2 | 298呎 (1房)
 $691万
 $23,198/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
         <is>
-          <t>B3 | 301呎 (1房)
+          <t>B3 | 300呎 (1房)
 $676万
-$22,449/呎
-(24年-11月-03日)</t>
+$22,524/呎
+(24年-11月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -58560,7 +58560,7 @@
           <t>B5 | 298呎 (1房)
 $669万
 $22,449/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -58568,7 +58568,7 @@
           <t>B6 | 437呎 (2房)
 $946万
 $21,648/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr"/>
@@ -58590,7 +58590,7 @@
           <t>A1 | 559呎 (2房)
 $1304万
 $23,336/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -58598,7 +58598,7 @@
           <t>A2 | 443呎 (2房)
 $1017万
 $22,965/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -58606,7 +58606,7 @@
           <t>A3 | 443呎 (2房)
 $1058万
 $23,894/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -58614,7 +58614,7 @@
           <t>A5 | 887呎 (4+房)
 $2399万
 $27,046/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr"/>
@@ -58623,7 +58623,7 @@
           <t>B1 | 458呎 (2房)
 $957万
 $20,898/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -58631,7 +58631,7 @@
           <t>B2 | 298呎 (1房)
 $667万
 $22,382/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -58639,7 +58639,7 @@
           <t>B3 | 300呎 (1房)
 $674万
 $22,457/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -58647,7 +58647,7 @@
           <t>B5 | 298呎 (1房)
 $667万
 $22,382/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -58655,7 +58655,7 @@
           <t>B6 | 437呎 (2房)
 $943万
 $21,584/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr"/>
@@ -58677,7 +58677,7 @@
           <t>A1 | 559呎 (2房)
 $1301万
 $23,266/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -58685,7 +58685,7 @@
           <t>A2 | 443呎 (2房)
 $1110万
 $25,053/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -58693,7 +58693,7 @@
           <t>A3 | 443呎 (2房)
 $1110万
 $25,053/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -58701,7 +58701,7 @@
           <t>A5 | 887呎 (4+房)
 $2357万
 $26,574/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
@@ -58710,7 +58710,7 @@
           <t>B1 | 458呎 (2房)
 $954万
 $20,835/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -58718,7 +58718,7 @@
           <t>B2 | 298呎 (1房)
 $665万
 $22,315/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -58726,7 +58726,7 @@
           <t>B3 | 301呎 (1房)
 $672万
 $22,315/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -58734,7 +58734,7 @@
           <t>B5 | 298呎 (1房)
 $665万
 $22,315/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -58742,7 +58742,7 @@
           <t>B6 | 437呎 (2房)
 $940万
 $21,519/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr"/>
@@ -58764,7 +58764,7 @@
           <t>A1 | 559呎 (2房)
 $1383万
 $24,738/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -58772,7 +58772,7 @@
           <t>A2 | 443呎 (2房)
 $1108万
 $25,003/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -58780,7 +58780,7 @@
           <t>A3 | 443呎 (2房)
 $1108万
 $25,003/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -58788,7 +58788,7 @@
           <t>A5 | 887呎 (4+房)
 $2265万
 $25,533/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -58797,7 +58797,7 @@
           <t>B1 | 458呎 (2房)
 $952万
 $20,794/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -58805,7 +58805,7 @@
           <t>B2 | 298呎 (1房)
 $664万
 $22,271/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -58813,7 +58813,7 @@
           <t>B3 | 301呎 (1房)
 $670万
 $22,271/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -58821,7 +58821,7 @@
           <t>B5 | 298呎 (1房)
 $663万
 $22,237/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -58829,7 +58829,7 @@
           <t>B6 | 437呎 (2房)
 $938万
 $21,476/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr"/>
@@ -58851,7 +58851,7 @@
           <t>A1 | 559呎 (2房)
 $1380万
 $24,689/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -58859,7 +58859,7 @@
           <t>A2 | 443呎 (2房)
 $1105万
 $24,953/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -58867,7 +58867,7 @@
           <t>A3 | 443呎 (2房)
 $1105万
 $24,953/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -58875,7 +58875,7 @@
           <t>A5 | 887呎 (4+房)
 $2431万
 $27,405/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -58884,7 +58884,7 @@
           <t>B1 | 458呎 (2房)
 $950万
 $20,752/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -58892,7 +58892,7 @@
           <t>B2 | 298呎 (1房)
 $684万
 $22,967/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -58900,7 +58900,7 @@
           <t>B3 | 301呎 (1房)
 $669万
 $22,226/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -58908,7 +58908,7 @@
           <t>B5 | 298呎 (1房)
 $662万
 $22,226/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -58916,7 +58916,7 @@
           <t>B6 | 437呎 (2房)
 $937万
 $21,433/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr"/>
@@ -58938,7 +58938,7 @@
           <t>A1 | 559呎 (2房)
 $1377万
 $24,640/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -58946,7 +58946,7 @@
           <t>A2 | 443呎 (2房)
 $1103万
 $24,903/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -58954,7 +58954,7 @@
           <t>A3 | 443呎 (2房)
 $1103万
 $24,903/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -58962,7 +58962,7 @@
           <t>A5 | 887呎 (4+房)
 $2321万
 $26,165/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
@@ -58971,7 +58971,7 @@
           <t>B1 | 458呎 (2房)
 $912万
 $19,905/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -58979,7 +58979,7 @@
           <t>B2 | 298呎 (1房)
 $661万
 $22,182/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -58987,7 +58987,7 @@
           <t>B3 | 300呎 (1房)
 $668万
 $22,256/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -58995,7 +58995,7 @@
           <t>B5 | 298呎 (1房)
 $661万
 $22,182/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -59003,7 +59003,7 @@
           <t>B6 | 437呎 (2房)
 $935万
 $21,390/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr"/>
@@ -59025,7 +59025,7 @@
           <t>A1 | 559呎 (2房)
 $1321万
 $23,634/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -59033,7 +59033,7 @@
           <t>A2 | 443呎 (2房)
 $1101万
 $24,853/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -59041,7 +59041,7 @@
           <t>A3 | 443呎 (2房)
 $1101万
 $24,853/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -59049,7 +59049,7 @@
           <t>A5 | 887呎 (4+房)
 $2498万
 $28,162/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr"/>
@@ -59058,7 +59058,7 @@
           <t>B1 | 458呎 (2房)
 $947万
 $20,669/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -59066,7 +59066,7 @@
           <t>B2 | 298呎 (1房)
 $660万
 $22,138/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -59074,7 +59074,7 @@
           <t>B3 | 301呎 (1房)
 $666万
 $22,138/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -59082,7 +59082,7 @@
           <t>B5 | 298呎 (1房)
 $660万
 $22,138/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -59090,7 +59090,7 @@
           <t>B6 | 437呎 (2房)
 $933万
 $21,348/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M32" s="20" t="inlineStr"/>
@@ -59112,7 +59112,7 @@
           <t>A1 | 559呎 (2房)
 $1372万
 $24,541/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -59120,7 +59120,7 @@
           <t>A2 | 443呎 (2房)
 $1099万
 $24,803/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -59128,7 +59128,7 @@
           <t>A3 | 443呎 (2房)
 $1099万
 $24,803/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -59136,7 +59136,7 @@
           <t>A5 | 887呎 (4+房)
 $2339万
 $26,368/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr"/>
@@ -59145,7 +59145,7 @@
           <t>B1 | 458呎 (2房)
 $945万
 $20,628/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -59153,7 +59153,7 @@
           <t>B2 | 298呎 (1房)
 $658万
 $22,093/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -59161,7 +59161,7 @@
           <t>B3 | 301呎 (1房)
 $665万
 $22,093/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -59169,7 +59169,7 @@
           <t>B5 | 298呎 (1房)
 $658万
 $22,093/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -59177,7 +59177,7 @@
           <t>B6 | 437呎 (2房)
 $931万
 $21,305/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr"/>
@@ -59199,7 +59199,7 @@
           <t>A1 | 559呎 (2房)
 $1316万
 $23,540/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -59207,7 +59207,7 @@
           <t>A2 | 443呎 (2房)
 $1097万
 $24,754/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -59215,7 +59215,7 @@
           <t>A3 | 443呎 (2房)
 $1097万
 $24,754/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -59223,7 +59223,7 @@
           <t>A5 | 887呎 (4+房)
 $2328万
 $26,246/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -59232,7 +59232,7 @@
           <t>B1 | 458呎 (2房)
 $943万
 $20,586/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -59240,7 +59240,7 @@
           <t>B2 | 298呎 (1房)
 $657万
 $22,049/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -59248,7 +59248,7 @@
           <t>B3 | 301呎 (1房)
 $664万
 $22,049/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -59256,7 +59256,7 @@
           <t>B5 | 298呎 (1房)
 $657万
 $22,049/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -59264,7 +59264,7 @@
           <t>B6 | 437呎 (2房)
 $929万
 $21,262/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M34" s="20" t="inlineStr"/>
@@ -59286,7 +59286,7 @@
           <t>A1 | 559呎 (2房)
 $1341万
 $23,990/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -59294,7 +59294,7 @@
           <t>A2 | 443呎 (2房)
 $1093万
 $24,679/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -59302,7 +59302,7 @@
           <t>A3 | 443呎 (2房)
 $1093万
 $24,679/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -59310,7 +59310,7 @@
           <t>A5 | 887呎 (4+房)
 $2404万
 $27,105/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
@@ -59319,7 +59319,7 @@
           <t>B1 | 458呎 (2房)
 $940万
 $20,525/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -59327,7 +59327,7 @@
           <t>B2 | 298呎 (1房)
 $655万
 $21,983/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -59335,7 +59335,7 @@
           <t>B3 | 301呎 (1房)
 $662万
 $21,983/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -59343,7 +59343,7 @@
           <t>B5 | 298呎 (1房)
 $655万
 $21,983/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -59351,7 +59351,7 @@
           <t>B6 | 437呎 (2房)
 $926万
 $21,198/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M35" s="20" t="inlineStr"/>
@@ -59373,7 +59373,7 @@
           <t>A1 | 559呎 (2房)
 $1337万
 $23,918/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -59381,7 +59381,7 @@
           <t>A2 | 443呎 (2房)
 $1090万
 $24,605/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -59389,7 +59389,7 @@
           <t>A3 | 443呎 (2房)
 $1090万
 $24,605/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -59397,7 +59397,7 @@
           <t>A5 | 887呎 (4+房)
 $2204万
 $24,848/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr"/>
@@ -59406,7 +59406,7 @@
           <t>B1 | 458呎 (2房)
 $937万
 $20,463/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -59414,7 +59414,7 @@
           <t>B2 | 298呎 (1房)
 $653万
 $21,917/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -59422,7 +59422,7 @@
           <t>B3 | 300呎 (1房)
 $660万
 $21,990/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -59430,7 +59430,7 @@
           <t>B5 | 298呎 (1房)
 $653万
 $21,917/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -59438,7 +59438,7 @@
           <t>B6 | 437呎 (2房)
 $924万
 $21,135/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M36" s="20" t="inlineStr"/>
@@ -59460,7 +59460,7 @@
           <t>A1 | 559呎 (2房)
 $1262万
 $22,569/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -59468,7 +59468,7 @@
           <t>A2 | 443呎 (2房)
 $1067万
 $24,093/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -59476,7 +59476,7 @@
           <t>A3 | 443呎 (2房)
 $1067万
 $24,093/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -59484,7 +59484,7 @@
           <t>A5 | 887呎 (4+房)
 $2220万
 $25,028/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
@@ -59493,7 +59493,7 @@
           <t>B1 | 458呎 (2房)
 $934万
 $20,402/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -59501,7 +59501,7 @@
           <t>B2 | 298呎 (1房)
 $651万
 $21,851/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -59509,7 +59509,7 @@
           <t>B3 | 300呎 (1房)
 $658万
 $21,924/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -59517,7 +59517,7 @@
           <t>B5 | 298呎 (1房)
 $651万
 $21,851/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -59525,7 +59525,7 @@
           <t>B6 | 437呎 (2房)
 $921万
 $21,071/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M37" s="20" t="inlineStr"/>
@@ -59547,7 +59547,7 @@
           <t>A1 | 559呎 (2房)
 $1252万
 $22,391/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -59555,7 +59555,7 @@
           <t>A2 | 443呎 (2房)
 $1060万
 $23,931/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -59563,7 +59563,7 @@
           <t>A3 | 443呎 (2房)
 $1060万
 $23,931/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -59571,7 +59571,7 @@
           <t>A5 | 887呎 (4+房)
 $2266万
 $25,547/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
@@ -59580,7 +59580,7 @@
           <t>B1 | 458呎 (2房)
 $927万
 $20,247/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -59588,7 +59588,7 @@
           <t>B2 | 298呎 (1房)
 $646万
 $21,688/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -59596,7 +59596,7 @@
           <t>B3 | 301呎 (1房)
 $652万
 $21,655/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
@@ -59604,7 +59604,7 @@
           <t>B5 | 298呎 (1房)
 $646万
 $21,688/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
@@ -59612,7 +59612,7 @@
           <t>B6 | 437呎 (2房)
 $914万
 $20,911/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M38" s="20" t="inlineStr"/>
@@ -59634,7 +59634,7 @@
           <t>A1 | 559呎 (2房)
 $1213万
 $21,697/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -59642,7 +59642,7 @@
           <t>A2 | 443呎 (2房)
 $1004万
 $22,671/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -59650,7 +59650,7 @@
           <t>A3 | 443呎 (2房)
 $1004万
 $22,671/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -59658,7 +59658,7 @@
           <t>A5 | 887呎 (4+房)
 $2127万
 $23,977/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -59667,7 +59667,7 @@
           <t>B1 | 458呎 (2房)
 $919万
 $20,059/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -59675,7 +59675,7 @@
           <t>B2 | 298呎 (1房)
 $640万
 $21,492/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
@@ -59683,7 +59683,7 @@
           <t>B3 | 301呎 (1房)
 $647万
 $21,492/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K39" s="22" t="inlineStr">
@@ -59691,7 +59691,7 @@
           <t>B5 | 298呎 (1房)
 $640万
 $21,492/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr">
@@ -59699,7 +59699,7 @@
           <t>B6 | 438呎 (2房)
 $905万
 $20,670/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr"/>
@@ -59721,7 +59721,7 @@
           <t>A1 | 559呎 (2房)
 $1125万
 $20,125/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -59729,7 +59729,7 @@
           <t>A2 | 443呎 (2房)
 $964万
 $21,765/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
@@ -59737,7 +59737,7 @@
           <t>A3 | 443呎 (2房)
 $964万
 $21,765/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -59745,7 +59745,7 @@
           <t>A5 | 887呎 (4+房)
 $2079万
 $23,439/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -59754,7 +59754,7 @@
           <t>B1 | 458呎 (2房)
 $906万
 $19,777/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I40" s="22" t="inlineStr">
@@ -59762,7 +59762,7 @@
           <t>B2 | 298呎 (1房)
 $632万
 $21,199/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J40" s="22" t="inlineStr">
@@ -59770,7 +59770,7 @@
           <t>B3 | 301呎 (1房)
 $638万
 $21,199/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K40" s="22" t="inlineStr">
@@ -59778,7 +59778,7 @@
           <t>B5 | 298呎 (1房)
 $632万
 $21,199/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr">
@@ -59786,7 +59786,7 @@
           <t>B6 | 437呎 (2房)
 $922万
 $21,107/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M40" s="20" t="inlineStr"/>
@@ -59808,7 +59808,7 @@
           <t>A1 | 559呎 (2房)
 $1012万
 $18,112/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -59816,7 +59816,7 @@
           <t>A2 | 443呎 (2房)
 $868万
 $19,588/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
@@ -59824,7 +59824,7 @@
           <t>A3 | 443呎 (2房)
 $868万
 $19,588/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
@@ -59832,7 +59832,7 @@
           <t>A5 | 854呎 (3房)
 $1869万
 $21,888/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
@@ -59841,7 +59841,7 @@
           <t>B1 | 459呎 (2房)
 $874万
 $19,043/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I41" s="22" t="inlineStr">
@@ -59849,7 +59849,7 @@
           <t>B2 | 298呎 (1房)
 $610万
 $20,457/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr">
@@ -59857,7 +59857,7 @@
           <t>B3 | 301呎 (1房)
 $616万
 $20,457/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K41" s="22" t="inlineStr">
@@ -59865,7 +59865,7 @@
           <t>B5 | 298呎 (1房)
 $610万
 $20,457/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L41" s="22" t="inlineStr">
@@ -59873,7 +59873,7 @@
           <t>B6 | 437呎 (2房)
 $890万
 $20,368/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M41" s="20" t="inlineStr"/>
@@ -60219,7 +60219,7 @@
           <t>A | 929呎 (4+房)
 $3300万
 $35,522/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -60233,7 +60233,7 @@
           <t>B | 686呎 (3房)
 $1967万
 $28,676/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr"/>
@@ -60247,7 +60247,7 @@
           <t>C | 919呎 (3房)
 $2900万
 $31,556/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -60255,7 +60255,7 @@
           <t>D | 655呎 (2房)
 $1469万
 $22,430/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R7" s="22" t="inlineStr">
@@ -60263,7 +60263,7 @@
           <t>E | 457呎 (2房)
 $991万
 $21,674/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S7" s="22" t="inlineStr">
@@ -60271,7 +60271,7 @@
           <t>F | 458呎 (2房)
 $991万
 $21,627/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T7" s="22" t="inlineStr">
@@ -60279,7 +60279,7 @@
           <t>G | 614呎 (2房)
 $1420万
 $23,127/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U7" s="20" t="inlineStr"/>
@@ -60298,7 +60298,7 @@
           <t>A | 929呎 (4+房)
 $3104万
 $33,408/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -60312,7 +60312,7 @@
           <t>B | 686呎 (3房)
 $1961万
 $28,591/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr"/>
@@ -60326,7 +60326,7 @@
           <t>C | 919呎 (3房)
 $2966万
 $32,276/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -60334,7 +60334,7 @@
           <t>D | 655呎 (2房)
 $1465万
 $22,363/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R8" s="22" t="inlineStr">
@@ -60342,7 +60342,7 @@
           <t>E | 457呎 (2房)
 $988万
 $21,609/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="S8" s="22" t="inlineStr">
@@ -60350,7 +60350,7 @@
           <t>F | 458呎 (2房)
 $988万
 $21,562/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="T8" s="22" t="inlineStr">
@@ -60358,7 +60358,7 @@
           <t>G | 614呎 (2房)
 $1416万
 $23,058/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr"/>
@@ -60377,7 +60377,7 @@
           <t>A | 929呎 (4+房)
 $3236万
 $34,835/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -60391,7 +60391,7 @@
           <t>B | 686呎 (3房)
 $1879万
 $27,397/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr"/>
@@ -60405,7 +60405,7 @@
           <t>C | 919呎 (3房)
 $2711万
 $29,499/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q9" s="22" t="inlineStr">
@@ -60413,7 +60413,7 @@
           <t>D | 655呎 (2房)
 $1460万
 $22,296/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R9" s="22" t="inlineStr">
@@ -60421,7 +60421,7 @@
           <t>E | 457呎 (2房)
 $985万
 $21,545/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S9" s="22" t="inlineStr">
@@ -60429,7 +60429,7 @@
           <t>F | 458呎 (2房)
 $985万
 $21,498/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T9" s="22" t="inlineStr">
@@ -60437,7 +60437,7 @@
           <t>G | 614呎 (2房)
 $1412万
 $22,989/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U9" s="20" t="inlineStr"/>
@@ -60456,7 +60456,7 @@
           <t>A | 929呎 (4+房)
 $3053万
 $32,861/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -60470,7 +60470,7 @@
           <t>B | 686呎 (3房)
 $1950万
 $28,420/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr"/>
@@ -60484,7 +60484,7 @@
           <t>C | 919呎 (3房)
 $2874万
 $31,271/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -60492,7 +60492,7 @@
           <t>D | 655呎 (2房)
 $1456万
 $22,229/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R10" s="22" t="inlineStr">
@@ -60500,7 +60500,7 @@
           <t>E | 457呎 (2房)
 $1014万
 $22,196/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S10" s="22" t="inlineStr">
@@ -60508,7 +60508,7 @@
           <t>F | 458呎 (2房)
 $982万
 $21,433/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T10" s="22" t="inlineStr">
@@ -60516,7 +60516,7 @@
           <t>G | 614呎 (2房)
 $1407万
 $22,920/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U10" s="20" t="inlineStr"/>
@@ -60535,7 +60535,7 @@
           <t>A | 929呎 (4+房)
 $3001万
 $32,305/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -60549,7 +60549,7 @@
           <t>B | 686呎 (3房)
 $1944万
 $28,334/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr"/>
@@ -60563,7 +60563,7 @@
           <t>C | 919呎 (3房)
 $2688万
 $29,249/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -60571,7 +60571,7 @@
           <t>D | 655呎 (2房)
 $1452万
 $22,163/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R11" s="22" t="inlineStr">
@@ -60579,7 +60579,7 @@
           <t>E | 457呎 (2房)
 $979万
 $21,416/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="S11" s="22" t="inlineStr">
@@ -60587,7 +60587,7 @@
           <t>F | 458呎 (2房)
 $979万
 $21,369/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="T11" s="22" t="inlineStr">
@@ -60595,7 +60595,7 @@
           <t>G | 614呎 (2房)
 $1403万
 $22,851/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U11" s="20" t="inlineStr"/>
@@ -60614,7 +60614,7 @@
           <t>A | 929呎 (4+房)
 $3001万
 $32,300/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -60628,7 +60628,7 @@
           <t>B | 686呎 (3房)
 $1938万
 $28,249/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr"/>
@@ -60642,7 +60642,7 @@
           <t>C | 919呎 (3房)
 $2662万
 $28,972/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -60650,7 +60650,7 @@
           <t>D | 655呎 (2房)
 $1447万
 $22,096/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="R12" s="22" t="inlineStr">
@@ -60658,7 +60658,7 @@
           <t>E | 457呎 (2房)
 $976万
 $21,351/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="S12" s="22" t="inlineStr">
@@ -60666,7 +60666,7 @@
           <t>F | 458呎 (2房)
 $976万
 $21,305/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T12" s="22" t="inlineStr">
@@ -60674,7 +60674,7 @@
           <t>G | 614呎 (2房)
 $1399万
 $22,783/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U12" s="20" t="inlineStr"/>
@@ -60693,7 +60693,7 @@
           <t>A | 929呎 (4+房)
 $2856万
 $30,743/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -60707,7 +60707,7 @@
           <t>B | 686呎 (3房)
 $1932万
 $28,164/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr"/>
@@ -60721,7 +60721,7 @@
           <t>C | 919呎 (3房)
 $2835万
 $30,849/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -60729,7 +60729,7 @@
           <t>D | 655呎 (2房)
 $1443万
 $22,030/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="R13" s="22" t="inlineStr">
@@ -60737,7 +60737,7 @@
           <t>E | 457呎 (2房)
 $973万
 $21,287/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="S13" s="22" t="inlineStr">
@@ -60745,7 +60745,7 @@
           <t>F | 458呎 (2房)
 $973万
 $21,241/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="T13" s="22" t="inlineStr">
@@ -60753,7 +60753,7 @@
           <t>G | 614呎 (2房)
 $1340万
 $21,831/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U13" s="20" t="inlineStr"/>
@@ -60772,7 +60772,7 @@
           <t>A | 929呎 (4+房)
 $3100万
 $33,369/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr"/>
@@ -60786,7 +60786,7 @@
           <t>B | 687呎 (3房)
 $1851万
 $26,949/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr"/>
@@ -60800,7 +60800,7 @@
           <t>C | 919呎 (3房)
 $2766万
 $30,098/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="Q14" s="22" t="inlineStr">
@@ -60808,7 +60808,7 @@
           <t>D | 655呎 (2房)
 $1809万
 $27,621/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R14" s="22" t="inlineStr">
@@ -60816,7 +60816,7 @@
           <t>E | 457呎 (2房)
 $1110万
 $24,289/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S14" s="21" t="inlineStr">
@@ -60852,7 +60852,7 @@
           <t>A1 | 501呎 (2房)
 $1182万
 $23,585/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -60860,7 +60860,7 @@
           <t>A2 | 295呎 (1房)
 $745万
 $25,241/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -60868,7 +60868,7 @@
           <t>A3 | 299呎 (1房)
 $748万
 $25,015/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -60876,7 +60876,7 @@
           <t>A5 | 299呎 (1房)
 $748万
 $25,015/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -60884,7 +60884,7 @@
           <t>A6 | 297呎 (1房)
 $748万
 $25,177/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -60892,7 +60892,7 @@
           <t>A8 | 509呎 (2房)
 $1152万
 $22,634/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr"/>
@@ -60901,7 +60901,7 @@
           <t>B1 | 454呎 (2房)
 $994万
 $21,884/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -60909,7 +60909,7 @@
           <t>B2 | 299呎 (1房)
 $661万
 $22,121/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -60917,7 +60917,7 @@
           <t>B3 | 296呎 (1房)
 $655万
 $22,121/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -60925,7 +60925,7 @@
           <t>B5 | 240呎 (开放式)
 $573万
 $23,863/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -60933,7 +60933,7 @@
           <t>B6 | 236呎 (开放式)
 $566万
 $23,997/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">
@@ -60941,7 +60941,7 @@
           <t>B8 | 460呎 (2房)
 $959万
 $20,838/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr"/>
@@ -60966,7 +60966,7 @@
           <t>A1 | 501呎 (2房)
 $1162万
 $23,193/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -60974,7 +60974,7 @@
           <t>A2 | 295呎 (1房)
 $737万
 $24,992/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -60982,7 +60982,7 @@
           <t>A3 | 299呎 (1房)
 $741万
 $24,767/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -60990,7 +60990,7 @@
           <t>A5 | 298呎 (1房)
 $741万
 $24,850/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -60998,7 +60998,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,927/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -61006,7 +61006,7 @@
           <t>A8 | 509呎 (2房)
 $1132万
 $22,243/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr"/>
@@ -61015,7 +61015,7 @@
           <t>B1 | 454呎 (2房)
 $988万
 $21,753/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -61023,7 +61023,7 @@
           <t>B2 | 299呎 (1房)
 $659万
 $22,033/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -61031,7 +61031,7 @@
           <t>B3 | 296呎 (1房)
 $652万
 $22,033/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -61039,7 +61039,7 @@
           <t>B5 | 240呎 (开放式)
 $568万
 $23,678/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -61047,7 +61047,7 @@
           <t>B6 | 236呎 (开放式)
 $562万
 $23,808/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O16" s="22" t="inlineStr">
@@ -61055,7 +61055,7 @@
           <t>B8 | 460呎 (2房)
 $953万
 $20,714/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr"/>
@@ -61080,7 +61080,7 @@
           <t>A1 | 501呎 (2房)
 $1148万
 $22,918/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -61088,7 +61088,7 @@
           <t>A2 | 295呎 (1房)
 $737万
 $24,971/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -61096,7 +61096,7 @@
           <t>A3 | 298呎 (1房)
 $740万
 $24,826/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -61104,7 +61104,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,743/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -61112,7 +61112,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,903/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -61120,7 +61120,7 @@
           <t>A8 | 509呎 (2房)
 $1118万
 $21,969/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr"/>
@@ -61129,7 +61129,7 @@
           <t>B1 | 454呎 (2房)
 $984万
 $21,667/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -61137,7 +61137,7 @@
           <t>B2 | 299呎 (1房)
 $657万
 $21,989/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -61145,7 +61145,7 @@
           <t>B3 | 296呎 (1房)
 $650万
 $21,955/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -61153,7 +61153,7 @@
           <t>B5 | 240呎 (开放式)
 $565万
 $23,539/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -61161,7 +61161,7 @@
           <t>B6 | 236呎 (开放式)
 $559万
 $23,669/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O17" s="22" t="inlineStr">
@@ -61169,7 +61169,7 @@
           <t>B8 | 460呎 (2房)
 $949万
 $20,632/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr"/>
@@ -61194,7 +61194,7 @@
           <t>A1 | 501呎 (2房)
 $1144万
 $22,840/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -61202,7 +61202,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,936/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -61210,7 +61210,7 @@
           <t>A3 | 299呎 (1房)
 $739万
 $24,709/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -61218,7 +61218,7 @@
           <t>A5 | 299呎 (1房)
 $739万
 $24,709/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -61226,7 +61226,7 @@
           <t>A6 | 297呎 (1房)
 $739万
 $24,870/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -61234,7 +61234,7 @@
           <t>A8 | 509呎 (2房)
 $1113万
 $21,871/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr"/>
@@ -61243,7 +61243,7 @@
           <t>B1 | 454呎 (2房)
 $980万
 $21,580/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -61251,7 +61251,7 @@
           <t>B2 | 299呎 (1房)
 $656万
 $21,945/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -61259,7 +61259,7 @@
           <t>B3 | 296呎 (1房)
 $650万
 $21,945/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -61267,7 +61267,7 @@
           <t>B5 | 240呎 (开放式)
 $562万
 $23,400/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -61275,7 +61275,7 @@
           <t>B6 | 236呎 (开放式)
 $534万
 $22,614/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O18" s="22" t="inlineStr">
@@ -61283,7 +61283,7 @@
           <t>B8 | 460呎 (2房)
 $945万
 $20,549/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr"/>
@@ -61308,7 +61308,7 @@
           <t>A1 | 501呎 (2房)
 $1136万
 $22,674/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -61316,7 +61316,7 @@
           <t>A2 | 295呎 (1房)
 $735万
 $24,901/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -61324,7 +61324,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,673/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -61332,7 +61332,7 @@
           <t>A5 | 299呎 (1房)
 $737万
 $24,640/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -61340,7 +61340,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,833/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -61348,7 +61348,7 @@
           <t>A8 | 509呎 (2房)
 $1106万
 $21,725/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr"/>
@@ -61357,7 +61357,7 @@
           <t>B1 | 454呎 (2房)
 $976万
 $21,494/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -61365,7 +61365,7 @@
           <t>B2 | 299呎 (1房)
 $655万
 $21,901/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -61373,7 +61373,7 @@
           <t>B3 | 296呎 (1房)
 $648万
 $21,901/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -61381,7 +61381,7 @@
           <t>B5 | 240呎 (开放式)
 $549万
 $22,870/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -61389,7 +61389,7 @@
           <t>B6 | 236呎 (开放式)
 $545万
 $23,102/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O19" s="22" t="inlineStr">
@@ -61397,7 +61397,7 @@
           <t>B8 | 460呎 (2房)
 $941万
 $20,467/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr"/>
@@ -61422,7 +61422,7 @@
           <t>A1 | 501呎 (2房)
 $1250万
 $24,942/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -61430,7 +61430,7 @@
           <t>A2 | 295呎 (1房)
 $734万
 $24,865/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -61438,7 +61438,7 @@
           <t>A3 | 299呎 (1房)
 $737万
 $24,637/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -61446,7 +61446,7 @@
           <t>A5 | 298呎 (1房)
 $737万
 $24,720/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -61454,7 +61454,7 @@
           <t>A6 | 297呎 (1房)
 $736万
 $24,797/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -61462,7 +61462,7 @@
           <t>A8 | 509呎 (2房)
 $1101万
 $21,639/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr"/>
@@ -61471,7 +61471,7 @@
           <t>B1 | 454呎 (2房)
 $972万
 $21,409/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -61479,7 +61479,7 @@
           <t>B2 | 299呎 (1房)
 $652万
 $21,814/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -61487,7 +61487,7 @@
           <t>B3 | 296呎 (1房)
 $646万
 $21,814/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -61495,7 +61495,7 @@
           <t>B5 | 240呎 (开放式)
 $547万
 $22,779/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -61503,7 +61503,7 @@
           <t>B6 | 236呎 (开放式)
 $543万
 $23,010/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O20" s="22" t="inlineStr">
@@ -61511,7 +61511,7 @@
           <t>B8 | 460呎 (2房)
 $938万
 $20,386/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr"/>
@@ -61536,7 +61536,7 @@
           <t>A1 | 501呎 (2房)
 $1246万
 $24,868/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -61544,7 +61544,7 @@
           <t>A2 | 295呎 (1房)
 $760万
 $25,766/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -61552,7 +61552,7 @@
           <t>A3 | 299呎 (1房)
 $764万
 $25,535/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -61560,7 +61560,7 @@
           <t>A5 | 299呎 (1房)
 $762万
 $25,502/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -61568,7 +61568,7 @@
           <t>A6 | 297呎 (1房)
 $763万
 $25,700/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -61576,7 +61576,7 @@
           <t>A8 | 509呎 (2房)
 $1098万
 $21,574/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr"/>
@@ -61585,7 +61585,7 @@
           <t>B1 | 454呎 (2房)
 $969万
 $21,345/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -61593,7 +61593,7 @@
           <t>B2 | 299呎 (1房)
 $650万
 $21,749/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -61601,7 +61601,7 @@
           <t>B3 | 296呎 (1房)
 $644万
 $21,749/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -61609,7 +61609,7 @@
           <t>B5 | 240呎 (开放式)
 $545万
 $22,710/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -61617,7 +61617,7 @@
           <t>B6 | 236呎 (开放式)
 $541万
 $22,941/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O21" s="22" t="inlineStr">
@@ -61625,7 +61625,7 @@
           <t>B8 | 460呎 (2房)
 $935万
 $20,325/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr"/>
@@ -61650,7 +61650,7 @@
           <t>A1 | 501呎 (2房)
 $1242万
 $24,793/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -61658,7 +61658,7 @@
           <t>A2 | 295呎 (1房)
 $758万
 $25,689/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -61666,7 +61666,7 @@
           <t>A3 | 299呎 (1房)
 $761万
 $25,459/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -61674,7 +61674,7 @@
           <t>A5 | 299呎 (1房)
 $761万
 $25,459/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -61682,7 +61682,7 @@
           <t>A6 | 297呎 (1房)
 $761万
 $25,624/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -61690,7 +61690,7 @@
           <t>A8 | 509呎 (2房)
 $1095万
 $21,509/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr"/>
@@ -61699,7 +61699,7 @@
           <t>B1 | 454呎 (2房)
 $966万
 $21,281/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -61707,7 +61707,7 @@
           <t>B2 | 299呎 (1房)
 $648万
 $21,684/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -61715,7 +61715,7 @@
           <t>B3 | 296呎 (1房)
 $642万
 $21,684/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -61723,7 +61723,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,642/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -61731,7 +61731,7 @@
           <t>B6 | 236呎 (开放式)
 $540万
 $22,872/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O22" s="22" t="inlineStr">
@@ -61739,7 +61739,7 @@
           <t>B8 | 460呎 (2房)
 $931万
 $20,242/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr"/>
@@ -61764,7 +61764,7 @@
           <t>A1 | 501呎 (2房)
 $1238万
 $24,719/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -61772,7 +61772,7 @@
           <t>A2 | 295呎 (1房)
 $740万
 $25,100/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -61780,7 +61780,7 @@
           <t>A3 | 299呎 (1房)
 $745万
 $24,908/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -61788,7 +61788,7 @@
           <t>A5 | 299呎 (1房)
 $745万
 $24,908/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -61796,7 +61796,7 @@
           <t>A6 | 297呎 (1房)
 $744万
 $25,036/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -61804,7 +61804,7 @@
           <t>A8 | 509呎 (2房)
 $1092万
 $21,445/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr"/>
@@ -61813,7 +61813,7 @@
           <t>B1 | 454呎 (2房)
 $963万
 $21,217/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -61821,7 +61821,7 @@
           <t>B2 | 299呎 (1房)
 $645万
 $21,585/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -61829,7 +61829,7 @@
           <t>B3 | 296呎 (1房)
 $640万
 $21,619/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -61837,7 +61837,7 @@
           <t>B5 | 240呎 (开放式)
 $542万
 $22,575/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -61845,7 +61845,7 @@
           <t>B6 | 236呎 (开放式)
 $538万
 $22,804/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O23" s="22" t="inlineStr">
@@ -61853,7 +61853,7 @@
           <t>B8 | 460呎 (2房)
 $929万
 $20,203/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr"/>
@@ -61878,7 +61878,7 @@
           <t>A1 | 501呎 (2房)
 $1235万
 $24,645/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -61886,7 +61886,7 @@
           <t>A2 | 295呎 (1房)
 $739万
 $25,059/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -61894,7 +61894,7 @@
           <t>A3 | 299呎 (1房)
 $742万
 $24,800/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -61902,7 +61902,7 @@
           <t>A5 | 299呎 (1房)
 $743万
 $24,833/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -61910,7 +61910,7 @@
           <t>A6 | 297呎 (1房)
 $741万
 $24,961/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -61918,7 +61918,7 @@
           <t>A8 | 509呎 (2房)
 $1087万
 $21,361/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr"/>
@@ -61927,7 +61927,7 @@
           <t>B1 | 454呎 (2房)
 $960万
 $21,154/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -61935,7 +61935,7 @@
           <t>B2 | 299呎 (1房)
 $643万
 $21,521/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -61943,7 +61943,7 @@
           <t>B3 | 296呎 (1房)
 $638万
 $21,554/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -61951,7 +61951,7 @@
           <t>B5 | 240呎 (开放式)
 $540万
 $22,508/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -61959,7 +61959,7 @@
           <t>B6 | 236呎 (开放式)
 $537万
 $22,736/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O24" s="22" t="inlineStr">
@@ -61967,7 +61967,7 @@
           <t>B8 | 460呎 (2房)
 $927万
 $20,143/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr"/>
@@ -61992,7 +61992,7 @@
           <t>A1 | 501呎 (2房)
 $1273万
 $25,416/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -62000,7 +62000,7 @@
           <t>A2 | 295呎 (1房)
 $738万
 $25,008/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -62008,7 +62008,7 @@
           <t>A3 | 299呎 (1房)
 $741万
 $24,784/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -62016,7 +62016,7 @@
           <t>A5 | 299呎 (1房)
 $741万
 $24,784/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -62024,7 +62024,7 @@
           <t>A6 | 297呎 (1房)
 $741万
 $24,945/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -62032,7 +62032,7 @@
           <t>A8 | 508呎 (2房)
 $1085万
 $21,360/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr"/>
@@ -62041,7 +62041,7 @@
           <t>B1 | 454呎 (2房)
 $958万
 $21,111/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -62049,7 +62049,7 @@
           <t>B2 | 299呎 (1房)
 $642万
 $21,478/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -62057,7 +62057,7 @@
           <t>B3 | 296呎 (1房)
 $637万
 $21,511/呎
-(24年-10月-21日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -62065,7 +62065,7 @@
           <t>B5 | 240呎 (开放式)
 $538万
 $22,421/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -62073,7 +62073,7 @@
           <t>B6 | 236呎 (开放式)
 $536万
 $22,691/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O25" s="22" t="inlineStr">
@@ -62081,7 +62081,7 @@
           <t>B8 | 460呎 (2房)
 $924万
 $20,081/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr"/>
@@ -62106,7 +62106,7 @@
           <t>A1 | 501呎 (2房)
 $1230万
 $24,547/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -62114,7 +62114,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,959/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -62122,7 +62122,7 @@
           <t>A3 | 299呎 (1房)
 $740万
 $24,734/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -62130,7 +62130,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,734/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -62138,7 +62138,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,861/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -62146,7 +62146,7 @@
           <t>A8 | 509呎 (2房)
 $1084万
 $21,295/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr"/>
@@ -62155,7 +62155,7 @@
           <t>B1 | 454呎 (2房)
 $957万
 $21,069/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -62163,7 +62163,7 @@
           <t>B2 | 299呎 (1房)
 $642万
 $21,468/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -62171,7 +62171,7 @@
           <t>B3 | 296呎 (1房)
 $634万
 $21,434/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -62179,7 +62179,7 @@
           <t>B5 | 240呎 (开放式)
 $556万
 $23,165/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -62187,7 +62187,7 @@
           <t>B6 | 236呎 (开放式)
 $534万
 $22,645/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O26" s="22" t="inlineStr">
@@ -62195,7 +62195,7 @@
           <t>B8 | 460呎 (2房)
 $887万
 $19,282/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P26" s="20" t="inlineStr"/>
@@ -62220,7 +62220,7 @@
           <t>A1 | 501呎 (2房)
 $1227万
 $24,498/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -62228,7 +62228,7 @@
           <t>A2 | 295呎 (1房)
 $735万
 $24,909/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -62236,7 +62236,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,685/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -62244,7 +62244,7 @@
           <t>A5 | 299呎 (1房)
 $738万
 $24,685/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -62252,7 +62252,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,845/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -62260,7 +62260,7 @@
           <t>A8 | 509呎 (2房)
 $1082万
 $21,253/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr"/>
@@ -62269,7 +62269,7 @@
           <t>B1 | 454呎 (2房)
 $955万
 $21,027/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -62277,7 +62277,7 @@
           <t>B2 | 299呎 (1房)
 $641万
 $21,425/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -62285,7 +62285,7 @@
           <t>B3 | 296呎 (1房)
 $633万
 $21,392/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -62293,7 +62293,7 @@
           <t>B5 | 240呎 (开放式)
 $537万
 $22,373/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -62301,7 +62301,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,600/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O27" s="22" t="inlineStr">
@@ -62309,7 +62309,7 @@
           <t>B8 | 460呎 (2房)
 $921万
 $20,023/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P27" s="20" t="inlineStr"/>
@@ -62334,7 +62334,7 @@
           <t>A1 | 501呎 (2房)
 $1225万
 $24,449/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -62342,7 +62342,7 @@
           <t>A2 | 295呎 (1房)
 $733万
 $24,859/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -62350,7 +62350,7 @@
           <t>A3 | 299呎 (1房)
 $737万
 $24,636/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -62358,7 +62358,7 @@
           <t>A5 | 299呎 (1房)
 $737万
 $24,636/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -62366,7 +62366,7 @@
           <t>A6 | 297呎 (1房)
 $708万
 $23,831/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -62374,7 +62374,7 @@
           <t>A8 | 509呎 (2房)
 $1080万
 $21,210/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr"/>
@@ -62383,7 +62383,7 @@
           <t>B1 | 454呎 (2房)
 $953万
 $20,985/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -62391,7 +62391,7 @@
           <t>B2 | 299呎 (1房)
 $639万
 $21,383/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -62399,7 +62399,7 @@
           <t>B3 | 296呎 (1房)
 $632万
 $21,349/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -62407,7 +62407,7 @@
           <t>B5 | 240呎 (开放式)
 $536万
 $22,328/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -62415,7 +62415,7 @@
           <t>B6 | 236呎 (开放式)
 $532万
 $22,555/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O28" s="22" t="inlineStr">
@@ -62423,7 +62423,7 @@
           <t>B8 | 460呎 (2房)
 $919万
 $19,983/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P28" s="20" t="inlineStr"/>
@@ -62448,7 +62448,7 @@
           <t>A1 | 501呎 (2房)
 $1222万
 $24,400/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -62456,7 +62456,7 @@
           <t>A2 | 295呎 (1房)
 $732万
 $24,809/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -62464,7 +62464,7 @@
           <t>A3 | 298呎 (1房)
 $735万
 $24,669/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -62472,7 +62472,7 @@
           <t>A5 | 299呎 (1房)
 $735万
 $24,586/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -62480,7 +62480,7 @@
           <t>A6 | 297呎 (1房)
 $735万
 $24,746/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -62488,7 +62488,7 @@
           <t>A8 | 509呎 (2房)
 $1077万
 $21,168/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr"/>
@@ -62497,7 +62497,7 @@
           <t>B1 | 454呎 (2房)
 $951万
 $20,943/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -62505,7 +62505,7 @@
           <t>B2 | 299呎 (1房)
 $659万
 $22,051/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -62513,7 +62513,7 @@
           <t>B3 | 296呎 (1房)
 $632万
 $21,340/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -62521,7 +62521,7 @@
           <t>B5 | 240呎 (开放式)
 $535万
 $22,283/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N29" s="22" t="inlineStr">
@@ -62529,7 +62529,7 @@
           <t>B6 | 236呎 (开放式)
 $531万
 $22,510/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O29" s="22" t="inlineStr">
@@ -62537,7 +62537,7 @@
           <t>B8 | 460呎 (2房)
 $917万
 $19,943/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P29" s="20" t="inlineStr"/>
@@ -62562,7 +62562,7 @@
           <t>A1 | 501呎 (2房)
 $1220万
 $24,351/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -62570,7 +62570,7 @@
           <t>A2 | 295呎 (1房)
 $730万
 $24,760/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -62578,7 +62578,7 @@
           <t>A3 | 299呎 (1房)
 $734万
 $24,537/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -62586,7 +62586,7 @@
           <t>A5 | 299呎 (1房)
 $734万
 $24,537/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -62594,7 +62594,7 @@
           <t>A6 | 297呎 (1房)
 $733万
 $24,696/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -62602,7 +62602,7 @@
           <t>A8 | 509呎 (2房)
 $1075万
 $21,126/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr"/>
@@ -62611,7 +62611,7 @@
           <t>B1 | 454呎 (2房)
 $949万
 $20,902/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -62619,7 +62619,7 @@
           <t>B2 | 299呎 (1房)
 $637万
 $21,297/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -62627,7 +62627,7 @@
           <t>B3 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -62635,7 +62635,7 @@
           <t>B5 | 240呎 (开放式)
 $534万
 $22,239/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
@@ -62643,7 +62643,7 @@
           <t>B6 | 236呎 (开放式)
 $530万
 $22,465/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O30" s="22" t="inlineStr">
@@ -62651,7 +62651,7 @@
           <t>B8 | 460呎 (2房)
 $916万
 $19,903/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P30" s="20" t="inlineStr"/>
@@ -62676,7 +62676,7 @@
           <t>A1 | 501呎 (2房)
 $1141万
 $22,779/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -62684,7 +62684,7 @@
           <t>A2 | 295呎 (1房)
 $728万
 $24,685/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -62692,7 +62692,7 @@
           <t>A3 | 299呎 (1房)
 $731万
 $24,464/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -62700,7 +62700,7 @@
           <t>A5 | 299呎 (1房)
 $731万
 $24,464/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -62708,7 +62708,7 @@
           <t>A6 | 297呎 (1房)
 $731万
 $24,622/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -62716,7 +62716,7 @@
           <t>A8 | 509呎 (2房)
 $1072万
 $21,062/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr"/>
@@ -62725,7 +62725,7 @@
           <t>B1 | 454呎 (2房)
 $946万
 $20,839/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -62733,7 +62733,7 @@
           <t>B2 | 299呎 (1房)
 $635万
 $21,233/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -62741,7 +62741,7 @@
           <t>B3 | 296呎 (1房)
 $628万
 $21,233/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -62749,7 +62749,7 @@
           <t>B5 | 240呎 (开放式)
 $532万
 $22,172/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N31" s="22" t="inlineStr">
@@ -62757,7 +62757,7 @@
           <t>B6 | 236呎 (开放式)
 $529万
 $22,397/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O31" s="22" t="inlineStr">
@@ -62765,7 +62765,7 @@
           <t>B8 | 460呎 (2房)
 $913万
 $19,843/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P31" s="20" t="inlineStr"/>
@@ -62790,7 +62790,7 @@
           <t>A1 | 501呎 (2房)
 $1138万
 $22,711/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -62798,7 +62798,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,963/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -62806,7 +62806,7 @@
           <t>A3 | 299呎 (1房)
 $739万
 $24,705/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -62814,7 +62814,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,739/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -62822,7 +62822,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,899/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -62830,7 +62830,7 @@
           <t>A8 | 509呎 (2房)
 $1069万
 $20,999/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr"/>
@@ -62839,7 +62839,7 @@
           <t>B1 | 454呎 (2房)
 $943万
 $20,776/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -62847,7 +62847,7 @@
           <t>B2 | 299呎 (1房)
 $633万
 $21,170/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -62855,7 +62855,7 @@
           <t>B3 | 296呎 (1房)
 $627万
 $21,170/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -62863,7 +62863,7 @@
           <t>B5 | 240呎 (开放式)
 $531万
 $22,106/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
@@ -62871,7 +62871,7 @@
           <t>B6 | 236呎 (开放式)
 $527万
 $22,330/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O32" s="22" t="inlineStr">
@@ -62879,7 +62879,7 @@
           <t>B8 | 460呎 (2房)
 $910万
 $19,783/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P32" s="20" t="inlineStr"/>
@@ -62904,7 +62904,7 @@
           <t>A1 | 501呎 (2房)
 $1134万
 $22,643/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -62912,7 +62912,7 @@
           <t>A2 | 295呎 (1房)
 $724万
 $24,538/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -62920,7 +62920,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,317/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -62936,7 +62936,7 @@
           <t>A6 | 297呎 (1房)
 $727万
 $24,475/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -62944,7 +62944,7 @@
           <t>A8 | 509呎 (2房)
 $1066万
 $20,936/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr"/>
@@ -62953,7 +62953,7 @@
           <t>B1 | 454呎 (2房)
 $940万
 $20,714/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -62961,7 +62961,7 @@
           <t>B2 | 299呎 (1房)
 $631万
 $21,106/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -62969,7 +62969,7 @@
           <t>B3 | 296呎 (1房)
 $625万
 $21,106/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -62977,7 +62977,7 @@
           <t>B5 | 240呎 (开放式)
 $529万
 $22,039/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N33" s="22" t="inlineStr">
@@ -62985,7 +62985,7 @@
           <t>B6 | 236呎 (开放式)
 $525万
 $22,263/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O33" s="22" t="inlineStr">
@@ -62993,7 +62993,7 @@
           <t>B8 | 460呎 (2房)
 $907万
 $19,724/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr"/>
@@ -63018,7 +63018,7 @@
           <t>A1 | 501呎 (2房)
 $1127万
 $22,490/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -63026,7 +63026,7 @@
           <t>A2 | 295呎 (1房)
 $685万
 $23,214/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -63034,7 +63034,7 @@
           <t>A3 | 299呎 (1房)
 $688万
 $23,006/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -63042,7 +63042,7 @@
           <t>A5 | 299呎 (1房)
 $688万
 $23,006/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -63050,7 +63050,7 @@
           <t>A6 | 297呎 (1房)
 $688万
 $23,155/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
@@ -63058,7 +63058,7 @@
           <t>A8 | 509呎 (2房)
 $1058万
 $20,795/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr"/>
@@ -63067,7 +63067,7 @@
           <t>B1 | 454呎 (2房)
 $933万
 $20,556/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -63075,7 +63075,7 @@
           <t>B2 | 299呎 (1房)
 $602万
 $20,134/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -63083,7 +63083,7 @@
           <t>B3 | 296呎 (1房)
 $620万
 $20,949/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -63091,7 +63091,7 @@
           <t>B5 | 240呎 (开放式)
 $525万
 $21,881/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N34" s="22" t="inlineStr">
@@ -63099,7 +63099,7 @@
           <t>B6 | 236呎 (开放式)
 $522万
 $22,104/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O34" s="22" t="inlineStr">
@@ -63107,7 +63107,7 @@
           <t>B8 | 460呎 (2房)
 $900万
 $19,574/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P34" s="20" t="inlineStr"/>
@@ -63132,7 +63132,7 @@
           <t>A1 | 501呎 (2房)
 $1118万
 $22,321/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -63140,7 +63140,7 @@
           <t>A2 | 295呎 (1房)
 $680万
 $23,043/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -63148,7 +63148,7 @@
           <t>A3 | 299呎 (1房)
 $683万
 $22,837/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -63156,7 +63156,7 @@
           <t>A5 | 299呎 (1房)
 $683万
 $22,837/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -63164,7 +63164,7 @@
           <t>A6 | 297呎 (1房)
 $683万
 $22,985/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -63172,7 +63172,7 @@
           <t>A8 | 509呎 (2房)
 $1050万
 $20,639/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr"/>
@@ -63181,7 +63181,7 @@
           <t>B1 | 454呎 (2房)
 $925万
 $20,366/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -63189,7 +63189,7 @@
           <t>B2 | 299呎 (1房)
 $621万
 $20,760/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -63197,7 +63197,7 @@
           <t>B3 | 296呎 (1房)
 $614万
 $20,759/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -63205,7 +63205,7 @@
           <t>B5 | 240呎 (开放式)
 $521万
 $21,696/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N35" s="22" t="inlineStr">
@@ -63213,7 +63213,7 @@
           <t>B6 | 236呎 (开放式)
 $517万
 $21,920/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O35" s="22" t="inlineStr">
@@ -63221,7 +63221,7 @@
           <t>B8 | 460呎 (2房)
 $857万
 $18,638/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P35" s="20" t="inlineStr"/>
@@ -63246,7 +63246,7 @@
           <t>A1 | 501呎 (2房)
 $1074万
 $21,428/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -63254,7 +63254,7 @@
           <t>A2 | 295呎 (1房)
 $653万
 $22,122/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -63262,7 +63262,7 @@
           <t>A3 | 299呎 (1房)
 $656万
 $21,923/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -63270,7 +63270,7 @@
           <t>A5 | 299呎 (1房)
 $656万
 $21,923/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -63278,7 +63278,7 @@
           <t>A6 | 297呎 (1房)
 $655万
 $22,065/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -63286,7 +63286,7 @@
           <t>A8 | 509呎 (2房)
 $1008万
 $19,813/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr"/>
@@ -63295,7 +63295,7 @@
           <t>B1 | 454呎 (2房)
 $912万
 $20,080/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -63303,7 +63303,7 @@
           <t>B2 | 299呎 (1房)
 $613万
 $20,489/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -63311,7 +63311,7 @@
           <t>B3 | 296呎 (1房)
 $606万
 $20,476/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -63319,7 +63319,7 @@
           <t>B5 | 240呎 (开放式)
 $514万
 $21,408/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N36" s="22" t="inlineStr">
@@ -63327,7 +63327,7 @@
           <t>B6 | 236呎 (开放式)
 $511万
 $21,643/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O36" s="22" t="inlineStr">
@@ -63335,7 +63335,7 @@
           <t>B8 | 460呎 (2房)
 $910万
 $19,792/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P36" s="20" t="inlineStr"/>
@@ -63360,7 +63360,7 @@
           <t>A1 | 501呎 (2房)
 $919万
 $18,336/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -63368,7 +63368,7 @@
           <t>A2 | 295呎 (1房)
 $574万
 $19,467/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -63376,7 +63376,7 @@
           <t>A3 | 299呎 (1房)
 $577万
 $19,292/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -63384,7 +63384,7 @@
           <t>A5 | 298呎 (1房)
 $577万
 $19,357/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -63392,7 +63392,7 @@
           <t>A6 | 297呎 (1房)
 $577万
 $19,418/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -63400,7 +63400,7 @@
           <t>A8 | 509呎 (2房)
 $901万
 $17,703/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr"/>
@@ -63409,7 +63409,7 @@
           <t>B1 | 454呎 (2房)
 $880万
 $19,377/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -63417,7 +63417,7 @@
           <t>B2 | 299呎 (1房)
 $591万
 $19,772/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -63425,7 +63425,7 @@
           <t>B3 | 296呎 (1房)
 $585万
 $19,759/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -63433,7 +63433,7 @@
           <t>B5 | 240呎 (开放式)
 $496万
 $20,658/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N37" s="22" t="inlineStr">
@@ -63441,7 +63441,7 @@
           <t>B6 | 236呎 (开放式)
 $493万
 $20,885/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O37" s="22" t="inlineStr">
@@ -63449,7 +63449,7 @@
           <t>B8 | 460呎 (2房)
 $850万
 $18,483/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="P37" s="20" t="inlineStr"/>
@@ -63783,7 +63783,7 @@
           <t>SSV B | 1622呎 (4+房)
 $5915万
 $36,465/呎
-(25年-01月-06日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -63798,7 +63798,7 @@
           <t>A | 909呎 (4+房)
 $3219万
 $35,417/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -63811,7 +63811,7 @@
           <t>B | 672呎 (3房)
 $2000万
 $29,764/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr"/>
@@ -63825,7 +63825,7 @@
           <t>C | 907呎 (4+房)
 $2928万
 $32,283/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P7" s="22" t="inlineStr">
@@ -63833,7 +63833,7 @@
           <t>D | 445呎 (2房)
 $1008万
 $22,661/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -63841,7 +63841,7 @@
           <t>E | 469呎 (2房)
 $1018万
 $21,709/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R7" s="22" t="inlineStr">
@@ -63849,7 +63849,7 @@
           <t>F | 460呎 (2房)
 $1005万
 $21,851/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S7" s="22" t="inlineStr">
@@ -63857,7 +63857,7 @@
           <t>G | 454呎 (2房)
 $962万
 $21,199/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T7" s="22" t="inlineStr">
@@ -63865,7 +63865,7 @@
           <t>H | 692呎 (2房)
 $1554万
 $22,449/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U7" s="20" t="inlineStr"/>
@@ -63884,7 +63884,7 @@
           <t>A | 909呎 (4+房)
 $3126万
 $34,391/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -63897,7 +63897,7 @@
           <t>B | 672呎 (3房)
 $1994万
 $29,675/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr"/>
@@ -63911,7 +63911,7 @@
           <t>C | 907呎 (4+房)
 $2777万
 $30,620/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P8" s="22" t="inlineStr">
@@ -63919,7 +63919,7 @@
           <t>D | 445呎 (2房)
 $1005万
 $22,593/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -63927,7 +63927,7 @@
           <t>E | 469呎 (2房)
 $1015万
 $21,644/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R8" s="22" t="inlineStr">
@@ -63935,7 +63935,7 @@
           <t>F | 460呎 (2房)
 $1002万
 $21,785/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S8" s="22" t="inlineStr">
@@ -63943,7 +63943,7 @@
           <t>G | 454呎 (2房)
 $960万
 $21,136/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T8" s="22" t="inlineStr">
@@ -63951,7 +63951,7 @@
           <t>H | 692呎 (2房)
 $1549万
 $22,382/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr"/>
@@ -63970,7 +63970,7 @@
           <t>A | 909呎 (4+房)
 $3114万
 $34,255/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -63983,7 +63983,7 @@
           <t>B | 672呎 (3房)
 $1984万
 $29,528/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr"/>
@@ -63997,7 +63997,7 @@
           <t>C | 907呎 (4+房)
 $2780万
 $30,650/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P9" s="22" t="inlineStr">
@@ -64005,7 +64005,7 @@
           <t>D | 445呎 (2房)
 $995万
 $22,369/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q9" s="22" t="inlineStr">
@@ -64013,7 +64013,7 @@
           <t>E | 469呎 (2房)
 $1012万
 $21,579/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R9" s="22" t="inlineStr">
@@ -64021,7 +64021,7 @@
           <t>F | 460呎 (2房)
 $999万
 $21,720/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S9" s="22" t="inlineStr">
@@ -64029,7 +64029,7 @@
           <t>G | 454呎 (2房)
 $995万
 $21,925/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T9" s="22" t="inlineStr">
@@ -64037,7 +64037,7 @@
           <t>H | 692呎 (2房)
 $1541万
 $22,271/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U9" s="20" t="inlineStr"/>
@@ -64056,7 +64056,7 @@
           <t>A | 909呎 (4+房)
 $3032万
 $33,361/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -64069,7 +64069,7 @@
           <t>B | 672呎 (3房)
 $1974万
 $29,380/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr"/>
@@ -64083,7 +64083,7 @@
           <t>C | 907呎 (4+房)
 $2759万
 $30,419/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P10" s="22" t="inlineStr">
@@ -64091,7 +64091,7 @@
           <t>D | 445呎 (2房)
 $990万
 $22,258/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -64099,7 +64099,7 @@
           <t>E | 469呎 (2房)
 $1010万
 $21,525/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R10" s="22" t="inlineStr">
@@ -64107,7 +64107,7 @@
           <t>F | 460呎 (2房)
 $997万
 $21,666/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S10" s="22" t="inlineStr">
@@ -64115,7 +64115,7 @@
           <t>G | 454呎 (2房)
 $993万
 $21,870/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T10" s="22" t="inlineStr">
@@ -64123,7 +64123,7 @@
           <t>H | 692呎 (2房)
 $1533万
 $22,160/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U10" s="20" t="inlineStr"/>
@@ -64142,7 +64142,7 @@
           <t>A | 909呎 (4+房)
 $3091万
 $34,000/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -64155,7 +64155,7 @@
           <t>B | 672呎 (3房)
 $1964万
 $29,233/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr"/>
@@ -64169,7 +64169,7 @@
           <t>C | 907呎 (4+房)
 $2872万
 $31,667/呎
-(24年-12月-01日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="P11" s="22" t="inlineStr">
@@ -64177,7 +64177,7 @@
           <t>D | 445呎 (2房)
 $981万
 $22,037/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -64185,7 +64185,7 @@
           <t>E | 469呎 (2房)
 $994万
 $21,191/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R11" s="22" t="inlineStr">
@@ -64193,7 +64193,7 @@
           <t>F | 460呎 (2房)
 $1013万
 $22,020/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S11" s="22" t="inlineStr">
@@ -64201,7 +64201,7 @@
           <t>G | 454呎 (2房)
 $1009万
 $22,224/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T11" s="22" t="inlineStr">
@@ -64209,7 +64209,7 @@
           <t>H | 692呎 (2房)
 $1526万
 $22,049/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U11" s="20" t="inlineStr"/>
@@ -64228,7 +64228,7 @@
           <t>A | 909呎 (4+房)
 $2909万
 $32,000/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -64241,7 +64241,7 @@
           <t>B | 672呎 (3房)
 $1955万
 $29,087/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr"/>
@@ -64255,7 +64255,7 @@
           <t>C | 907呎 (4+房)
 $2739万
 $30,200/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="P12" s="22" t="inlineStr">
@@ -64263,7 +64263,7 @@
           <t>D | 445呎 (2房)
 $976万
 $21,927/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -64271,7 +64271,7 @@
           <t>E | 469呎 (2房)
 $1031万
 $21,993/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R12" s="22" t="inlineStr">
@@ -64279,7 +64279,7 @@
           <t>F | 460呎 (2房)
 $1010万
 $21,965/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S12" s="22" t="inlineStr">
@@ -64287,7 +64287,7 @@
           <t>G | 454呎 (2房)
 $1006万
 $22,168/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T12" s="22" t="inlineStr">
@@ -64295,7 +64295,7 @@
           <t>H | 692呎 (2房)
 $1518万
 $21,938/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U12" s="20" t="inlineStr"/>
@@ -64314,7 +64314,7 @@
           <t>A | 909呎 (4+房)
 $3050万
 $33,552/呎
-(24年-12月-08日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -64327,7 +64327,7 @@
           <t>B | 672呎 (3房)
 $1945万
 $28,942/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr"/>
@@ -64341,7 +64341,7 @@
           <t>C | 907呎 (4+房)
 $2892万
 $31,886/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="P13" s="22" t="inlineStr">
@@ -64349,7 +64349,7 @@
           <t>D | 445呎 (2房)
 $971万
 $21,817/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -64357,7 +64357,7 @@
           <t>E | 469呎 (2房)
 $1063万
 $22,670/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R13" s="22" t="inlineStr">
@@ -64365,7 +64365,7 @@
           <t>F | 460呎 (2房)
 $1008万
 $21,910/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S13" s="22" t="inlineStr">
@@ -64373,7 +64373,7 @@
           <t>G | 454呎 (2房)
 $1004万
 $22,113/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T13" s="22" t="inlineStr">
@@ -64381,7 +64381,7 @@
           <t>H | 692呎 (2房)
 $1511万
 $21,829/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U13" s="20" t="inlineStr"/>
@@ -64413,7 +64413,7 @@
           <t>B | 672呎 (3房)
 $1935万
 $28,797/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr"/>
@@ -64427,7 +64427,7 @@
           <t>C | 907呎 (4+房)
 $2902万
 $31,990/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="P14" s="22" t="inlineStr">
@@ -64435,7 +64435,7 @@
           <t>D | 445呎 (2房)
 $1100万
 $24,719/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="Q14" s="22" t="inlineStr">
@@ -64443,7 +64443,7 @@
           <t>E | 469呎 (2房)
 $1030万
 $21,966/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="R14" s="22" t="inlineStr">
@@ -64451,7 +64451,7 @@
           <t>F | 460呎 (2房)
 $1280万
 $27,826/呎
-(24年-11月-26日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="S14" s="22" t="inlineStr">
@@ -64459,7 +64459,7 @@
           <t>G | 454呎 (2房)
 $1147万
 $25,258/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="T14" s="22" t="inlineStr">
@@ -64467,7 +64467,7 @@
           <t>H | 692呎 (2房)
 $1735万
 $25,068/呎
-(24年-11月-28日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="U14" s="20" t="inlineStr"/>
@@ -64487,7 +64487,7 @@
           <t>A1 | 497呎 (2房)
 $1330万
 $26,763/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -64495,7 +64495,7 @@
           <t>A2 | 298呎 (1房)
 $753万
 $25,266/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -64503,7 +64503,7 @@
           <t>A3 | 299呎 (1房)
 $773万
 $25,866/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -64511,7 +64511,7 @@
           <t>A5 | 300呎 (1房)
 $790万
 $26,332/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -64519,7 +64519,7 @@
           <t>A6 | 469呎 (2房)
 $1307万
 $27,868/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -64528,7 +64528,7 @@
           <t>B1 | 467呎 (2房)
 $964万
 $20,633/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -64536,7 +64536,7 @@
           <t>B2 | 296呎 (1房)
 $688万
 $23,227/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -64544,7 +64544,7 @@
           <t>B3 | 296呎 (1房)
 $687万
 $23,193/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -64552,7 +64552,7 @@
           <t>B5 | 240呎 (开放式)
 $573万
 $23,863/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -64560,7 +64560,7 @@
           <t>B6 | 236呎 (开放式)
 $566万
 $23,997/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -64568,7 +64568,7 @@
           <t>B8 | 477呎 (2房)
 $1014万
 $21,262/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr"/>
@@ -64594,7 +64594,7 @@
           <t>A1 | 497呎 (2房)
 $1309万
 $26,347/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -64602,7 +64602,7 @@
           <t>A2 | 298呎 (1房)
 $746万
 $25,018/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -64610,7 +64610,7 @@
           <t>A3 | 299呎 (1房)
 $766万
 $25,610/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -64618,7 +64618,7 @@
           <t>A5 | 300呎 (1房)
 $782万
 $26,071/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -64626,7 +64626,7 @@
           <t>A6 | 469呎 (2房)
 $1288万
 $27,457/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -64635,7 +64635,7 @@
           <t>B1 | 467呎 (2房)
 $958万
 $20,510/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -64643,7 +64643,7 @@
           <t>B2 | 296呎 (1房)
 $685万
 $23,135/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -64651,7 +64651,7 @@
           <t>B3 | 296呎 (1房)
 $684万
 $23,101/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -64659,7 +64659,7 @@
           <t>B5 | 240呎 (开放式)
 $568万
 $23,678/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -64667,7 +64667,7 @@
           <t>B6 | 236呎 (开放式)
 $562万
 $23,808/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -64675,7 +64675,7 @@
           <t>B8 | 477呎 (2房)
 $1008万
 $21,136/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr"/>
@@ -64701,7 +64701,7 @@
           <t>A1 | 497呎 (2房)
 $1297万
 $26,093/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -64709,7 +64709,7 @@
           <t>A2 | 298呎 (1房)
 $744万
 $24,966/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -64717,7 +64717,7 @@
           <t>A3 | 299呎 (1房)
 $753万
 $25,187/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -64725,7 +64725,7 @@
           <t>A5 | 300呎 (1房)
 $769万
 $25,641/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -64733,7 +64733,7 @@
           <t>A6 | 469呎 (2房)
 $1275万
 $27,184/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -64742,7 +64742,7 @@
           <t>B1 | 467呎 (2房)
 $954万
 $20,428/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -64750,7 +64750,7 @@
           <t>B2 | 296呎 (1房)
 $683万
 $23,089/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -64758,7 +64758,7 @@
           <t>B3 | 296呎 (1房)
 $683万
 $23,089/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -64766,7 +64766,7 @@
           <t>B5 | 240呎 (开放式)
 $565万
 $23,539/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -64774,7 +64774,7 @@
           <t>B6 | 236呎 (开放式)
 $559万
 $23,669/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -64782,7 +64782,7 @@
           <t>B8 | 477呎 (2房)
 $1004万
 $21,052/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr"/>
@@ -64808,7 +64808,7 @@
           <t>A1 | 497呎 (2房)
 $1286万
 $25,883/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -64816,7 +64816,7 @@
           <t>A2 | 298呎 (1房)
 $743万
 $24,932/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -64824,7 +64824,7 @@
           <t>A3 | 299呎 (1房)
 $749万
 $25,036/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -64832,7 +64832,7 @@
           <t>A5 | 300呎 (1房)
 $765万
 $25,488/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -64840,7 +64840,7 @@
           <t>A6 | 469呎 (2房)
 $1323万
 $28,210/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -64849,7 +64849,7 @@
           <t>B1 | 467呎 (2房)
 $950万
 $20,347/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -64857,7 +64857,7 @@
           <t>B2 | 296呎 (1房)
 $682万
 $23,043/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -64865,7 +64865,7 @@
           <t>B3 | 296呎 (1房)
 $682万
 $23,043/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -64873,7 +64873,7 @@
           <t>B5 | 240呎 (开放式)
 $562万
 $23,400/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -64881,7 +64881,7 @@
           <t>B6 | 236呎 (开放式)
 $555万
 $23,530/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -64889,7 +64889,7 @@
           <t>B8 | 477呎 (2房)
 $1000万
 $20,968/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr"/>
@@ -64915,7 +64915,7 @@
           <t>A1 | 497呎 (2房)
 $1277万
 $25,688/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -64923,7 +64923,7 @@
           <t>A2 | 298呎 (1房)
 $767万
 $25,738/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -64931,7 +64931,7 @@
           <t>A3 | 299呎 (1房)
 $743万
 $24,849/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -64939,7 +64939,7 @@
           <t>A5 | 300呎 (1房)
 $759万
 $25,297/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -64947,7 +64947,7 @@
           <t>A6 | 469呎 (2房)
 $1313万
 $27,997/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -64956,7 +64956,7 @@
           <t>B1 | 467呎 (2房)
 $946万
 $20,266/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -64964,7 +64964,7 @@
           <t>B2 | 296呎 (1房)
 $681万
 $22,996/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -64972,7 +64972,7 @@
           <t>B3 | 296呎 (1房)
 $681万
 $22,996/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -64980,7 +64980,7 @@
           <t>B5 | 240呎 (开放式)
 $551万
 $22,974/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -64988,7 +64988,7 @@
           <t>B6 | 236呎 (开放式)
 $548万
 $23,208/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -64996,7 +64996,7 @@
           <t>B8 | 477呎 (2房)
 $996万
 $20,884/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr"/>
@@ -65022,7 +65022,7 @@
           <t>A1 | 497呎 (2房)
 $1319万
 $26,535/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -65030,7 +65030,7 @@
           <t>A2 | 298呎 (1房)
 $766万
 $25,699/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -65038,7 +65038,7 @@
           <t>A3 | 299呎 (1房)
 $740万
 $24,751/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -65046,7 +65046,7 @@
           <t>A5 | 300呎 (1房)
 $756万
 $25,197/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -65054,7 +65054,7 @@
           <t>A6 | 469呎 (2房)
 $1308万
 $27,886/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -65063,7 +65063,7 @@
           <t>B1 | 467呎 (2房)
 $943万
 $20,185/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -65071,7 +65071,7 @@
           <t>B2 | 296呎 (1房)
 $678万
 $22,905/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -65079,7 +65079,7 @@
           <t>B3 | 296呎 (1房)
 $678万
 $22,905/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -65087,7 +65087,7 @@
           <t>B5 | 240呎 (开放式)
 $549万
 $22,883/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -65095,7 +65095,7 @@
           <t>B6 | 236呎 (开放式)
 $546万
 $23,116/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -65103,7 +65103,7 @@
           <t>B8 | 477呎 (2房)
 $954万
 $19,992/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr"/>
@@ -65129,7 +65129,7 @@
           <t>A1 | 497呎 (2房)
 $1315万
 $26,456/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -65137,7 +65137,7 @@
           <t>A2 | 298呎 (1房)
 $761万
 $25,535/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -65145,7 +65145,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,676/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -65153,7 +65153,7 @@
           <t>A5 | 300呎 (1房)
 $754万
 $25,121/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -65161,7 +65161,7 @@
           <t>A6 | 469呎 (2房)
 $1280万
 $27,297/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
@@ -65170,7 +65170,7 @@
           <t>B1 | 467呎 (2房)
 $940万
 $20,124/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -65178,7 +65178,7 @@
           <t>B2 | 296呎 (1房)
 $676万
 $22,836/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -65186,7 +65186,7 @@
           <t>B3 | 296呎 (1房)
 $676万
 $22,836/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -65194,7 +65194,7 @@
           <t>B5 | 240呎 (开放式)
 $548万
 $22,815/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -65202,7 +65202,7 @@
           <t>B6 | 236呎 (开放式)
 $544万
 $23,047/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -65210,7 +65210,7 @@
           <t>B8 | 477呎 (2房)
 $989万
 $20,739/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr"/>
@@ -65236,7 +65236,7 @@
           <t>A1 | 497呎 (2房)
 $1311万
 $26,376/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -65244,7 +65244,7 @@
           <t>A2 | 298呎 (1房)
 $759万
 $25,459/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -65252,7 +65252,7 @@
           <t>A3 | 299呎 (1房)
 $707万
 $23,646/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -65260,7 +65260,7 @@
           <t>A5 | 300呎 (1房)
 $751万
 $25,046/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -65268,7 +65268,7 @@
           <t>A6 | 469呎 (2房)
 $1253万
 $26,711/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
@@ -65277,7 +65277,7 @@
           <t>B1 | 467呎 (2房)
 $937万
 $20,064/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -65285,7 +65285,7 @@
           <t>B2 | 296呎 (1房)
 $673万
 $22,734/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -65293,7 +65293,7 @@
           <t>B3 | 296呎 (1房)
 $674万
 $22,768/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -65301,7 +65301,7 @@
           <t>B5 | 240呎 (开放式)
 $546万
 $22,747/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -65309,7 +65309,7 @@
           <t>B6 | 236呎 (开放式)
 $542万
 $22,978/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -65317,7 +65317,7 @@
           <t>B8 | 477呎 (2房)
 $986万
 $20,677/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr"/>
@@ -65343,7 +65343,7 @@
           <t>A1 | 497呎 (2房)
 $1307万
 $26,297/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -65351,7 +65351,7 @@
           <t>A2 | 298呎 (1房)
 $755万
 $25,349/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -65359,7 +65359,7 @@
           <t>A3 | 299呎 (1房)
 $733万
 $24,529/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -65367,7 +65367,7 @@
           <t>A5 | 300呎 (1房)
 $749万
 $24,971/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -65375,7 +65375,7 @@
           <t>A6 | 469呎 (2房)
 $1132万
 $24,147/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
@@ -65384,7 +65384,7 @@
           <t>B1 | 467呎 (2房)
 $934万
 $20,004/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -65392,7 +65392,7 @@
           <t>B2 | 296呎 (1房)
 $671万
 $22,666/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -65400,7 +65400,7 @@
           <t>B3 | 296呎 (1房)
 $672万
 $22,700/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -65408,7 +65408,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,638/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -65416,7 +65416,7 @@
           <t>B6 | 236呎 (开放式)
 $520万
 $22,019/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -65424,7 +65424,7 @@
           <t>B8 | 477呎 (2房)
 $983万
 $20,615/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr"/>
@@ -65450,7 +65450,7 @@
           <t>A1 | 497呎 (2房)
 $1303万
 $26,219/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -65458,7 +65458,7 @@
           <t>A2 | 298呎 (1房)
 $754万
 $25,306/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -65466,7 +65466,7 @@
           <t>A3 | 298呎 (1房)
 $731万
 $24,538/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -65474,7 +65474,7 @@
           <t>A5 | 300呎 (1房)
 $747万
 $24,896/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -65482,7 +65482,7 @@
           <t>A6 | 469呎 (2房)
 $1175万
 $25,049/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
@@ -65491,7 +65491,7 @@
           <t>B1 | 467呎 (2房)
 $931万
 $19,945/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -65499,7 +65499,7 @@
           <t>B2 | 296呎 (1房)
 $670万
 $22,632/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -65507,7 +65507,7 @@
           <t>B3 | 296呎 (1房)
 $670万
 $22,632/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -65515,7 +65515,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,612/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -65523,7 +65523,7 @@
           <t>B6 | 236呎 (开放式)
 $539万
 $22,842/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -65531,7 +65531,7 @@
           <t>B8 | 477呎 (2房)
 $942万
 $19,754/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr"/>
@@ -65557,7 +65557,7 @@
           <t>A1 | 497呎 (2房)
 $1300万
 $26,167/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -65565,7 +65565,7 @@
           <t>A2 | 298呎 (1房)
 $753万
 $25,256/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -65573,7 +65573,7 @@
           <t>A3 | 299呎 (1房)
 $729万
 $24,374/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -65581,7 +65581,7 @@
           <t>A5 | 300呎 (1房)
 $744万
 $24,813/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -65589,7 +65589,7 @@
           <t>A6 | 469呎 (2房)
 $1172万
 $24,999/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
@@ -65598,7 +65598,7 @@
           <t>B1 | 467呎 (2房)
 $930万
 $19,904/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -65606,7 +65606,7 @@
           <t>B2 | 296呎 (1房)
 $669万
 $22,587/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -65614,7 +65614,7 @@
           <t>B3 | 296呎 (1房)
 $669万
 $22,587/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -65622,7 +65622,7 @@
           <t>B5 | 240呎 (开放式)
 $542万
 $22,567/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -65630,7 +65630,7 @@
           <t>B6 | 236呎 (开放式)
 $556万
 $23,556/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -65638,7 +65638,7 @@
           <t>B8 | 477呎 (2房)
 $978万
 $20,512/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr"/>
@@ -65664,7 +65664,7 @@
           <t>A1 | 497呎 (2房)
 $1298万
 $26,114/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -65672,7 +65672,7 @@
           <t>A2 | 298呎 (1房)
 $722万
 $24,226/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -65680,7 +65680,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,325/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -65688,7 +65688,7 @@
           <t>A5 | 300呎 (1房)
 $743万
 $24,764/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -65696,7 +65696,7 @@
           <t>A6 | 469呎 (2房)
 $1170万
 $24,949/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
@@ -65705,7 +65705,7 @@
           <t>B1 | 467呎 (2房)
 $928万
 $19,865/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -65713,7 +65713,7 @@
           <t>B2 | 296呎 (1房)
 $666万
 $22,508/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -65721,7 +65721,7 @@
           <t>B3 | 296呎 (1房)
 $667万
 $22,542/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -65729,7 +65729,7 @@
           <t>B5 | 240呎 (开放式)
 $541万
 $22,522/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -65737,7 +65737,7 @@
           <t>B6 | 237呎 (开放式)
 $537万
 $22,655/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -65745,7 +65745,7 @@
           <t>B8 | 477呎 (2房)
 $976万
 $20,471/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O26" s="20" t="inlineStr"/>
@@ -65771,7 +65771,7 @@
           <t>A1 | 497呎 (2房)
 $1245万
 $25,049/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -65779,7 +65779,7 @@
           <t>A2 | 298呎 (1房)
 $775万
 $25,994/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -65787,7 +65787,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,309/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -65795,7 +65795,7 @@
           <t>A5 | 300呎 (1房)
 $742万
 $24,747/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -65803,7 +65803,7 @@
           <t>A6 | 469呎 (2房)
 $1168万
 $24,899/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
@@ -65812,7 +65812,7 @@
           <t>B1 | 467呎 (2房)
 $926万
 $19,825/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -65820,7 +65820,7 @@
           <t>B2 | 296呎 (1房)
 $688万
 $23,247/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -65828,7 +65828,7 @@
           <t>B3 | 296呎 (1房)
 $666万
 $22,497/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -65836,7 +65836,7 @@
           <t>B5 | 240呎 (开放式)
 $539万
 $22,478/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -65844,7 +65844,7 @@
           <t>B6 | 236呎 (开放式)
 $554万
 $23,463/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -65852,7 +65852,7 @@
           <t>B8 | 477呎 (2房)
 $975万
 $20,430/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O27" s="20" t="inlineStr"/>
@@ -65878,7 +65878,7 @@
           <t>A1 | 497呎 (2房)
 $1242万
 $24,999/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -65886,7 +65886,7 @@
           <t>A2 | 298呎 (1房)
 $748万
 $25,105/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -65894,7 +65894,7 @@
           <t>A3 | 299呎 (1房)
 $725万
 $24,261/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -65902,7 +65902,7 @@
           <t>A5 | 300呎 (1房)
 $740万
 $24,665/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -65910,7 +65910,7 @@
           <t>A6 | 469呎 (2房)
 $1165万
 $24,849/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
@@ -65919,7 +65919,7 @@
           <t>B1 | 467呎 (2房)
 $924万
 $19,785/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -65927,7 +65927,7 @@
           <t>B2 | 296呎 (1房)
 $665万
 $22,452/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -65935,7 +65935,7 @@
           <t>B3 | 296呎 (1房)
 $686万
 $23,167/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -65943,15 +65943,15 @@
           <t>B5 | 240呎 (开放式)
 $538万
 $22,432/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
         <is>
-          <t>B6 | 236呎 (开放式)
+          <t>B6 | 237呎 (开放式)
 $535万
-$22,661/呎
-(24年-11月-05日)</t>
+$22,565/呎
+(24年-11月)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -65959,7 +65959,7 @@
           <t>B8 | 477呎 (2房)
 $973万
 $20,390/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O28" s="20" t="inlineStr"/>
@@ -65985,7 +65985,7 @@
           <t>A1 | 497呎 (2房)
 $1290万
 $25,958/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -65993,7 +65993,7 @@
           <t>A2 | 298呎 (1房)
 $754万
 $25,289/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -66001,7 +66001,7 @@
           <t>A3 | 299呎 (1房)
 $724万
 $24,212/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -66009,7 +66009,7 @@
           <t>A5 | 300呎 (1房)
 $739万
 $24,649/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -66017,7 +66017,7 @@
           <t>A6 | 469呎 (2房)
 $1163万
 $24,800/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
@@ -66026,7 +66026,7 @@
           <t>B1 | 467呎 (2房)
 $922万
 $19,746/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -66034,7 +66034,7 @@
           <t>B2 | 296呎 (1房)
 $672万
 $22,713/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -66042,7 +66042,7 @@
           <t>B3 | 296呎 (1房)
 $663万
 $22,407/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -66050,7 +66050,7 @@
           <t>B5 | 240呎 (开放式)
 $537万
 $22,388/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -66058,7 +66058,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,573/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N29" s="22" t="inlineStr">
@@ -66066,7 +66066,7 @@
           <t>B8 | 477呎 (2房)
 $971万
 $20,349/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O29" s="20" t="inlineStr"/>
@@ -66092,7 +66092,7 @@
           <t>A1 | 497呎 (2房)
 $1214万
 $24,420/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -66100,7 +66100,7 @@
           <t>A2 | 298呎 (1房)
 $752万
 $25,239/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -66108,7 +66108,7 @@
           <t>A3 | 299呎 (1房)
 $723万
 $24,164/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -66116,7 +66116,7 @@
           <t>A5 | 300呎 (1房)
 $738万
 $24,599/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -66124,7 +66124,7 @@
           <t>A6 | 469呎 (2房)
 $1161万
 $24,750/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
@@ -66133,7 +66133,7 @@
           <t>B1 | 467呎 (2房)
 $920万
 $19,706/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -66141,7 +66141,7 @@
           <t>B2 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -66149,7 +66149,7 @@
           <t>B3 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -66157,7 +66157,7 @@
           <t>B5 | 240呎 (开放式)
 $536万
 $22,343/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -66165,7 +66165,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,571/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
@@ -66173,7 +66173,7 @@
           <t>B8 | 477呎 (2房)
 $969万
 $20,308/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O30" s="20" t="inlineStr"/>
@@ -66199,7 +66199,7 @@
           <t>A1 | 497呎 (2房)
 $1210万
 $24,346/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -66207,7 +66207,7 @@
           <t>A2 | 298呎 (1房)
 $736万
 $24,697/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -66215,7 +66215,7 @@
           <t>A3 | 299呎 (1房)
 $720万
 $24,092/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -66223,7 +66223,7 @@
           <t>A5 | 300呎 (1房)
 $736万
 $24,525/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -66231,7 +66231,7 @@
           <t>A6 | 469呎 (2房)
 $1157万
 $24,676/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
@@ -66240,7 +66240,7 @@
           <t>B1 | 467呎 (2房)
 $948万
 $20,302/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -66248,7 +66248,7 @@
           <t>B2 | 296呎 (1房)
 $649万
 $21,941/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -66256,7 +66256,7 @@
           <t>B3 | 296呎 (1房)
 $628万
 $21,233/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -66264,7 +66264,7 @@
           <t>B5 | 240呎 (开放式)
 $535万
 $22,277/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -66272,7 +66272,7 @@
           <t>B6 | 236呎 (开放式)
 $531万
 $22,503/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N31" s="22" t="inlineStr">
@@ -66280,7 +66280,7 @@
           <t>B8 | 477呎 (2房)
 $966万
 $20,247/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O31" s="20" t="inlineStr"/>
@@ -66306,7 +66306,7 @@
           <t>A1 | 497呎 (2房)
 $1164万
 $23,429/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -66314,7 +66314,7 @@
           <t>A2 | 298呎 (1房)
 $720万
 $24,158/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -66322,7 +66322,7 @@
           <t>A3 | 299呎 (1房)
 $718万
 $24,019/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -66330,7 +66330,7 @@
           <t>A5 | 300呎 (1房)
 $734万
 $24,452/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -66338,7 +66338,7 @@
           <t>A6 | 469呎 (2房)
 $1154万
 $24,601/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
@@ -66347,7 +66347,7 @@
           <t>B1 | 467呎 (2房)
 $945万
 $20,241/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -66355,7 +66355,7 @@
           <t>B2 | 296呎 (1房)
 $648万
 $21,875/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -66363,7 +66363,7 @@
           <t>B3 | 296呎 (1房)
 $627万
 $21,170/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -66371,7 +66371,7 @@
           <t>B5 | 240呎 (开放式)
 $533万
 $22,210/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -66379,7 +66379,7 @@
           <t>B6 | 236呎 (开放式)
 $529万
 $22,436/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
@@ -66387,7 +66387,7 @@
           <t>B8 | 477呎 (2房)
 $963万
 $20,186/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O32" s="20" t="inlineStr"/>
@@ -66413,7 +66413,7 @@
           <t>A1 | 497呎 (2房)
 $1161万
 $23,359/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -66421,7 +66421,7 @@
           <t>A2 | 298呎 (1房)
 $711万
 $23,854/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -66429,7 +66429,7 @@
           <t>A3 | 299呎 (1房)
 $716万
 $23,947/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -66437,7 +66437,7 @@
           <t>A5 | 300呎 (1房)
 $731万
 $24,379/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -66445,7 +66445,7 @@
           <t>A6 | 469呎 (2房)
 $1150万
 $24,528/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
@@ -66454,7 +66454,7 @@
           <t>B1 | 467呎 (2房)
 $912万
 $19,530/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -66462,7 +66462,7 @@
           <t>B2 | 296呎 (1房)
 $646万
 $21,809/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -66470,7 +66470,7 @@
           <t>B3 | 296呎 (1房)
 $624万
 $21,072/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -66478,7 +66478,7 @@
           <t>B5 | 240呎 (开放式)
 $531万
 $22,144/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -66486,7 +66486,7 @@
           <t>B6 | 236呎 (开放式)
 $528万
 $22,369/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N33" s="22" t="inlineStr">
@@ -66494,7 +66494,7 @@
           <t>B8 | 477呎 (2房)
 $960万
 $20,126/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr"/>
@@ -66520,7 +66520,7 @@
           <t>A1 | 497呎 (2房)
 $1153万
 $23,202/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -66528,7 +66528,7 @@
           <t>A2 | 298呎 (1房)
 $688万
 $23,084/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -66536,7 +66536,7 @@
           <t>A3 | 299呎 (1房)
 $688万
 $22,998/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -66544,7 +66544,7 @@
           <t>A5 | 300呎 (1房)
 $689万
 $22,965/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -66552,7 +66552,7 @@
           <t>A6 | 469呎 (2房)
 $1131万
 $24,117/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
@@ -66561,7 +66561,7 @@
           <t>B1 | 467呎 (2房)
 $905万
 $19,381/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -66569,7 +66569,7 @@
           <t>B2 | 296呎 (1房)
 $641万
 $21,647/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -66577,7 +66577,7 @@
           <t>B3 | 296呎 (1房)
 $620万
 $20,949/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -66585,7 +66585,7 @@
           <t>B5 | 240呎 (开放式)
 $527万
 $21,943/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -66593,7 +66593,7 @@
           <t>B6 | 236呎 (开放式)
 $523万
 $22,168/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N34" s="22" t="inlineStr">
@@ -66601,7 +66601,7 @@
           <t>B8 | 477呎 (2房)
 $953万
 $19,973/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O34" s="20" t="inlineStr"/>
@@ -66627,7 +66627,7 @@
           <t>A1 | 497呎 (2房)
 $1183万
 $23,794/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -66635,7 +66635,7 @@
           <t>A2 | 298呎 (1房)
 $706万
 $23,679/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -66643,7 +66643,7 @@
           <t>A3 | 298呎 (1房)
 $683万
 $22,906/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -66651,7 +66651,7 @@
           <t>A5 | 300呎 (1房)
 $658万
 $21,941/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -66659,7 +66659,7 @@
           <t>A6 | 469呎 (2房)
 $1106万
 $23,574/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
@@ -66668,7 +66668,7 @@
           <t>B1 | 467呎 (2房)
 $897万
 $19,201/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -66676,7 +66676,7 @@
           <t>B2 | 296呎 (1房)
 $635万
 $21,452/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -66684,7 +66684,7 @@
           <t>B3 | 296呎 (1房)
 $614万
 $20,759/呎
-(24年-10月-24日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -66692,7 +66692,7 @@
           <t>B5 | 240呎 (开放式)
 $523万
 $21,800/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -66700,7 +66700,7 @@
           <t>B6 | 236呎 (开放式)
 $520万
 $22,026/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N35" s="22" t="inlineStr">
@@ -66708,7 +66708,7 @@
           <t>B8 | 477呎 (2房)
 $944万
 $19,787/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="O35" s="20" t="inlineStr"/>
@@ -66734,7 +66734,7 @@
           <t>A1 | 497呎 (2房)
 $1116万
 $22,451/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -66742,7 +66742,7 @@
           <t>A2 | 298呎 (1房)
 $664万
 $22,266/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -66750,7 +66750,7 @@
           <t>A3 | 299呎 (1房)
 $687万
 $22,967/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -66758,7 +66758,7 @@
           <t>A5 | 300呎 (1房)
 $668万
 $22,258/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -66766,7 +66766,7 @@
           <t>A6 | 469呎 (2房)
 $1095万
 $23,338/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
@@ -66775,7 +66775,7 @@
           <t>B1 | 467呎 (2房)
 $884万
 $18,931/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -66783,7 +66783,7 @@
           <t>B2 | 296呎 (1房)
 $626万
 $21,158/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -66791,7 +66791,7 @@
           <t>B3 | 296呎 (1房)
 $626万
 $21,158/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -66799,7 +66799,7 @@
           <t>B5 | 240呎 (开放式)
 $517万
 $21,524/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -66807,7 +66807,7 @@
           <t>B6 | 236呎 (开放式)
 $513万
 $21,749/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N36" s="22" t="inlineStr">
@@ -66815,7 +66815,7 @@
           <t>B8 | 477呎 (2房)
 $931万
 $19,509/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O36" s="20" t="inlineStr"/>
@@ -66841,7 +66841,7 @@
           <t>A1 | 497呎 (2房)
 $1049万
 $21,104/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -66849,7 +66849,7 @@
           <t>A2 | 298呎 (1房)
 $624万
 $20,930/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -66857,7 +66857,7 @@
           <t>A3 | 299呎 (1房)
 $632万
 $21,145/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -66865,7 +66865,7 @@
           <t>A5 | 300呎 (1房)
 $641万
 $21,368/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -66873,7 +66873,7 @@
           <t>A6 | 469呎 (2房)
 $1116万
 $23,787/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
@@ -66882,7 +66882,7 @@
           <t>B1 | 467呎 (2房)
 $858万
 $18,363/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -66890,7 +66890,7 @@
           <t>B2 | 296呎 (1房)
 $588万
 $19,861/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -66898,7 +66898,7 @@
           <t>B3 | 296呎 (1房)
 $606万
 $20,457/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -66906,7 +66906,7 @@
           <t>B5 | 240呎 (开放式)
 $501万
 $20,881/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -66914,7 +66914,7 @@
           <t>B6 | 236呎 (开放式)
 $497万
 $21,057/呎
-(24年-11月-05日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="N37" s="22" t="inlineStr">
@@ -66922,7 +66922,7 @@
           <t>B8 | 477呎 (2房)
 $903万
 $18,924/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -57339,7 +57339,7 @@
           <t>A | 1993呎 (4+房)
 $8305万
 $41,672/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -57351,7 +57351,7 @@
           <t>B | 1991呎 (4+房)
 $9103万
 $45,722/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr"/>
@@ -57364,7 +57364,7 @@
           <t>C | 1367呎 (4+房)
 $3989万
 $29,180/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="N7" s="22" t="inlineStr">
@@ -57372,7 +57372,7 @@
           <t>D | 1227呎 (4+房)
 $3336万
 $27,184/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="O7" s="20" t="inlineStr"/>
@@ -57416,7 +57416,7 @@
           <t>C | 1367呎 (4+房)
 $4078万
 $29,832/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="N8" s="22" t="inlineStr">
@@ -57424,7 +57424,7 @@
           <t>D | 1227呎 (4+房)
 $3452万
 $28,134/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr"/>
@@ -57443,7 +57443,7 @@
           <t>A | 1993呎 (4+房)
 $8098万
 $40,631/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -57468,7 +57468,7 @@
           <t>C | 1367呎 (4+房)
 $3862万
 $28,255/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N9" s="22" t="inlineStr">
@@ -57476,7 +57476,7 @@
           <t>D | 1227呎 (4+房)
 $3258万
 $26,553/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr"/>
@@ -57495,7 +57495,7 @@
           <t>A | 1921呎 (4+房)
 $8015万
 $41,721/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -57507,7 +57507,7 @@
           <t>B | 1985呎 (4+房)
 $7810万
 $39,345/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr"/>
@@ -57520,7 +57520,7 @@
           <t>C | 1365呎 (4+房)
 $4069万
 $29,812/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="N10" s="22" t="inlineStr">
@@ -57528,7 +57528,7 @@
           <t>D | 1227呎 (4+房)
 $3260万
 $26,571/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr"/>
@@ -57547,7 +57547,7 @@
           <t>A | 1993呎 (4+房)
 $7994万
 $40,109/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -57559,7 +57559,7 @@
           <t>B | 1914呎 (4+房)
 $7755万
 $40,517/呎
-(24年-12月)</t>
+(24年-12月-08日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr"/>
@@ -57572,7 +57572,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,802/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="N11" s="22" t="inlineStr">
@@ -57580,7 +57580,7 @@
           <t>D | 1227呎 (4+房)
 $3299万
 $26,887/呎
-(24年-12月)</t>
+(24年-12月-03日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr"/>
@@ -57599,7 +57599,7 @@
           <t>A | 1993呎 (4+房)
 $7952万
 $39,901/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -57611,7 +57611,7 @@
           <t>B | 1985呎 (4+房)
 $7652万
 $38,547/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr"/>
@@ -57624,7 +57624,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,800/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N12" s="22" t="inlineStr">
@@ -57632,7 +57632,7 @@
           <t>D | 1227呎 (4+房)
 $3113万
 $25,370/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr"/>
@@ -57651,7 +57651,7 @@
           <t>A | 1993呎 (4+房)
 $7288万
 $36,568/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -57676,7 +57676,7 @@
           <t>C | 1365呎 (4+房)
 $4038万
 $29,579/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="N13" s="22" t="inlineStr">
@@ -57684,7 +57684,7 @@
           <t>D | 1227呎 (4+房)
 $3068万
 $25,008/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr"/>
@@ -57703,7 +57703,7 @@
           <t>A | 1993呎 (4+房)
 $7268万
 $36,467/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr"/>
@@ -57715,7 +57715,7 @@
           <t>B | 1985呎 (4+房)
 $7500万
 $37,783/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr"/>
@@ -57728,7 +57728,7 @@
           <t>C | 1365呎 (4+房)
 $4068万
 $29,800/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="N14" s="22" t="inlineStr">
@@ -57736,7 +57736,7 @@
           <t>D | 1227呎 (4+房)
 $3262万
 $26,584/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr"/>
@@ -57755,7 +57755,7 @@
           <t>A | 1993呎 (4+房)
 $6989万
 $35,067/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr"/>
@@ -57767,7 +57767,7 @@
           <t>B | 1985呎 (4+房)
 $7344万
 $36,997/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -57780,7 +57780,7 @@
           <t>C | 1365呎 (4+房)
 $3699万
 $27,099/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -57788,7 +57788,7 @@
           <t>D | 1227呎 (4+房)
 $3279万
 $26,727/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr"/>
@@ -57807,7 +57807,7 @@
           <t>A | 1993呎 (4+房)
 $7036万
 $35,305/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr"/>
@@ -57819,7 +57819,7 @@
           <t>B | 1985呎 (4+房)
 $7238万
 $36,463/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -57832,7 +57832,7 @@
           <t>C | 1365呎 (4+房)
 $4069万
 $29,810/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -57840,7 +57840,7 @@
           <t>D | 1227呎 (4+房)
 $3261万
 $26,575/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr"/>
@@ -57859,7 +57859,7 @@
           <t>A | 1993呎 (4+房)
 $6852万
 $34,380/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr"/>
@@ -57871,7 +57871,7 @@
           <t>B | 1985呎 (4+房)
 $7197万
 $36,255/呎
-(25年-01月)</t>
+(25年-01月-20日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -57884,7 +57884,7 @@
           <t>C | 1365呎 (4+房)
 $3982万
 $29,174/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -57892,7 +57892,7 @@
           <t>D | 1227呎 (4+房)
 $3017万
 $24,592/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr"/>
@@ -57911,7 +57911,7 @@
           <t>A | 1993呎 (4+房)
 $6894万
 $34,589/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr"/>
@@ -57923,7 +57923,7 @@
           <t>B | 1985呎 (4+房)
 $7093万
 $35,735/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -57936,7 +57936,7 @@
           <t>C | 1365呎 (4+房)
 $3456万
 $25,320/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -57944,7 +57944,7 @@
           <t>D | 1227呎 (4+房)
 $3222万
 $26,259/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr"/>
@@ -57963,7 +57963,7 @@
           <t>A | 1993呎 (4+房)
 $6644万
 $33,339/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr"/>
@@ -57975,7 +57975,7 @@
           <t>B | 1985呎 (4+房)
 $7031万
 $35,422/呎
-(24年-12月)</t>
+(24年-12月-08日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -57988,7 +57988,7 @@
           <t>C | 1365呎 (4+房)
 $3600万
 $26,374/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -57996,7 +57996,7 @@
           <t>D | 1227呎 (4+房)
 $3132万
 $25,530/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr"/>
@@ -58015,7 +58015,7 @@
           <t>A | 1993呎 (4+房)
 $7018万
 $35,214/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr"/>
@@ -58027,7 +58027,7 @@
           <t>B | 1985呎 (4+房)
 $6990万
 $35,214/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -58040,7 +58040,7 @@
           <t>C | 1365呎 (4+房)
 $3793万
 $27,785/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -58048,7 +58048,7 @@
           <t>D | 1227呎 (4+房)
 $3324万
 $27,092/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr"/>
@@ -58068,7 +58068,7 @@
           <t>A1 | 559呎 (2房)
 $1277万
 $22,851/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -58076,7 +58076,7 @@
           <t>A2 | 443呎 (2房)
 $1094万
 $24,697/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -58084,7 +58084,7 @@
           <t>A3 | 443呎 (2房)
 $1052万
 $23,736/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -58092,7 +58092,7 @@
           <t>A5 | 887呎 (4+房)
 $2525万
 $28,464/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr"/>
@@ -58101,7 +58101,7 @@
           <t>B1 | 458呎 (2房)
 $987万
 $21,554/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -58109,7 +58109,7 @@
           <t>B2 | 298呎 (1房)
 $678万
 $22,765/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -58117,7 +58117,7 @@
           <t>B3 | 301呎 (1房)
 $685万
 $22,765/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -58125,7 +58125,7 @@
           <t>B5 | 298呎 (1房)
 $678万
 $22,765/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -58133,7 +58133,7 @@
           <t>B6 | 437呎 (2房)
 $973万
 $22,261/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr"/>
@@ -58155,7 +58155,7 @@
           <t>A1 | 559呎 (2房)
 $1254万
 $22,431/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -58163,7 +58163,7 @@
           <t>A2 | 443呎 (2房)
 $1089万
 $24,590/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -58171,7 +58171,7 @@
           <t>A3 | 443呎 (2房)
 $1089万
 $24,590/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -58179,7 +58179,7 @@
           <t>A5 | 887呎 (4+房)
 $2600万
 $29,308/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr"/>
@@ -58188,7 +58188,7 @@
           <t>B1 | 458呎 (2房)
 $979万
 $21,383/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -58196,7 +58196,7 @@
           <t>B2 | 298呎 (1房)
 $676万
 $22,675/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -58204,7 +58204,7 @@
           <t>B3 | 301呎 (1房)
 $683万
 $22,675/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -58212,7 +58212,7 @@
           <t>B5 | 298呎 (1房)
 $676万
 $22,675/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -58220,7 +58220,7 @@
           <t>B6 | 437呎 (2房)
 $965万
 $22,084/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr"/>
@@ -58242,7 +58242,7 @@
           <t>A1 | 559呎 (2房)
 $1289万
 $23,054/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -58250,7 +58250,7 @@
           <t>A2 | 443呎 (2房)
 $1076万
 $24,284/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -58258,7 +58258,7 @@
           <t>A3 | 443呎 (2房)
 $1076万
 $24,284/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -58266,7 +58266,7 @@
           <t>A5 | 887呎 (4+房)
 $2422万
 $27,303/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr"/>
@@ -58275,7 +58275,7 @@
           <t>B1 | 458呎 (2房)
 $973万
 $21,255/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -58283,7 +58283,7 @@
           <t>B2 | 298呎 (1房)
 $674万
 $22,630/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -58291,7 +58291,7 @@
           <t>B3 | 301呎 (1房)
 $681万
 $22,630/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -58299,7 +58299,7 @@
           <t>B5 | 298呎 (1房)
 $674万
 $22,630/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -58307,7 +58307,7 @@
           <t>B6 | 437呎 (2房)
 $959万
 $21,953/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr"/>
@@ -58329,7 +58329,7 @@
           <t>A1 | 559呎 (2房)
 $1287万
 $23,022/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -58337,7 +58337,7 @@
           <t>A2 | 443呎 (2房)
 $1067万
 $24,083/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -58345,7 +58345,7 @@
           <t>A3 | 443呎 (2房)
 $1067万
 $24,083/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -58353,7 +58353,7 @@
           <t>A5 | 887呎 (4+房)
 $2361万
 $26,617/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr"/>
@@ -58362,7 +58362,7 @@
           <t>B1 | 459呎 (2房)
 $968万
 $21,082/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -58370,7 +58370,7 @@
           <t>B2 | 298呎 (1房)
 $673万
 $22,585/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -58378,7 +58378,7 @@
           <t>B3 | 301呎 (1房)
 $680万
 $22,584/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -58386,7 +58386,7 @@
           <t>B5 | 298呎 (1房)
 $673万
 $22,585/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -58394,7 +58394,7 @@
           <t>B6 | 437呎 (2房)
 $954万
 $21,822/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr"/>
@@ -58416,7 +58416,7 @@
           <t>A1 | 559呎 (2房)
 $1285万
 $22,990/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -58424,7 +58424,7 @@
           <t>A2 | 443呎 (2房)
 $1023万
 $23,103/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -58432,7 +58432,7 @@
           <t>A3 | 443呎 (2房)
 $1023万
 $23,103/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -58440,7 +58440,7 @@
           <t>A5 | 887呎 (4+房)
 $2536万
 $28,591/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr"/>
@@ -58449,7 +58449,7 @@
           <t>B1 | 458呎 (2房)
 $963万
 $21,023/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -58457,7 +58457,7 @@
           <t>B2 | 298呎 (1房)
 $671万
 $22,517/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -58465,7 +58465,7 @@
           <t>B3 | 301呎 (1房)
 $677万
 $22,484/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -58473,7 +58473,7 @@
           <t>B5 | 298呎 (1房)
 $671万
 $22,517/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -58481,7 +58481,7 @@
           <t>B6 | 437呎 (2房)
 $949万
 $21,713/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr"/>
@@ -58503,7 +58503,7 @@
           <t>A1 | 559呎 (2房)
 $1308万
 $23,406/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -58511,7 +58511,7 @@
           <t>A2 | 443呎 (2房)
 $1020万
 $23,033/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -58519,7 +58519,7 @@
           <t>A3 | 443呎 (2房)
 $1062万
 $23,965/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -58527,7 +58527,7 @@
           <t>A5 | 887呎 (4+房)
 $2302万
 $25,950/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr"/>
@@ -58536,7 +58536,7 @@
           <t>B1 | 458呎 (2房)
 $960万
 $20,960/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -58544,7 +58544,7 @@
           <t>B2 | 298呎 (1房)
 $691万
 $23,198/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -58552,7 +58552,7 @@
           <t>B3 | 300呎 (1房)
 $676万
 $22,524/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -58560,7 +58560,7 @@
           <t>B5 | 298呎 (1房)
 $669万
 $22,449/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -58568,7 +58568,7 @@
           <t>B6 | 437呎 (2房)
 $946万
 $21,648/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M26" s="20" t="inlineStr"/>
@@ -58590,7 +58590,7 @@
           <t>A1 | 559呎 (2房)
 $1304万
 $23,336/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -58598,7 +58598,7 @@
           <t>A2 | 443呎 (2房)
 $1017万
 $22,965/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -58606,7 +58606,7 @@
           <t>A3 | 443呎 (2房)
 $1058万
 $23,894/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -58614,7 +58614,7 @@
           <t>A5 | 887呎 (4+房)
 $2399万
 $27,046/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr"/>
@@ -58623,7 +58623,7 @@
           <t>B1 | 458呎 (2房)
 $957万
 $20,898/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -58631,7 +58631,7 @@
           <t>B2 | 298呎 (1房)
 $667万
 $22,382/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -58639,7 +58639,7 @@
           <t>B3 | 300呎 (1房)
 $674万
 $22,457/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -58647,7 +58647,7 @@
           <t>B5 | 298呎 (1房)
 $667万
 $22,382/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -58655,7 +58655,7 @@
           <t>B6 | 437呎 (2房)
 $943万
 $21,584/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="M27" s="20" t="inlineStr"/>
@@ -58677,7 +58677,7 @@
           <t>A1 | 559呎 (2房)
 $1301万
 $23,266/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -58685,7 +58685,7 @@
           <t>A2 | 443呎 (2房)
 $1110万
 $25,053/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -58693,7 +58693,7 @@
           <t>A3 | 443呎 (2房)
 $1110万
 $25,053/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -58701,7 +58701,7 @@
           <t>A5 | 887呎 (4+房)
 $2357万
 $26,574/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr"/>
@@ -58710,7 +58710,7 @@
           <t>B1 | 458呎 (2房)
 $954万
 $20,835/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -58718,7 +58718,7 @@
           <t>B2 | 298呎 (1房)
 $665万
 $22,315/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -58726,7 +58726,7 @@
           <t>B3 | 301呎 (1房)
 $672万
 $22,315/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -58734,7 +58734,7 @@
           <t>B5 | 298呎 (1房)
 $665万
 $22,315/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -58742,7 +58742,7 @@
           <t>B6 | 437呎 (2房)
 $940万
 $21,519/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M28" s="20" t="inlineStr"/>
@@ -58764,7 +58764,7 @@
           <t>A1 | 559呎 (2房)
 $1383万
 $24,738/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -58772,7 +58772,7 @@
           <t>A2 | 443呎 (2房)
 $1108万
 $25,003/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -58780,7 +58780,7 @@
           <t>A3 | 443呎 (2房)
 $1108万
 $25,003/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -58788,7 +58788,7 @@
           <t>A5 | 887呎 (4+房)
 $2265万
 $25,533/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr"/>
@@ -58797,7 +58797,7 @@
           <t>B1 | 458呎 (2房)
 $952万
 $20,794/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -58805,7 +58805,7 @@
           <t>B2 | 298呎 (1房)
 $664万
 $22,271/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -58813,7 +58813,7 @@
           <t>B3 | 301呎 (1房)
 $670万
 $22,271/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -58821,7 +58821,7 @@
           <t>B5 | 298呎 (1房)
 $663万
 $22,237/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -58829,7 +58829,7 @@
           <t>B6 | 437呎 (2房)
 $938万
 $21,476/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M29" s="20" t="inlineStr"/>
@@ -58851,7 +58851,7 @@
           <t>A1 | 559呎 (2房)
 $1380万
 $24,689/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -58859,7 +58859,7 @@
           <t>A2 | 443呎 (2房)
 $1105万
 $24,953/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -58867,7 +58867,7 @@
           <t>A3 | 443呎 (2房)
 $1105万
 $24,953/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -58875,7 +58875,7 @@
           <t>A5 | 887呎 (4+房)
 $2431万
 $27,405/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr"/>
@@ -58884,7 +58884,7 @@
           <t>B1 | 458呎 (2房)
 $950万
 $20,752/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -58892,7 +58892,7 @@
           <t>B2 | 298呎 (1房)
 $684万
 $22,967/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -58900,7 +58900,7 @@
           <t>B3 | 301呎 (1房)
 $669万
 $22,226/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -58908,7 +58908,7 @@
           <t>B5 | 298呎 (1房)
 $662万
 $22,226/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -58916,7 +58916,7 @@
           <t>B6 | 437呎 (2房)
 $937万
 $21,433/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M30" s="20" t="inlineStr"/>
@@ -58938,7 +58938,7 @@
           <t>A1 | 559呎 (2房)
 $1377万
 $24,640/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -58946,7 +58946,7 @@
           <t>A2 | 443呎 (2房)
 $1103万
 $24,903/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -58954,7 +58954,7 @@
           <t>A3 | 443呎 (2房)
 $1103万
 $24,903/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -58962,7 +58962,7 @@
           <t>A5 | 887呎 (4+房)
 $2321万
 $26,165/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr"/>
@@ -58971,7 +58971,7 @@
           <t>B1 | 458呎 (2房)
 $912万
 $19,905/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -58979,7 +58979,7 @@
           <t>B2 | 298呎 (1房)
 $661万
 $22,182/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -58987,7 +58987,7 @@
           <t>B3 | 300呎 (1房)
 $668万
 $22,256/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -58995,7 +58995,7 @@
           <t>B5 | 298呎 (1房)
 $661万
 $22,182/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -59003,7 +59003,7 @@
           <t>B6 | 437呎 (2房)
 $935万
 $21,390/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="M31" s="20" t="inlineStr"/>
@@ -59025,7 +59025,7 @@
           <t>A1 | 559呎 (2房)
 $1321万
 $23,634/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -59033,7 +59033,7 @@
           <t>A2 | 443呎 (2房)
 $1101万
 $24,853/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -59041,7 +59041,7 @@
           <t>A3 | 443呎 (2房)
 $1101万
 $24,853/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -59049,7 +59049,7 @@
           <t>A5 | 887呎 (4+房)
 $2498万
 $28,162/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr"/>
@@ -59058,7 +59058,7 @@
           <t>B1 | 458呎 (2房)
 $947万
 $20,669/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -59066,7 +59066,7 @@
           <t>B2 | 298呎 (1房)
 $660万
 $22,138/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -59074,7 +59074,7 @@
           <t>B3 | 301呎 (1房)
 $666万
 $22,138/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -59082,7 +59082,7 @@
           <t>B5 | 298呎 (1房)
 $660万
 $22,138/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -59090,7 +59090,7 @@
           <t>B6 | 437呎 (2房)
 $933万
 $21,348/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M32" s="20" t="inlineStr"/>
@@ -59112,7 +59112,7 @@
           <t>A1 | 559呎 (2房)
 $1372万
 $24,541/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -59120,7 +59120,7 @@
           <t>A2 | 443呎 (2房)
 $1099万
 $24,803/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -59128,7 +59128,7 @@
           <t>A3 | 443呎 (2房)
 $1099万
 $24,803/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -59136,7 +59136,7 @@
           <t>A5 | 887呎 (4+房)
 $2339万
 $26,368/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr"/>
@@ -59145,7 +59145,7 @@
           <t>B1 | 458呎 (2房)
 $945万
 $20,628/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -59153,7 +59153,7 @@
           <t>B2 | 298呎 (1房)
 $658万
 $22,093/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -59161,7 +59161,7 @@
           <t>B3 | 301呎 (1房)
 $665万
 $22,093/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -59169,7 +59169,7 @@
           <t>B5 | 298呎 (1房)
 $658万
 $22,093/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -59177,7 +59177,7 @@
           <t>B6 | 437呎 (2房)
 $931万
 $21,305/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M33" s="20" t="inlineStr"/>
@@ -59199,7 +59199,7 @@
           <t>A1 | 559呎 (2房)
 $1316万
 $23,540/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -59207,7 +59207,7 @@
           <t>A2 | 443呎 (2房)
 $1097万
 $24,754/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -59215,7 +59215,7 @@
           <t>A3 | 443呎 (2房)
 $1097万
 $24,754/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -59223,7 +59223,7 @@
           <t>A5 | 887呎 (4+房)
 $2328万
 $26,246/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr"/>
@@ -59232,7 +59232,7 @@
           <t>B1 | 458呎 (2房)
 $943万
 $20,586/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -59240,7 +59240,7 @@
           <t>B2 | 298呎 (1房)
 $657万
 $22,049/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -59248,7 +59248,7 @@
           <t>B3 | 301呎 (1房)
 $664万
 $22,049/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -59256,7 +59256,7 @@
           <t>B5 | 298呎 (1房)
 $657万
 $22,049/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -59264,7 +59264,7 @@
           <t>B6 | 437呎 (2房)
 $929万
 $21,262/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M34" s="20" t="inlineStr"/>
@@ -59286,7 +59286,7 @@
           <t>A1 | 559呎 (2房)
 $1341万
 $23,990/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -59294,7 +59294,7 @@
           <t>A2 | 443呎 (2房)
 $1093万
 $24,679/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -59302,7 +59302,7 @@
           <t>A3 | 443呎 (2房)
 $1093万
 $24,679/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -59310,7 +59310,7 @@
           <t>A5 | 887呎 (4+房)
 $2404万
 $27,105/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr"/>
@@ -59319,7 +59319,7 @@
           <t>B1 | 458呎 (2房)
 $940万
 $20,525/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -59327,7 +59327,7 @@
           <t>B2 | 298呎 (1房)
 $655万
 $21,983/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -59335,7 +59335,7 @@
           <t>B3 | 301呎 (1房)
 $662万
 $21,983/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -59343,7 +59343,7 @@
           <t>B5 | 298呎 (1房)
 $655万
 $21,983/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -59351,7 +59351,7 @@
           <t>B6 | 437呎 (2房)
 $926万
 $21,198/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M35" s="20" t="inlineStr"/>
@@ -59373,7 +59373,7 @@
           <t>A1 | 559呎 (2房)
 $1337万
 $23,918/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -59381,7 +59381,7 @@
           <t>A2 | 443呎 (2房)
 $1090万
 $24,605/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -59389,7 +59389,7 @@
           <t>A3 | 443呎 (2房)
 $1090万
 $24,605/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -59397,7 +59397,7 @@
           <t>A5 | 887呎 (4+房)
 $2204万
 $24,848/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr"/>
@@ -59406,7 +59406,7 @@
           <t>B1 | 458呎 (2房)
 $937万
 $20,463/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -59414,7 +59414,7 @@
           <t>B2 | 298呎 (1房)
 $653万
 $21,917/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -59422,7 +59422,7 @@
           <t>B3 | 300呎 (1房)
 $660万
 $21,990/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -59430,7 +59430,7 @@
           <t>B5 | 298呎 (1房)
 $653万
 $21,917/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -59438,7 +59438,7 @@
           <t>B6 | 437呎 (2房)
 $924万
 $21,135/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="M36" s="20" t="inlineStr"/>
@@ -59460,7 +59460,7 @@
           <t>A1 | 559呎 (2房)
 $1262万
 $22,569/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -59468,7 +59468,7 @@
           <t>A2 | 443呎 (2房)
 $1067万
 $24,093/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -59476,7 +59476,7 @@
           <t>A3 | 443呎 (2房)
 $1067万
 $24,093/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -59484,7 +59484,7 @@
           <t>A5 | 887呎 (4+房)
 $2220万
 $25,028/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr"/>
@@ -59493,7 +59493,7 @@
           <t>B1 | 458呎 (2房)
 $934万
 $20,402/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -59501,7 +59501,7 @@
           <t>B2 | 298呎 (1房)
 $651万
 $21,851/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -59509,7 +59509,7 @@
           <t>B3 | 300呎 (1房)
 $658万
 $21,924/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -59517,7 +59517,7 @@
           <t>B5 | 298呎 (1房)
 $651万
 $21,851/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -59525,7 +59525,7 @@
           <t>B6 | 437呎 (2房)
 $921万
 $21,071/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M37" s="20" t="inlineStr"/>
@@ -59547,7 +59547,7 @@
           <t>A1 | 559呎 (2房)
 $1252万
 $22,391/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -59555,7 +59555,7 @@
           <t>A2 | 443呎 (2房)
 $1060万
 $23,931/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -59563,7 +59563,7 @@
           <t>A3 | 443呎 (2房)
 $1060万
 $23,931/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -59571,7 +59571,7 @@
           <t>A5 | 887呎 (4+房)
 $2266万
 $25,547/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G38" s="20" t="inlineStr"/>
@@ -59580,7 +59580,7 @@
           <t>B1 | 458呎 (2房)
 $927万
 $20,247/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -59588,7 +59588,7 @@
           <t>B2 | 298呎 (1房)
 $646万
 $21,688/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -59596,7 +59596,7 @@
           <t>B3 | 301呎 (1房)
 $652万
 $21,655/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
@@ -59604,7 +59604,7 @@
           <t>B5 | 298呎 (1房)
 $646万
 $21,688/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
@@ -59612,7 +59612,7 @@
           <t>B6 | 437呎 (2房)
 $914万
 $20,911/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M38" s="20" t="inlineStr"/>
@@ -59634,7 +59634,7 @@
           <t>A1 | 559呎 (2房)
 $1213万
 $21,697/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -59642,7 +59642,7 @@
           <t>A2 | 443呎 (2房)
 $1004万
 $22,671/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -59650,7 +59650,7 @@
           <t>A3 | 443呎 (2房)
 $1004万
 $22,671/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -59658,7 +59658,7 @@
           <t>A5 | 887呎 (4+房)
 $2127万
 $23,977/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="G39" s="20" t="inlineStr"/>
@@ -59667,7 +59667,7 @@
           <t>B1 | 458呎 (2房)
 $919万
 $20,059/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -59675,7 +59675,7 @@
           <t>B2 | 298呎 (1房)
 $640万
 $21,492/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
@@ -59683,7 +59683,7 @@
           <t>B3 | 301呎 (1房)
 $647万
 $21,492/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="K39" s="22" t="inlineStr">
@@ -59691,7 +59691,7 @@
           <t>B5 | 298呎 (1房)
 $640万
 $21,492/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr">
@@ -59699,7 +59699,7 @@
           <t>B6 | 438呎 (2房)
 $905万
 $20,670/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="M39" s="20" t="inlineStr"/>
@@ -59721,7 +59721,7 @@
           <t>A1 | 559呎 (2房)
 $1125万
 $20,125/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="D40" s="22" t="inlineStr">
@@ -59729,7 +59729,7 @@
           <t>A2 | 443呎 (2房)
 $964万
 $21,765/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E40" s="22" t="inlineStr">
@@ -59737,7 +59737,7 @@
           <t>A3 | 443呎 (2房)
 $964万
 $21,765/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F40" s="22" t="inlineStr">
@@ -59745,7 +59745,7 @@
           <t>A5 | 887呎 (4+房)
 $2079万
 $23,439/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G40" s="20" t="inlineStr"/>
@@ -59754,7 +59754,7 @@
           <t>B1 | 458呎 (2房)
 $906万
 $19,777/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I40" s="22" t="inlineStr">
@@ -59762,7 +59762,7 @@
           <t>B2 | 298呎 (1房)
 $632万
 $21,199/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J40" s="22" t="inlineStr">
@@ -59770,7 +59770,7 @@
           <t>B3 | 301呎 (1房)
 $638万
 $21,199/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K40" s="22" t="inlineStr">
@@ -59778,7 +59778,7 @@
           <t>B5 | 298呎 (1房)
 $632万
 $21,199/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="L40" s="22" t="inlineStr">
@@ -59786,7 +59786,7 @@
           <t>B6 | 437呎 (2房)
 $922万
 $21,107/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="M40" s="20" t="inlineStr"/>
@@ -59808,7 +59808,7 @@
           <t>A1 | 559呎 (2房)
 $1012万
 $18,112/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D41" s="22" t="inlineStr">
@@ -59816,7 +59816,7 @@
           <t>A2 | 443呎 (2房)
 $868万
 $19,588/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E41" s="22" t="inlineStr">
@@ -59824,7 +59824,7 @@
           <t>A3 | 443呎 (2房)
 $868万
 $19,588/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F41" s="22" t="inlineStr">
@@ -59832,7 +59832,7 @@
           <t>A5 | 854呎 (3房)
 $1869万
 $21,888/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G41" s="20" t="inlineStr"/>
@@ -59841,7 +59841,7 @@
           <t>B1 | 459呎 (2房)
 $874万
 $19,043/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="I41" s="22" t="inlineStr">
@@ -59849,7 +59849,7 @@
           <t>B2 | 298呎 (1房)
 $610万
 $20,457/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J41" s="22" t="inlineStr">
@@ -59857,7 +59857,7 @@
           <t>B3 | 301呎 (1房)
 $616万
 $20,457/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K41" s="22" t="inlineStr">
@@ -59865,7 +59865,7 @@
           <t>B5 | 298呎 (1房)
 $610万
 $20,457/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="L41" s="22" t="inlineStr">
@@ -59873,7 +59873,7 @@
           <t>B6 | 437呎 (2房)
 $890万
 $20,368/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M41" s="20" t="inlineStr"/>
@@ -60219,7 +60219,7 @@
           <t>A | 929呎 (4+房)
 $3300万
 $35,522/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -60233,7 +60233,7 @@
           <t>B | 686呎 (3房)
 $1967万
 $28,676/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr"/>
@@ -60247,7 +60247,7 @@
           <t>C | 919呎 (3房)
 $2900万
 $31,556/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -60255,7 +60255,7 @@
           <t>D | 655呎 (2房)
 $1469万
 $22,430/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="R7" s="22" t="inlineStr">
@@ -60263,7 +60263,7 @@
           <t>E | 457呎 (2房)
 $991万
 $21,674/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="S7" s="22" t="inlineStr">
@@ -60271,7 +60271,7 @@
           <t>F | 458呎 (2房)
 $991万
 $21,627/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="T7" s="22" t="inlineStr">
@@ -60279,7 +60279,7 @@
           <t>G | 614呎 (2房)
 $1420万
 $23,127/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="U7" s="20" t="inlineStr"/>
@@ -60298,7 +60298,7 @@
           <t>A | 929呎 (4+房)
 $3104万
 $33,408/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -60312,7 +60312,7 @@
           <t>B | 686呎 (3房)
 $1961万
 $28,591/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr"/>
@@ -60326,7 +60326,7 @@
           <t>C | 919呎 (3房)
 $2966万
 $32,276/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -60334,7 +60334,7 @@
           <t>D | 655呎 (2房)
 $1465万
 $22,363/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="R8" s="22" t="inlineStr">
@@ -60342,7 +60342,7 @@
           <t>E | 457呎 (2房)
 $988万
 $21,609/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="S8" s="22" t="inlineStr">
@@ -60350,7 +60350,7 @@
           <t>F | 458呎 (2房)
 $988万
 $21,562/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="T8" s="22" t="inlineStr">
@@ -60358,7 +60358,7 @@
           <t>G | 614呎 (2房)
 $1416万
 $23,058/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr"/>
@@ -60377,7 +60377,7 @@
           <t>A | 929呎 (4+房)
 $3236万
 $34,835/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -60391,7 +60391,7 @@
           <t>B | 686呎 (3房)
 $1879万
 $27,397/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr"/>
@@ -60405,7 +60405,7 @@
           <t>C | 919呎 (3房)
 $2711万
 $29,499/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="Q9" s="22" t="inlineStr">
@@ -60413,7 +60413,7 @@
           <t>D | 655呎 (2房)
 $1460万
 $22,296/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="R9" s="22" t="inlineStr">
@@ -60421,7 +60421,7 @@
           <t>E | 457呎 (2房)
 $985万
 $21,545/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="S9" s="22" t="inlineStr">
@@ -60429,7 +60429,7 @@
           <t>F | 458呎 (2房)
 $985万
 $21,498/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="T9" s="22" t="inlineStr">
@@ -60437,7 +60437,7 @@
           <t>G | 614呎 (2房)
 $1412万
 $22,989/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="U9" s="20" t="inlineStr"/>
@@ -60456,7 +60456,7 @@
           <t>A | 929呎 (4+房)
 $3053万
 $32,861/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -60470,7 +60470,7 @@
           <t>B | 686呎 (3房)
 $1950万
 $28,420/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr"/>
@@ -60484,7 +60484,7 @@
           <t>C | 919呎 (3房)
 $2874万
 $31,271/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -60492,7 +60492,7 @@
           <t>D | 655呎 (2房)
 $1456万
 $22,229/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="R10" s="22" t="inlineStr">
@@ -60500,7 +60500,7 @@
           <t>E | 457呎 (2房)
 $1014万
 $22,196/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="S10" s="22" t="inlineStr">
@@ -60508,7 +60508,7 @@
           <t>F | 458呎 (2房)
 $982万
 $21,433/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="T10" s="22" t="inlineStr">
@@ -60516,7 +60516,7 @@
           <t>G | 614呎 (2房)
 $1407万
 $22,920/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="U10" s="20" t="inlineStr"/>
@@ -60535,7 +60535,7 @@
           <t>A | 929呎 (4+房)
 $3001万
 $32,305/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -60549,7 +60549,7 @@
           <t>B | 686呎 (3房)
 $1944万
 $28,334/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr"/>
@@ -60563,7 +60563,7 @@
           <t>C | 919呎 (3房)
 $2688万
 $29,249/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -60571,7 +60571,7 @@
           <t>D | 655呎 (2房)
 $1452万
 $22,163/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="R11" s="22" t="inlineStr">
@@ -60579,7 +60579,7 @@
           <t>E | 457呎 (2房)
 $979万
 $21,416/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="S11" s="22" t="inlineStr">
@@ -60587,7 +60587,7 @@
           <t>F | 458呎 (2房)
 $979万
 $21,369/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="T11" s="22" t="inlineStr">
@@ -60595,7 +60595,7 @@
           <t>G | 614呎 (2房)
 $1403万
 $22,851/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="U11" s="20" t="inlineStr"/>
@@ -60614,7 +60614,7 @@
           <t>A | 929呎 (4+房)
 $3001万
 $32,300/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -60628,7 +60628,7 @@
           <t>B | 686呎 (3房)
 $1938万
 $28,249/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr"/>
@@ -60642,7 +60642,7 @@
           <t>C | 919呎 (3房)
 $2662万
 $28,972/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -60650,7 +60650,7 @@
           <t>D | 655呎 (2房)
 $1447万
 $22,096/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="R12" s="22" t="inlineStr">
@@ -60658,7 +60658,7 @@
           <t>E | 457呎 (2房)
 $976万
 $21,351/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="S12" s="22" t="inlineStr">
@@ -60666,7 +60666,7 @@
           <t>F | 458呎 (2房)
 $976万
 $21,305/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="T12" s="22" t="inlineStr">
@@ -60674,7 +60674,7 @@
           <t>G | 614呎 (2房)
 $1399万
 $22,783/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="U12" s="20" t="inlineStr"/>
@@ -60693,7 +60693,7 @@
           <t>A | 929呎 (4+房)
 $2856万
 $30,743/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -60707,7 +60707,7 @@
           <t>B | 686呎 (3房)
 $1932万
 $28,164/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr"/>
@@ -60721,7 +60721,7 @@
           <t>C | 919呎 (3房)
 $2835万
 $30,849/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -60729,7 +60729,7 @@
           <t>D | 655呎 (2房)
 $1443万
 $22,030/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="R13" s="22" t="inlineStr">
@@ -60737,7 +60737,7 @@
           <t>E | 457呎 (2房)
 $973万
 $21,287/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="S13" s="22" t="inlineStr">
@@ -60745,7 +60745,7 @@
           <t>F | 458呎 (2房)
 $973万
 $21,241/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="T13" s="22" t="inlineStr">
@@ -60753,7 +60753,7 @@
           <t>G | 614呎 (2房)
 $1340万
 $21,831/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="U13" s="20" t="inlineStr"/>
@@ -60772,7 +60772,7 @@
           <t>A | 929呎 (4+房)
 $3100万
 $33,369/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr"/>
@@ -60786,7 +60786,7 @@
           <t>B | 687呎 (3房)
 $1851万
 $26,949/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr"/>
@@ -60800,7 +60800,7 @@
           <t>C | 919呎 (3房)
 $2766万
 $30,098/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="Q14" s="22" t="inlineStr">
@@ -60808,7 +60808,7 @@
           <t>D | 655呎 (2房)
 $1809万
 $27,621/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="R14" s="22" t="inlineStr">
@@ -60816,7 +60816,7 @@
           <t>E | 457呎 (2房)
 $1110万
 $24,289/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="S14" s="21" t="inlineStr">
@@ -60852,7 +60852,7 @@
           <t>A1 | 501呎 (2房)
 $1182万
 $23,585/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -60860,7 +60860,7 @@
           <t>A2 | 295呎 (1房)
 $745万
 $25,241/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -60868,7 +60868,7 @@
           <t>A3 | 299呎 (1房)
 $748万
 $25,015/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -60876,7 +60876,7 @@
           <t>A5 | 299呎 (1房)
 $748万
 $25,015/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -60884,7 +60884,7 @@
           <t>A6 | 297呎 (1房)
 $748万
 $25,177/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -60892,7 +60892,7 @@
           <t>A8 | 509呎 (2房)
 $1152万
 $22,634/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr"/>
@@ -60901,7 +60901,7 @@
           <t>B1 | 454呎 (2房)
 $994万
 $21,884/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -60909,7 +60909,7 @@
           <t>B2 | 299呎 (1房)
 $661万
 $22,121/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -60917,7 +60917,7 @@
           <t>B3 | 296呎 (1房)
 $655万
 $22,121/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -60925,7 +60925,7 @@
           <t>B5 | 240呎 (开放式)
 $573万
 $23,863/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -60933,7 +60933,7 @@
           <t>B6 | 236呎 (开放式)
 $566万
 $23,997/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="O15" s="22" t="inlineStr">
@@ -60941,7 +60941,7 @@
           <t>B8 | 460呎 (2房)
 $959万
 $20,838/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr"/>
@@ -60966,7 +60966,7 @@
           <t>A1 | 501呎 (2房)
 $1162万
 $23,193/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -60974,7 +60974,7 @@
           <t>A2 | 295呎 (1房)
 $737万
 $24,992/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -60982,7 +60982,7 @@
           <t>A3 | 299呎 (1房)
 $741万
 $24,767/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -60990,7 +60990,7 @@
           <t>A5 | 298呎 (1房)
 $741万
 $24,850/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -60998,7 +60998,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,927/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -61006,7 +61006,7 @@
           <t>A8 | 509呎 (2房)
 $1132万
 $22,243/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr"/>
@@ -61015,7 +61015,7 @@
           <t>B1 | 454呎 (2房)
 $988万
 $21,753/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -61023,7 +61023,7 @@
           <t>B2 | 299呎 (1房)
 $659万
 $22,033/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -61031,7 +61031,7 @@
           <t>B3 | 296呎 (1房)
 $652万
 $22,033/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -61039,7 +61039,7 @@
           <t>B5 | 240呎 (开放式)
 $568万
 $23,678/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -61047,7 +61047,7 @@
           <t>B6 | 236呎 (开放式)
 $562万
 $23,808/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="O16" s="22" t="inlineStr">
@@ -61055,7 +61055,7 @@
           <t>B8 | 460呎 (2房)
 $953万
 $20,714/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr"/>
@@ -61080,7 +61080,7 @@
           <t>A1 | 501呎 (2房)
 $1148万
 $22,918/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -61088,7 +61088,7 @@
           <t>A2 | 295呎 (1房)
 $737万
 $24,971/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -61096,7 +61096,7 @@
           <t>A3 | 298呎 (1房)
 $740万
 $24,826/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -61104,7 +61104,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,743/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -61112,7 +61112,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,903/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -61120,7 +61120,7 @@
           <t>A8 | 509呎 (2房)
 $1118万
 $21,969/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr"/>
@@ -61129,7 +61129,7 @@
           <t>B1 | 454呎 (2房)
 $984万
 $21,667/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -61137,7 +61137,7 @@
           <t>B2 | 299呎 (1房)
 $657万
 $21,989/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -61145,7 +61145,7 @@
           <t>B3 | 296呎 (1房)
 $650万
 $21,955/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -61153,7 +61153,7 @@
           <t>B5 | 240呎 (开放式)
 $565万
 $23,539/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -61161,7 +61161,7 @@
           <t>B6 | 236呎 (开放式)
 $559万
 $23,669/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="O17" s="22" t="inlineStr">
@@ -61169,7 +61169,7 @@
           <t>B8 | 460呎 (2房)
 $949万
 $20,632/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr"/>
@@ -61194,7 +61194,7 @@
           <t>A1 | 501呎 (2房)
 $1144万
 $22,840/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -61202,7 +61202,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,936/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -61210,7 +61210,7 @@
           <t>A3 | 299呎 (1房)
 $739万
 $24,709/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -61218,7 +61218,7 @@
           <t>A5 | 299呎 (1房)
 $739万
 $24,709/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -61226,7 +61226,7 @@
           <t>A6 | 297呎 (1房)
 $739万
 $24,870/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -61234,7 +61234,7 @@
           <t>A8 | 509呎 (2房)
 $1113万
 $21,871/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr"/>
@@ -61243,7 +61243,7 @@
           <t>B1 | 454呎 (2房)
 $980万
 $21,580/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -61251,7 +61251,7 @@
           <t>B2 | 299呎 (1房)
 $656万
 $21,945/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -61259,7 +61259,7 @@
           <t>B3 | 296呎 (1房)
 $650万
 $21,945/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -61267,7 +61267,7 @@
           <t>B5 | 240呎 (开放式)
 $562万
 $23,400/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -61275,7 +61275,7 @@
           <t>B6 | 236呎 (开放式)
 $534万
 $22,614/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="O18" s="22" t="inlineStr">
@@ -61283,7 +61283,7 @@
           <t>B8 | 460呎 (2房)
 $945万
 $20,549/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr"/>
@@ -61308,7 +61308,7 @@
           <t>A1 | 501呎 (2房)
 $1136万
 $22,674/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -61316,7 +61316,7 @@
           <t>A2 | 295呎 (1房)
 $735万
 $24,901/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -61324,7 +61324,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,673/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -61332,7 +61332,7 @@
           <t>A5 | 299呎 (1房)
 $737万
 $24,640/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -61340,7 +61340,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,833/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -61348,7 +61348,7 @@
           <t>A8 | 509呎 (2房)
 $1106万
 $21,725/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr"/>
@@ -61357,7 +61357,7 @@
           <t>B1 | 454呎 (2房)
 $976万
 $21,494/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -61365,7 +61365,7 @@
           <t>B2 | 299呎 (1房)
 $655万
 $21,901/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -61373,7 +61373,7 @@
           <t>B3 | 296呎 (1房)
 $648万
 $21,901/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -61381,7 +61381,7 @@
           <t>B5 | 240呎 (开放式)
 $549万
 $22,870/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -61389,7 +61389,7 @@
           <t>B6 | 236呎 (开放式)
 $545万
 $23,102/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O19" s="22" t="inlineStr">
@@ -61397,7 +61397,7 @@
           <t>B8 | 460呎 (2房)
 $941万
 $20,467/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr"/>
@@ -61422,7 +61422,7 @@
           <t>A1 | 501呎 (2房)
 $1250万
 $24,942/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -61430,7 +61430,7 @@
           <t>A2 | 295呎 (1房)
 $734万
 $24,865/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -61438,7 +61438,7 @@
           <t>A3 | 299呎 (1房)
 $737万
 $24,637/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -61446,7 +61446,7 @@
           <t>A5 | 298呎 (1房)
 $737万
 $24,720/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -61454,7 +61454,7 @@
           <t>A6 | 297呎 (1房)
 $736万
 $24,797/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -61462,7 +61462,7 @@
           <t>A8 | 509呎 (2房)
 $1101万
 $21,639/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr"/>
@@ -61471,7 +61471,7 @@
           <t>B1 | 454呎 (2房)
 $972万
 $21,409/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -61479,7 +61479,7 @@
           <t>B2 | 299呎 (1房)
 $652万
 $21,814/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -61487,7 +61487,7 @@
           <t>B3 | 296呎 (1房)
 $646万
 $21,814/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -61495,7 +61495,7 @@
           <t>B5 | 240呎 (开放式)
 $547万
 $22,779/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -61503,7 +61503,7 @@
           <t>B6 | 236呎 (开放式)
 $543万
 $23,010/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="O20" s="22" t="inlineStr">
@@ -61511,7 +61511,7 @@
           <t>B8 | 460呎 (2房)
 $938万
 $20,386/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr"/>
@@ -61536,7 +61536,7 @@
           <t>A1 | 501呎 (2房)
 $1246万
 $24,868/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -61544,7 +61544,7 @@
           <t>A2 | 295呎 (1房)
 $760万
 $25,766/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -61552,7 +61552,7 @@
           <t>A3 | 299呎 (1房)
 $764万
 $25,535/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -61560,7 +61560,7 @@
           <t>A5 | 299呎 (1房)
 $762万
 $25,502/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -61568,7 +61568,7 @@
           <t>A6 | 297呎 (1房)
 $763万
 $25,700/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -61576,7 +61576,7 @@
           <t>A8 | 509呎 (2房)
 $1098万
 $21,574/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr"/>
@@ -61585,7 +61585,7 @@
           <t>B1 | 454呎 (2房)
 $969万
 $21,345/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -61593,7 +61593,7 @@
           <t>B2 | 299呎 (1房)
 $650万
 $21,749/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -61601,7 +61601,7 @@
           <t>B3 | 296呎 (1房)
 $644万
 $21,749/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -61609,7 +61609,7 @@
           <t>B5 | 240呎 (开放式)
 $545万
 $22,710/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -61617,7 +61617,7 @@
           <t>B6 | 236呎 (开放式)
 $541万
 $22,941/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="O21" s="22" t="inlineStr">
@@ -61625,7 +61625,7 @@
           <t>B8 | 460呎 (2房)
 $935万
 $20,325/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr"/>
@@ -61650,7 +61650,7 @@
           <t>A1 | 501呎 (2房)
 $1242万
 $24,793/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -61658,7 +61658,7 @@
           <t>A2 | 295呎 (1房)
 $758万
 $25,689/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -61666,7 +61666,7 @@
           <t>A3 | 299呎 (1房)
 $761万
 $25,459/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -61674,7 +61674,7 @@
           <t>A5 | 299呎 (1房)
 $761万
 $25,459/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -61682,7 +61682,7 @@
           <t>A6 | 297呎 (1房)
 $761万
 $25,624/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -61690,7 +61690,7 @@
           <t>A8 | 509呎 (2房)
 $1095万
 $21,509/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr"/>
@@ -61699,7 +61699,7 @@
           <t>B1 | 454呎 (2房)
 $966万
 $21,281/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -61707,7 +61707,7 @@
           <t>B2 | 299呎 (1房)
 $648万
 $21,684/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -61715,7 +61715,7 @@
           <t>B3 | 296呎 (1房)
 $642万
 $21,684/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -61723,7 +61723,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,642/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -61731,7 +61731,7 @@
           <t>B6 | 236呎 (开放式)
 $540万
 $22,872/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="O22" s="22" t="inlineStr">
@@ -61739,7 +61739,7 @@
           <t>B8 | 460呎 (2房)
 $931万
 $20,242/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr"/>
@@ -61764,7 +61764,7 @@
           <t>A1 | 501呎 (2房)
 $1238万
 $24,719/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -61772,7 +61772,7 @@
           <t>A2 | 295呎 (1房)
 $740万
 $25,100/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -61780,7 +61780,7 @@
           <t>A3 | 299呎 (1房)
 $745万
 $24,908/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -61788,7 +61788,7 @@
           <t>A5 | 299呎 (1房)
 $745万
 $24,908/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -61796,7 +61796,7 @@
           <t>A6 | 297呎 (1房)
 $744万
 $25,036/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -61804,7 +61804,7 @@
           <t>A8 | 509呎 (2房)
 $1092万
 $21,445/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr"/>
@@ -61813,7 +61813,7 @@
           <t>B1 | 454呎 (2房)
 $963万
 $21,217/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -61821,7 +61821,7 @@
           <t>B2 | 299呎 (1房)
 $645万
 $21,585/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -61829,7 +61829,7 @@
           <t>B3 | 296呎 (1房)
 $640万
 $21,619/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -61837,7 +61837,7 @@
           <t>B5 | 240呎 (开放式)
 $542万
 $22,575/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -61845,7 +61845,7 @@
           <t>B6 | 236呎 (开放式)
 $538万
 $22,804/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="O23" s="22" t="inlineStr">
@@ -61853,7 +61853,7 @@
           <t>B8 | 460呎 (2房)
 $929万
 $20,203/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr"/>
@@ -61878,7 +61878,7 @@
           <t>A1 | 501呎 (2房)
 $1235万
 $24,645/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -61886,7 +61886,7 @@
           <t>A2 | 295呎 (1房)
 $739万
 $25,059/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -61894,7 +61894,7 @@
           <t>A3 | 299呎 (1房)
 $742万
 $24,800/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -61902,7 +61902,7 @@
           <t>A5 | 299呎 (1房)
 $743万
 $24,833/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -61910,7 +61910,7 @@
           <t>A6 | 297呎 (1房)
 $741万
 $24,961/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -61918,7 +61918,7 @@
           <t>A8 | 509呎 (2房)
 $1087万
 $21,361/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr"/>
@@ -61927,7 +61927,7 @@
           <t>B1 | 454呎 (2房)
 $960万
 $21,154/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -61935,7 +61935,7 @@
           <t>B2 | 299呎 (1房)
 $643万
 $21,521/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -61943,7 +61943,7 @@
           <t>B3 | 296呎 (1房)
 $638万
 $21,554/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -61951,7 +61951,7 @@
           <t>B5 | 240呎 (开放式)
 $540万
 $22,508/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -61959,7 +61959,7 @@
           <t>B6 | 236呎 (开放式)
 $537万
 $22,736/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="O24" s="22" t="inlineStr">
@@ -61967,7 +61967,7 @@
           <t>B8 | 460呎 (2房)
 $927万
 $20,143/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr"/>
@@ -61992,7 +61992,7 @@
           <t>A1 | 501呎 (2房)
 $1273万
 $25,416/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -62000,7 +62000,7 @@
           <t>A2 | 295呎 (1房)
 $738万
 $25,008/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -62008,7 +62008,7 @@
           <t>A3 | 299呎 (1房)
 $741万
 $24,784/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -62016,7 +62016,7 @@
           <t>A5 | 299呎 (1房)
 $741万
 $24,784/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -62024,7 +62024,7 @@
           <t>A6 | 297呎 (1房)
 $741万
 $24,945/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -62032,7 +62032,7 @@
           <t>A8 | 508呎 (2房)
 $1085万
 $21,360/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr"/>
@@ -62041,7 +62041,7 @@
           <t>B1 | 454呎 (2房)
 $958万
 $21,111/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -62049,7 +62049,7 @@
           <t>B2 | 299呎 (1房)
 $642万
 $21,478/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -62057,7 +62057,7 @@
           <t>B3 | 296呎 (1房)
 $637万
 $21,511/呎
-(24年-10月)</t>
+(24年-10月-21日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -62065,7 +62065,7 @@
           <t>B5 | 240呎 (开放式)
 $538万
 $22,421/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -62073,7 +62073,7 @@
           <t>B6 | 236呎 (开放式)
 $536万
 $22,691/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="O25" s="22" t="inlineStr">
@@ -62081,7 +62081,7 @@
           <t>B8 | 460呎 (2房)
 $924万
 $20,081/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr"/>
@@ -62106,7 +62106,7 @@
           <t>A1 | 501呎 (2房)
 $1230万
 $24,547/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -62114,7 +62114,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,959/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -62122,7 +62122,7 @@
           <t>A3 | 299呎 (1房)
 $740万
 $24,734/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -62130,7 +62130,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,734/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -62138,7 +62138,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,861/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -62146,7 +62146,7 @@
           <t>A8 | 509呎 (2房)
 $1084万
 $21,295/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr"/>
@@ -62155,7 +62155,7 @@
           <t>B1 | 454呎 (2房)
 $957万
 $21,069/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -62163,7 +62163,7 @@
           <t>B2 | 299呎 (1房)
 $642万
 $21,468/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -62171,7 +62171,7 @@
           <t>B3 | 296呎 (1房)
 $634万
 $21,434/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -62179,7 +62179,7 @@
           <t>B5 | 240呎 (开放式)
 $556万
 $23,165/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -62187,7 +62187,7 @@
           <t>B6 | 236呎 (开放式)
 $534万
 $22,645/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="O26" s="22" t="inlineStr">
@@ -62195,7 +62195,7 @@
           <t>B8 | 460呎 (2房)
 $887万
 $19,282/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="P26" s="20" t="inlineStr"/>
@@ -62220,7 +62220,7 @@
           <t>A1 | 501呎 (2房)
 $1227万
 $24,498/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -62228,7 +62228,7 @@
           <t>A2 | 295呎 (1房)
 $735万
 $24,909/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -62236,7 +62236,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,685/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -62244,7 +62244,7 @@
           <t>A5 | 299呎 (1房)
 $738万
 $24,685/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -62252,7 +62252,7 @@
           <t>A6 | 297呎 (1房)
 $738万
 $24,845/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -62260,7 +62260,7 @@
           <t>A8 | 509呎 (2房)
 $1082万
 $21,253/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr"/>
@@ -62269,7 +62269,7 @@
           <t>B1 | 454呎 (2房)
 $955万
 $21,027/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -62277,7 +62277,7 @@
           <t>B2 | 299呎 (1房)
 $641万
 $21,425/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -62285,7 +62285,7 @@
           <t>B3 | 296呎 (1房)
 $633万
 $21,392/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -62293,7 +62293,7 @@
           <t>B5 | 240呎 (开放式)
 $537万
 $22,373/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -62301,7 +62301,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,600/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O27" s="22" t="inlineStr">
@@ -62309,7 +62309,7 @@
           <t>B8 | 460呎 (2房)
 $921万
 $20,023/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="P27" s="20" t="inlineStr"/>
@@ -62334,7 +62334,7 @@
           <t>A1 | 501呎 (2房)
 $1225万
 $24,449/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -62342,7 +62342,7 @@
           <t>A2 | 295呎 (1房)
 $733万
 $24,859/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -62350,7 +62350,7 @@
           <t>A3 | 299呎 (1房)
 $737万
 $24,636/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -62358,7 +62358,7 @@
           <t>A5 | 299呎 (1房)
 $737万
 $24,636/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -62366,7 +62366,7 @@
           <t>A6 | 297呎 (1房)
 $708万
 $23,831/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -62374,7 +62374,7 @@
           <t>A8 | 509呎 (2房)
 $1080万
 $21,210/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr"/>
@@ -62383,7 +62383,7 @@
           <t>B1 | 454呎 (2房)
 $953万
 $20,985/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -62391,7 +62391,7 @@
           <t>B2 | 299呎 (1房)
 $639万
 $21,383/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -62399,7 +62399,7 @@
           <t>B3 | 296呎 (1房)
 $632万
 $21,349/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -62407,7 +62407,7 @@
           <t>B5 | 240呎 (开放式)
 $536万
 $22,328/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -62415,7 +62415,7 @@
           <t>B6 | 236呎 (开放式)
 $532万
 $22,555/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="O28" s="22" t="inlineStr">
@@ -62423,7 +62423,7 @@
           <t>B8 | 460呎 (2房)
 $919万
 $19,983/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P28" s="20" t="inlineStr"/>
@@ -62448,7 +62448,7 @@
           <t>A1 | 501呎 (2房)
 $1222万
 $24,400/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -62456,7 +62456,7 @@
           <t>A2 | 295呎 (1房)
 $732万
 $24,809/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -62464,7 +62464,7 @@
           <t>A3 | 298呎 (1房)
 $735万
 $24,669/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -62472,7 +62472,7 @@
           <t>A5 | 299呎 (1房)
 $735万
 $24,586/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -62480,7 +62480,7 @@
           <t>A6 | 297呎 (1房)
 $735万
 $24,746/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -62488,7 +62488,7 @@
           <t>A8 | 509呎 (2房)
 $1077万
 $21,168/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr"/>
@@ -62497,7 +62497,7 @@
           <t>B1 | 454呎 (2房)
 $951万
 $20,943/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -62505,7 +62505,7 @@
           <t>B2 | 299呎 (1房)
 $659万
 $22,051/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -62513,7 +62513,7 @@
           <t>B3 | 296呎 (1房)
 $632万
 $21,340/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -62521,7 +62521,7 @@
           <t>B5 | 240呎 (开放式)
 $535万
 $22,283/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N29" s="22" t="inlineStr">
@@ -62529,7 +62529,7 @@
           <t>B6 | 236呎 (开放式)
 $531万
 $22,510/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="O29" s="22" t="inlineStr">
@@ -62537,7 +62537,7 @@
           <t>B8 | 460呎 (2房)
 $917万
 $19,943/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P29" s="20" t="inlineStr"/>
@@ -62562,7 +62562,7 @@
           <t>A1 | 501呎 (2房)
 $1220万
 $24,351/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -62570,7 +62570,7 @@
           <t>A2 | 295呎 (1房)
 $730万
 $24,760/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -62578,7 +62578,7 @@
           <t>A3 | 299呎 (1房)
 $734万
 $24,537/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -62586,7 +62586,7 @@
           <t>A5 | 299呎 (1房)
 $734万
 $24,537/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -62594,7 +62594,7 @@
           <t>A6 | 297呎 (1房)
 $733万
 $24,696/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -62602,7 +62602,7 @@
           <t>A8 | 509呎 (2房)
 $1075万
 $21,126/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr"/>
@@ -62611,7 +62611,7 @@
           <t>B1 | 454呎 (2房)
 $949万
 $20,902/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -62619,7 +62619,7 @@
           <t>B2 | 299呎 (1房)
 $637万
 $21,297/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -62627,7 +62627,7 @@
           <t>B3 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -62635,7 +62635,7 @@
           <t>B5 | 240呎 (开放式)
 $534万
 $22,239/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
@@ -62643,7 +62643,7 @@
           <t>B6 | 236呎 (开放式)
 $530万
 $22,465/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="O30" s="22" t="inlineStr">
@@ -62651,7 +62651,7 @@
           <t>B8 | 460呎 (2房)
 $916万
 $19,903/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="P30" s="20" t="inlineStr"/>
@@ -62676,7 +62676,7 @@
           <t>A1 | 501呎 (2房)
 $1141万
 $22,779/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -62684,7 +62684,7 @@
           <t>A2 | 295呎 (1房)
 $728万
 $24,685/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -62692,7 +62692,7 @@
           <t>A3 | 299呎 (1房)
 $731万
 $24,464/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -62700,7 +62700,7 @@
           <t>A5 | 299呎 (1房)
 $731万
 $24,464/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -62708,7 +62708,7 @@
           <t>A6 | 297呎 (1房)
 $731万
 $24,622/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -62716,7 +62716,7 @@
           <t>A8 | 509呎 (2房)
 $1072万
 $21,062/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr"/>
@@ -62725,7 +62725,7 @@
           <t>B1 | 454呎 (2房)
 $946万
 $20,839/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -62733,7 +62733,7 @@
           <t>B2 | 299呎 (1房)
 $635万
 $21,233/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -62741,7 +62741,7 @@
           <t>B3 | 296呎 (1房)
 $628万
 $21,233/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -62749,7 +62749,7 @@
           <t>B5 | 240呎 (开放式)
 $532万
 $22,172/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="N31" s="22" t="inlineStr">
@@ -62757,7 +62757,7 @@
           <t>B6 | 236呎 (开放式)
 $529万
 $22,397/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="O31" s="22" t="inlineStr">
@@ -62765,7 +62765,7 @@
           <t>B8 | 460呎 (2房)
 $913万
 $19,843/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="P31" s="20" t="inlineStr"/>
@@ -62790,7 +62790,7 @@
           <t>A1 | 501呎 (2房)
 $1138万
 $22,711/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -62798,7 +62798,7 @@
           <t>A2 | 295呎 (1房)
 $736万
 $24,963/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -62806,7 +62806,7 @@
           <t>A3 | 299呎 (1房)
 $739万
 $24,705/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -62814,7 +62814,7 @@
           <t>A5 | 299呎 (1房)
 $740万
 $24,739/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -62822,7 +62822,7 @@
           <t>A6 | 297呎 (1房)
 $740万
 $24,899/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -62830,7 +62830,7 @@
           <t>A8 | 509呎 (2房)
 $1069万
 $20,999/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr"/>
@@ -62839,7 +62839,7 @@
           <t>B1 | 454呎 (2房)
 $943万
 $20,776/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -62847,7 +62847,7 @@
           <t>B2 | 299呎 (1房)
 $633万
 $21,170/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -62855,7 +62855,7 @@
           <t>B3 | 296呎 (1房)
 $627万
 $21,170/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -62863,7 +62863,7 @@
           <t>B5 | 240呎 (开放式)
 $531万
 $22,106/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
@@ -62871,7 +62871,7 @@
           <t>B6 | 236呎 (开放式)
 $527万
 $22,330/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="O32" s="22" t="inlineStr">
@@ -62879,7 +62879,7 @@
           <t>B8 | 460呎 (2房)
 $910万
 $19,783/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P32" s="20" t="inlineStr"/>
@@ -62904,7 +62904,7 @@
           <t>A1 | 501呎 (2房)
 $1134万
 $22,643/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -62912,7 +62912,7 @@
           <t>A2 | 295呎 (1房)
 $724万
 $24,538/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -62920,7 +62920,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,317/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -62936,7 +62936,7 @@
           <t>A6 | 297呎 (1房)
 $727万
 $24,475/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -62944,7 +62944,7 @@
           <t>A8 | 509呎 (2房)
 $1066万
 $20,936/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr"/>
@@ -62953,7 +62953,7 @@
           <t>B1 | 454呎 (2房)
 $940万
 $20,714/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -62961,7 +62961,7 @@
           <t>B2 | 299呎 (1房)
 $631万
 $21,106/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -62969,7 +62969,7 @@
           <t>B3 | 296呎 (1房)
 $625万
 $21,106/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -62977,7 +62977,7 @@
           <t>B5 | 240呎 (开放式)
 $529万
 $22,039/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="N33" s="22" t="inlineStr">
@@ -62985,7 +62985,7 @@
           <t>B6 | 236呎 (开放式)
 $525万
 $22,263/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="O33" s="22" t="inlineStr">
@@ -62993,7 +62993,7 @@
           <t>B8 | 460呎 (2房)
 $907万
 $19,724/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P33" s="20" t="inlineStr"/>
@@ -63018,7 +63018,7 @@
           <t>A1 | 501呎 (2房)
 $1127万
 $22,490/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -63026,7 +63026,7 @@
           <t>A2 | 295呎 (1房)
 $685万
 $23,214/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -63034,7 +63034,7 @@
           <t>A3 | 299呎 (1房)
 $688万
 $23,006/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -63042,7 +63042,7 @@
           <t>A5 | 299呎 (1房)
 $688万
 $23,006/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -63050,7 +63050,7 @@
           <t>A6 | 297呎 (1房)
 $688万
 $23,155/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
@@ -63058,7 +63058,7 @@
           <t>A8 | 509呎 (2房)
 $1058万
 $20,795/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr"/>
@@ -63067,7 +63067,7 @@
           <t>B1 | 454呎 (2房)
 $933万
 $20,556/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -63075,7 +63075,7 @@
           <t>B2 | 299呎 (1房)
 $602万
 $20,134/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -63083,7 +63083,7 @@
           <t>B3 | 296呎 (1房)
 $620万
 $20,949/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -63091,7 +63091,7 @@
           <t>B5 | 240呎 (开放式)
 $525万
 $21,881/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="N34" s="22" t="inlineStr">
@@ -63099,7 +63099,7 @@
           <t>B6 | 236呎 (开放式)
 $522万
 $22,104/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O34" s="22" t="inlineStr">
@@ -63107,7 +63107,7 @@
           <t>B8 | 460呎 (2房)
 $900万
 $19,574/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="P34" s="20" t="inlineStr"/>
@@ -63132,7 +63132,7 @@
           <t>A1 | 501呎 (2房)
 $1118万
 $22,321/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -63140,7 +63140,7 @@
           <t>A2 | 295呎 (1房)
 $680万
 $23,043/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -63148,7 +63148,7 @@
           <t>A3 | 299呎 (1房)
 $683万
 $22,837/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -63156,7 +63156,7 @@
           <t>A5 | 299呎 (1房)
 $683万
 $22,837/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -63164,7 +63164,7 @@
           <t>A6 | 297呎 (1房)
 $683万
 $22,985/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -63172,7 +63172,7 @@
           <t>A8 | 509呎 (2房)
 $1050万
 $20,639/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr"/>
@@ -63181,7 +63181,7 @@
           <t>B1 | 454呎 (2房)
 $925万
 $20,366/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -63189,7 +63189,7 @@
           <t>B2 | 299呎 (1房)
 $621万
 $20,760/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -63197,7 +63197,7 @@
           <t>B3 | 296呎 (1房)
 $614万
 $20,759/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -63205,7 +63205,7 @@
           <t>B5 | 240呎 (开放式)
 $521万
 $21,696/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="N35" s="22" t="inlineStr">
@@ -63213,7 +63213,7 @@
           <t>B6 | 236呎 (开放式)
 $517万
 $21,920/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="O35" s="22" t="inlineStr">
@@ -63221,7 +63221,7 @@
           <t>B8 | 460呎 (2房)
 $857万
 $18,638/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="P35" s="20" t="inlineStr"/>
@@ -63246,7 +63246,7 @@
           <t>A1 | 501呎 (2房)
 $1074万
 $21,428/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -63254,7 +63254,7 @@
           <t>A2 | 295呎 (1房)
 $653万
 $22,122/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -63262,7 +63262,7 @@
           <t>A3 | 299呎 (1房)
 $656万
 $21,923/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -63270,7 +63270,7 @@
           <t>A5 | 299呎 (1房)
 $656万
 $21,923/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -63278,7 +63278,7 @@
           <t>A6 | 297呎 (1房)
 $655万
 $22,065/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -63286,7 +63286,7 @@
           <t>A8 | 509呎 (2房)
 $1008万
 $19,813/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="I36" s="20" t="inlineStr"/>
@@ -63295,7 +63295,7 @@
           <t>B1 | 454呎 (2房)
 $912万
 $20,080/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -63303,7 +63303,7 @@
           <t>B2 | 299呎 (1房)
 $613万
 $20,489/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -63311,7 +63311,7 @@
           <t>B3 | 296呎 (1房)
 $606万
 $20,476/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -63319,7 +63319,7 @@
           <t>B5 | 240呎 (开放式)
 $514万
 $21,408/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="N36" s="22" t="inlineStr">
@@ -63327,7 +63327,7 @@
           <t>B6 | 236呎 (开放式)
 $511万
 $21,643/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="O36" s="22" t="inlineStr">
@@ -63335,7 +63335,7 @@
           <t>B8 | 460呎 (2房)
 $910万
 $19,792/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="P36" s="20" t="inlineStr"/>
@@ -63360,7 +63360,7 @@
           <t>A1 | 501呎 (2房)
 $919万
 $18,336/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -63368,7 +63368,7 @@
           <t>A2 | 295呎 (1房)
 $574万
 $19,467/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -63376,7 +63376,7 @@
           <t>A3 | 299呎 (1房)
 $577万
 $19,292/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -63384,7 +63384,7 @@
           <t>A5 | 298呎 (1房)
 $577万
 $19,357/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -63392,7 +63392,7 @@
           <t>A6 | 297呎 (1房)
 $577万
 $19,418/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -63400,7 +63400,7 @@
           <t>A8 | 509呎 (2房)
 $901万
 $17,703/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="I37" s="20" t="inlineStr"/>
@@ -63409,7 +63409,7 @@
           <t>B1 | 454呎 (2房)
 $880万
 $19,377/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -63417,7 +63417,7 @@
           <t>B2 | 299呎 (1房)
 $591万
 $19,772/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -63425,7 +63425,7 @@
           <t>B3 | 296呎 (1房)
 $585万
 $19,759/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -63433,7 +63433,7 @@
           <t>B5 | 240呎 (开放式)
 $496万
 $20,658/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="N37" s="22" t="inlineStr">
@@ -63441,7 +63441,7 @@
           <t>B6 | 236呎 (开放式)
 $493万
 $20,885/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="O37" s="22" t="inlineStr">
@@ -63449,7 +63449,7 @@
           <t>B8 | 460呎 (2房)
 $850万
 $18,483/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="P37" s="20" t="inlineStr"/>
@@ -63783,7 +63783,7 @@
           <t>SSV B | 1622呎 (4+房)
 $5915万
 $36,465/呎
-(25年-01月)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -63798,7 +63798,7 @@
           <t>A | 909呎 (4+房)
 $3219万
 $35,417/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr"/>
@@ -63811,7 +63811,7 @@
           <t>B | 672呎 (3房)
 $2000万
 $29,764/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr"/>
@@ -63825,7 +63825,7 @@
           <t>C | 907呎 (4+房)
 $2928万
 $32,283/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="P7" s="22" t="inlineStr">
@@ -63833,7 +63833,7 @@
           <t>D | 445呎 (2房)
 $1008万
 $22,661/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="Q7" s="22" t="inlineStr">
@@ -63841,7 +63841,7 @@
           <t>E | 469呎 (2房)
 $1018万
 $21,709/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="R7" s="22" t="inlineStr">
@@ -63849,7 +63849,7 @@
           <t>F | 460呎 (2房)
 $1005万
 $21,851/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="S7" s="22" t="inlineStr">
@@ -63857,7 +63857,7 @@
           <t>G | 454呎 (2房)
 $962万
 $21,199/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="T7" s="22" t="inlineStr">
@@ -63865,7 +63865,7 @@
           <t>H | 692呎 (2房)
 $1554万
 $22,449/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="U7" s="20" t="inlineStr"/>
@@ -63884,7 +63884,7 @@
           <t>A | 909呎 (4+房)
 $3126万
 $34,391/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr"/>
@@ -63897,7 +63897,7 @@
           <t>B | 672呎 (3房)
 $1994万
 $29,675/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr"/>
@@ -63911,7 +63911,7 @@
           <t>C | 907呎 (4+房)
 $2777万
 $30,620/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="P8" s="22" t="inlineStr">
@@ -63919,7 +63919,7 @@
           <t>D | 445呎 (2房)
 $1005万
 $22,593/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="Q8" s="22" t="inlineStr">
@@ -63927,7 +63927,7 @@
           <t>E | 469呎 (2房)
 $1015万
 $21,644/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="R8" s="22" t="inlineStr">
@@ -63935,7 +63935,7 @@
           <t>F | 460呎 (2房)
 $1002万
 $21,785/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="S8" s="22" t="inlineStr">
@@ -63943,7 +63943,7 @@
           <t>G | 454呎 (2房)
 $960万
 $21,136/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="T8" s="22" t="inlineStr">
@@ -63951,7 +63951,7 @@
           <t>H | 692呎 (2房)
 $1549万
 $22,382/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="U8" s="20" t="inlineStr"/>
@@ -63970,7 +63970,7 @@
           <t>A | 909呎 (4+房)
 $3114万
 $34,255/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr"/>
@@ -63983,7 +63983,7 @@
           <t>B | 672呎 (3房)
 $1984万
 $29,528/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr"/>
@@ -63997,7 +63997,7 @@
           <t>C | 907呎 (4+房)
 $2780万
 $30,650/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="P9" s="22" t="inlineStr">
@@ -64005,7 +64005,7 @@
           <t>D | 445呎 (2房)
 $995万
 $22,369/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="Q9" s="22" t="inlineStr">
@@ -64013,7 +64013,7 @@
           <t>E | 469呎 (2房)
 $1012万
 $21,579/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="R9" s="22" t="inlineStr">
@@ -64021,7 +64021,7 @@
           <t>F | 460呎 (2房)
 $999万
 $21,720/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="S9" s="22" t="inlineStr">
@@ -64029,7 +64029,7 @@
           <t>G | 454呎 (2房)
 $995万
 $21,925/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="T9" s="22" t="inlineStr">
@@ -64037,7 +64037,7 @@
           <t>H | 692呎 (2房)
 $1541万
 $22,271/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="U9" s="20" t="inlineStr"/>
@@ -64056,7 +64056,7 @@
           <t>A | 909呎 (4+房)
 $3032万
 $33,361/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr"/>
@@ -64069,7 +64069,7 @@
           <t>B | 672呎 (3房)
 $1974万
 $29,380/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr"/>
@@ -64083,7 +64083,7 @@
           <t>C | 907呎 (4+房)
 $2759万
 $30,419/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="P10" s="22" t="inlineStr">
@@ -64091,7 +64091,7 @@
           <t>D | 445呎 (2房)
 $990万
 $22,258/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="Q10" s="22" t="inlineStr">
@@ -64099,7 +64099,7 @@
           <t>E | 469呎 (2房)
 $1010万
 $21,525/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="R10" s="22" t="inlineStr">
@@ -64107,7 +64107,7 @@
           <t>F | 460呎 (2房)
 $997万
 $21,666/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="S10" s="22" t="inlineStr">
@@ -64115,7 +64115,7 @@
           <t>G | 454呎 (2房)
 $993万
 $21,870/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="T10" s="22" t="inlineStr">
@@ -64123,7 +64123,7 @@
           <t>H | 692呎 (2房)
 $1533万
 $22,160/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="U10" s="20" t="inlineStr"/>
@@ -64142,7 +64142,7 @@
           <t>A | 909呎 (4+房)
 $3091万
 $34,000/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr"/>
@@ -64155,7 +64155,7 @@
           <t>B | 672呎 (3房)
 $1964万
 $29,233/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr"/>
@@ -64169,7 +64169,7 @@
           <t>C | 907呎 (4+房)
 $2872万
 $31,667/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
       <c r="P11" s="22" t="inlineStr">
@@ -64177,7 +64177,7 @@
           <t>D | 445呎 (2房)
 $981万
 $22,037/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="Q11" s="22" t="inlineStr">
@@ -64185,7 +64185,7 @@
           <t>E | 469呎 (2房)
 $994万
 $21,191/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="R11" s="22" t="inlineStr">
@@ -64193,7 +64193,7 @@
           <t>F | 460呎 (2房)
 $1013万
 $22,020/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="S11" s="22" t="inlineStr">
@@ -64201,7 +64201,7 @@
           <t>G | 454呎 (2房)
 $1009万
 $22,224/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="T11" s="22" t="inlineStr">
@@ -64209,7 +64209,7 @@
           <t>H | 692呎 (2房)
 $1526万
 $22,049/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="U11" s="20" t="inlineStr"/>
@@ -64228,7 +64228,7 @@
           <t>A | 909呎 (4+房)
 $2909万
 $32,000/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr"/>
@@ -64241,7 +64241,7 @@
           <t>B | 672呎 (3房)
 $1955万
 $29,087/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr"/>
@@ -64255,7 +64255,7 @@
           <t>C | 907呎 (4+房)
 $2739万
 $30,200/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="P12" s="22" t="inlineStr">
@@ -64263,7 +64263,7 @@
           <t>D | 445呎 (2房)
 $976万
 $21,927/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="Q12" s="22" t="inlineStr">
@@ -64271,7 +64271,7 @@
           <t>E | 469呎 (2房)
 $1031万
 $21,993/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="R12" s="22" t="inlineStr">
@@ -64279,7 +64279,7 @@
           <t>F | 460呎 (2房)
 $1010万
 $21,965/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="S12" s="22" t="inlineStr">
@@ -64287,7 +64287,7 @@
           <t>G | 454呎 (2房)
 $1006万
 $22,168/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="T12" s="22" t="inlineStr">
@@ -64295,7 +64295,7 @@
           <t>H | 692呎 (2房)
 $1518万
 $21,938/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="U12" s="20" t="inlineStr"/>
@@ -64314,7 +64314,7 @@
           <t>A | 909呎 (4+房)
 $3050万
 $33,552/呎
-(24年-12月)</t>
+(24年-12月-08日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr"/>
@@ -64327,7 +64327,7 @@
           <t>B | 672呎 (3房)
 $1945万
 $28,942/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr"/>
@@ -64341,7 +64341,7 @@
           <t>C | 907呎 (4+房)
 $2892万
 $31,886/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="P13" s="22" t="inlineStr">
@@ -64349,7 +64349,7 @@
           <t>D | 445呎 (2房)
 $971万
 $21,817/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="Q13" s="22" t="inlineStr">
@@ -64357,7 +64357,7 @@
           <t>E | 469呎 (2房)
 $1063万
 $22,670/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="R13" s="22" t="inlineStr">
@@ -64365,7 +64365,7 @@
           <t>F | 460呎 (2房)
 $1008万
 $21,910/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="S13" s="22" t="inlineStr">
@@ -64373,7 +64373,7 @@
           <t>G | 454呎 (2房)
 $1004万
 $22,113/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="T13" s="22" t="inlineStr">
@@ -64381,7 +64381,7 @@
           <t>H | 692呎 (2房)
 $1511万
 $21,829/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="U13" s="20" t="inlineStr"/>
@@ -64413,7 +64413,7 @@
           <t>B | 672呎 (3房)
 $1935万
 $28,797/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr"/>
@@ -64427,7 +64427,7 @@
           <t>C | 907呎 (4+房)
 $2902万
 $31,990/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="P14" s="22" t="inlineStr">
@@ -64435,7 +64435,7 @@
           <t>D | 445呎 (2房)
 $1100万
 $24,719/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="Q14" s="22" t="inlineStr">
@@ -64443,7 +64443,7 @@
           <t>E | 469呎 (2房)
 $1030万
 $21,966/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="R14" s="22" t="inlineStr">
@@ -64451,7 +64451,7 @@
           <t>F | 460呎 (2房)
 $1280万
 $27,826/呎
-(24年-11月)</t>
+(24年-11月-26日)</t>
         </is>
       </c>
       <c r="S14" s="22" t="inlineStr">
@@ -64459,7 +64459,7 @@
           <t>G | 454呎 (2房)
 $1147万
 $25,258/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="T14" s="22" t="inlineStr">
@@ -64467,7 +64467,7 @@
           <t>H | 692呎 (2房)
 $1735万
 $25,068/呎
-(24年-11月)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="U14" s="20" t="inlineStr"/>
@@ -64487,7 +64487,7 @@
           <t>A1 | 497呎 (2房)
 $1330万
 $26,763/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -64495,7 +64495,7 @@
           <t>A2 | 298呎 (1房)
 $753万
 $25,266/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -64503,7 +64503,7 @@
           <t>A3 | 299呎 (1房)
 $773万
 $25,866/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -64511,7 +64511,7 @@
           <t>A5 | 300呎 (1房)
 $790万
 $26,332/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -64519,7 +64519,7 @@
           <t>A6 | 469呎 (2房)
 $1307万
 $27,868/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr"/>
@@ -64528,7 +64528,7 @@
           <t>B1 | 467呎 (2房)
 $964万
 $20,633/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="J15" s="22" t="inlineStr">
@@ -64536,7 +64536,7 @@
           <t>B2 | 296呎 (1房)
 $688万
 $23,227/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -64544,7 +64544,7 @@
           <t>B3 | 296呎 (1房)
 $687万
 $23,193/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L15" s="22" t="inlineStr">
@@ -64552,7 +64552,7 @@
           <t>B5 | 240呎 (开放式)
 $573万
 $23,863/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M15" s="22" t="inlineStr">
@@ -64560,7 +64560,7 @@
           <t>B6 | 236呎 (开放式)
 $566万
 $23,997/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="N15" s="22" t="inlineStr">
@@ -64568,7 +64568,7 @@
           <t>B8 | 477呎 (2房)
 $1014万
 $21,262/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr"/>
@@ -64594,7 +64594,7 @@
           <t>A1 | 497呎 (2房)
 $1309万
 $26,347/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -64602,7 +64602,7 @@
           <t>A2 | 298呎 (1房)
 $746万
 $25,018/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -64610,7 +64610,7 @@
           <t>A3 | 299呎 (1房)
 $766万
 $25,610/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -64618,7 +64618,7 @@
           <t>A5 | 300呎 (1房)
 $782万
 $26,071/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -64626,7 +64626,7 @@
           <t>A6 | 469呎 (2房)
 $1288万
 $27,457/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr"/>
@@ -64635,7 +64635,7 @@
           <t>B1 | 467呎 (2房)
 $958万
 $20,510/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
@@ -64643,7 +64643,7 @@
           <t>B2 | 296呎 (1房)
 $685万
 $23,135/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
@@ -64651,7 +64651,7 @@
           <t>B3 | 296呎 (1房)
 $684万
 $23,101/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L16" s="22" t="inlineStr">
@@ -64659,7 +64659,7 @@
           <t>B5 | 240呎 (开放式)
 $568万
 $23,678/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M16" s="22" t="inlineStr">
@@ -64667,7 +64667,7 @@
           <t>B6 | 236呎 (开放式)
 $562万
 $23,808/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="N16" s="22" t="inlineStr">
@@ -64675,7 +64675,7 @@
           <t>B8 | 477呎 (2房)
 $1008万
 $21,136/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr"/>
@@ -64701,7 +64701,7 @@
           <t>A1 | 497呎 (2房)
 $1297万
 $26,093/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -64709,7 +64709,7 @@
           <t>A2 | 298呎 (1房)
 $744万
 $24,966/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -64717,7 +64717,7 @@
           <t>A3 | 299呎 (1房)
 $753万
 $25,187/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -64725,7 +64725,7 @@
           <t>A5 | 300呎 (1房)
 $769万
 $25,641/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -64733,7 +64733,7 @@
           <t>A6 | 469呎 (2房)
 $1275万
 $27,184/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr"/>
@@ -64742,7 +64742,7 @@
           <t>B1 | 467呎 (2房)
 $954万
 $20,428/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="J17" s="22" t="inlineStr">
@@ -64750,7 +64750,7 @@
           <t>B2 | 296呎 (1房)
 $683万
 $23,089/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K17" s="22" t="inlineStr">
@@ -64758,7 +64758,7 @@
           <t>B3 | 296呎 (1房)
 $683万
 $23,089/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L17" s="22" t="inlineStr">
@@ -64766,7 +64766,7 @@
           <t>B5 | 240呎 (开放式)
 $565万
 $23,539/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -64774,7 +64774,7 @@
           <t>B6 | 236呎 (开放式)
 $559万
 $23,669/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="N17" s="22" t="inlineStr">
@@ -64782,7 +64782,7 @@
           <t>B8 | 477呎 (2房)
 $1004万
 $21,052/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr"/>
@@ -64808,7 +64808,7 @@
           <t>A1 | 497呎 (2房)
 $1286万
 $25,883/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -64816,7 +64816,7 @@
           <t>A2 | 298呎 (1房)
 $743万
 $24,932/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -64824,7 +64824,7 @@
           <t>A3 | 299呎 (1房)
 $749万
 $25,036/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -64832,7 +64832,7 @@
           <t>A5 | 300呎 (1房)
 $765万
 $25,488/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -64840,7 +64840,7 @@
           <t>A6 | 469呎 (2房)
 $1323万
 $28,210/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr"/>
@@ -64849,7 +64849,7 @@
           <t>B1 | 467呎 (2房)
 $950万
 $20,347/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="J18" s="22" t="inlineStr">
@@ -64857,7 +64857,7 @@
           <t>B2 | 296呎 (1房)
 $682万
 $23,043/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K18" s="22" t="inlineStr">
@@ -64865,7 +64865,7 @@
           <t>B3 | 296呎 (1房)
 $682万
 $23,043/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="L18" s="22" t="inlineStr">
@@ -64873,7 +64873,7 @@
           <t>B5 | 240呎 (开放式)
 $562万
 $23,400/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M18" s="22" t="inlineStr">
@@ -64881,7 +64881,7 @@
           <t>B6 | 236呎 (开放式)
 $555万
 $23,530/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="N18" s="22" t="inlineStr">
@@ -64889,7 +64889,7 @@
           <t>B8 | 477呎 (2房)
 $1000万
 $20,968/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr"/>
@@ -64915,7 +64915,7 @@
           <t>A1 | 497呎 (2房)
 $1277万
 $25,688/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -64923,7 +64923,7 @@
           <t>A2 | 298呎 (1房)
 $767万
 $25,738/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -64931,7 +64931,7 @@
           <t>A3 | 299呎 (1房)
 $743万
 $24,849/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -64939,7 +64939,7 @@
           <t>A5 | 300呎 (1房)
 $759万
 $25,297/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -64947,7 +64947,7 @@
           <t>A6 | 469呎 (2房)
 $1313万
 $27,997/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr"/>
@@ -64956,7 +64956,7 @@
           <t>B1 | 467呎 (2房)
 $946万
 $20,266/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J19" s="22" t="inlineStr">
@@ -64964,7 +64964,7 @@
           <t>B2 | 296呎 (1房)
 $681万
 $22,996/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K19" s="22" t="inlineStr">
@@ -64972,7 +64972,7 @@
           <t>B3 | 296呎 (1房)
 $681万
 $22,996/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="L19" s="22" t="inlineStr">
@@ -64980,7 +64980,7 @@
           <t>B5 | 240呎 (开放式)
 $551万
 $22,974/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -64988,7 +64988,7 @@
           <t>B6 | 236呎 (开放式)
 $548万
 $23,208/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="N19" s="22" t="inlineStr">
@@ -64996,7 +64996,7 @@
           <t>B8 | 477呎 (2房)
 $996万
 $20,884/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr"/>
@@ -65022,7 +65022,7 @@
           <t>A1 | 497呎 (2房)
 $1319万
 $26,535/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -65030,7 +65030,7 @@
           <t>A2 | 298呎 (1房)
 $766万
 $25,699/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -65038,7 +65038,7 @@
           <t>A3 | 299呎 (1房)
 $740万
 $24,751/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -65046,7 +65046,7 @@
           <t>A5 | 300呎 (1房)
 $756万
 $25,197/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -65054,7 +65054,7 @@
           <t>A6 | 469呎 (2房)
 $1308万
 $27,886/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr"/>
@@ -65063,7 +65063,7 @@
           <t>B1 | 467呎 (2房)
 $943万
 $20,185/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="J20" s="22" t="inlineStr">
@@ -65071,7 +65071,7 @@
           <t>B2 | 296呎 (1房)
 $678万
 $22,905/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K20" s="22" t="inlineStr">
@@ -65079,7 +65079,7 @@
           <t>B3 | 296呎 (1房)
 $678万
 $22,905/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L20" s="22" t="inlineStr">
@@ -65087,7 +65087,7 @@
           <t>B5 | 240呎 (开放式)
 $549万
 $22,883/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -65095,7 +65095,7 @@
           <t>B6 | 236呎 (开放式)
 $546万
 $23,116/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="N20" s="22" t="inlineStr">
@@ -65103,7 +65103,7 @@
           <t>B8 | 477呎 (2房)
 $954万
 $19,992/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr"/>
@@ -65129,7 +65129,7 @@
           <t>A1 | 497呎 (2房)
 $1315万
 $26,456/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -65137,7 +65137,7 @@
           <t>A2 | 298呎 (1房)
 $761万
 $25,535/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -65145,7 +65145,7 @@
           <t>A3 | 299呎 (1房)
 $738万
 $24,676/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -65153,7 +65153,7 @@
           <t>A5 | 300呎 (1房)
 $754万
 $25,121/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -65161,7 +65161,7 @@
           <t>A6 | 469呎 (2房)
 $1280万
 $27,297/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr"/>
@@ -65170,7 +65170,7 @@
           <t>B1 | 467呎 (2房)
 $940万
 $20,124/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J21" s="22" t="inlineStr">
@@ -65178,7 +65178,7 @@
           <t>B2 | 296呎 (1房)
 $676万
 $22,836/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="K21" s="22" t="inlineStr">
@@ -65186,7 +65186,7 @@
           <t>B3 | 296呎 (1房)
 $676万
 $22,836/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L21" s="22" t="inlineStr">
@@ -65194,7 +65194,7 @@
           <t>B5 | 240呎 (开放式)
 $548万
 $22,815/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -65202,7 +65202,7 @@
           <t>B6 | 236呎 (开放式)
 $544万
 $23,047/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N21" s="22" t="inlineStr">
@@ -65210,7 +65210,7 @@
           <t>B8 | 477呎 (2房)
 $989万
 $20,739/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr"/>
@@ -65236,7 +65236,7 @@
           <t>A1 | 497呎 (2房)
 $1311万
 $26,376/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -65244,7 +65244,7 @@
           <t>A2 | 298呎 (1房)
 $759万
 $25,459/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -65252,7 +65252,7 @@
           <t>A3 | 299呎 (1房)
 $707万
 $23,646/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -65260,7 +65260,7 @@
           <t>A5 | 300呎 (1房)
 $751万
 $25,046/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -65268,7 +65268,7 @@
           <t>A6 | 469呎 (2房)
 $1253万
 $26,711/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr"/>
@@ -65277,7 +65277,7 @@
           <t>B1 | 467呎 (2房)
 $937万
 $20,064/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -65285,7 +65285,7 @@
           <t>B2 | 296呎 (1房)
 $673万
 $22,734/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -65293,7 +65293,7 @@
           <t>B3 | 296呎 (1房)
 $674万
 $22,768/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -65301,7 +65301,7 @@
           <t>B5 | 240呎 (开放式)
 $546万
 $22,747/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -65309,7 +65309,7 @@
           <t>B6 | 236呎 (开放式)
 $542万
 $22,978/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N22" s="22" t="inlineStr">
@@ -65317,7 +65317,7 @@
           <t>B8 | 477呎 (2房)
 $986万
 $20,677/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr"/>
@@ -65343,7 +65343,7 @@
           <t>A1 | 497呎 (2房)
 $1307万
 $26,297/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -65351,7 +65351,7 @@
           <t>A2 | 298呎 (1房)
 $755万
 $25,349/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -65359,7 +65359,7 @@
           <t>A3 | 299呎 (1房)
 $733万
 $24,529/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -65367,7 +65367,7 @@
           <t>A5 | 300呎 (1房)
 $749万
 $24,971/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -65375,7 +65375,7 @@
           <t>A6 | 469呎 (2房)
 $1132万
 $24,147/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr"/>
@@ -65384,7 +65384,7 @@
           <t>B1 | 467呎 (2房)
 $934万
 $20,004/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -65392,7 +65392,7 @@
           <t>B2 | 296呎 (1房)
 $671万
 $22,666/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -65400,7 +65400,7 @@
           <t>B3 | 296呎 (1房)
 $672万
 $22,700/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -65408,7 +65408,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,638/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -65416,7 +65416,7 @@
           <t>B6 | 236呎 (开放式)
 $520万
 $22,019/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="N23" s="22" t="inlineStr">
@@ -65424,7 +65424,7 @@
           <t>B8 | 477呎 (2房)
 $983万
 $20,615/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr"/>
@@ -65450,7 +65450,7 @@
           <t>A1 | 497呎 (2房)
 $1303万
 $26,219/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -65458,7 +65458,7 @@
           <t>A2 | 298呎 (1房)
 $754万
 $25,306/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -65466,7 +65466,7 @@
           <t>A3 | 298呎 (1房)
 $731万
 $24,538/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -65474,7 +65474,7 @@
           <t>A5 | 300呎 (1房)
 $747万
 $24,896/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -65482,7 +65482,7 @@
           <t>A6 | 469呎 (2房)
 $1175万
 $25,049/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr"/>
@@ -65491,7 +65491,7 @@
           <t>B1 | 467呎 (2房)
 $931万
 $19,945/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -65499,7 +65499,7 @@
           <t>B2 | 296呎 (1房)
 $670万
 $22,632/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -65507,7 +65507,7 @@
           <t>B3 | 296呎 (1房)
 $670万
 $22,632/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -65515,7 +65515,7 @@
           <t>B5 | 240呎 (开放式)
 $543万
 $22,612/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -65523,7 +65523,7 @@
           <t>B6 | 236呎 (开放式)
 $539万
 $22,842/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="N24" s="22" t="inlineStr">
@@ -65531,7 +65531,7 @@
           <t>B8 | 477呎 (2房)
 $942万
 $19,754/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr"/>
@@ -65557,7 +65557,7 @@
           <t>A1 | 497呎 (2房)
 $1300万
 $26,167/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -65565,7 +65565,7 @@
           <t>A2 | 298呎 (1房)
 $753万
 $25,256/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -65573,7 +65573,7 @@
           <t>A3 | 299呎 (1房)
 $729万
 $24,374/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -65581,7 +65581,7 @@
           <t>A5 | 300呎 (1房)
 $744万
 $24,813/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -65589,7 +65589,7 @@
           <t>A6 | 469呎 (2房)
 $1172万
 $24,999/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr"/>
@@ -65598,7 +65598,7 @@
           <t>B1 | 467呎 (2房)
 $930万
 $19,904/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -65606,7 +65606,7 @@
           <t>B2 | 296呎 (1房)
 $669万
 $22,587/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -65614,7 +65614,7 @@
           <t>B3 | 296呎 (1房)
 $669万
 $22,587/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -65622,7 +65622,7 @@
           <t>B5 | 240呎 (开放式)
 $542万
 $22,567/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -65630,7 +65630,7 @@
           <t>B6 | 236呎 (开放式)
 $556万
 $23,556/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -65638,7 +65638,7 @@
           <t>B8 | 477呎 (2房)
 $978万
 $20,512/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr"/>
@@ -65664,7 +65664,7 @@
           <t>A1 | 497呎 (2房)
 $1298万
 $26,114/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -65672,7 +65672,7 @@
           <t>A2 | 298呎 (1房)
 $722万
 $24,226/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -65680,7 +65680,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,325/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -65688,7 +65688,7 @@
           <t>A5 | 300呎 (1房)
 $743万
 $24,764/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -65696,7 +65696,7 @@
           <t>A6 | 469呎 (2房)
 $1170万
 $24,949/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr"/>
@@ -65705,7 +65705,7 @@
           <t>B1 | 467呎 (2房)
 $928万
 $19,865/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -65713,7 +65713,7 @@
           <t>B2 | 296呎 (1房)
 $666万
 $22,508/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -65721,7 +65721,7 @@
           <t>B3 | 296呎 (1房)
 $667万
 $22,542/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -65729,7 +65729,7 @@
           <t>B5 | 240呎 (开放式)
 $541万
 $22,522/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -65737,7 +65737,7 @@
           <t>B6 | 237呎 (开放式)
 $537万
 $22,655/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N26" s="22" t="inlineStr">
@@ -65745,7 +65745,7 @@
           <t>B8 | 477呎 (2房)
 $976万
 $20,471/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="O26" s="20" t="inlineStr"/>
@@ -65771,7 +65771,7 @@
           <t>A1 | 497呎 (2房)
 $1245万
 $25,049/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -65779,7 +65779,7 @@
           <t>A2 | 298呎 (1房)
 $775万
 $25,994/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -65787,7 +65787,7 @@
           <t>A3 | 299呎 (1房)
 $727万
 $24,309/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -65795,7 +65795,7 @@
           <t>A5 | 300呎 (1房)
 $742万
 $24,747/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -65803,7 +65803,7 @@
           <t>A6 | 469呎 (2房)
 $1168万
 $24,899/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr"/>
@@ -65812,7 +65812,7 @@
           <t>B1 | 467呎 (2房)
 $926万
 $19,825/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -65820,7 +65820,7 @@
           <t>B2 | 296呎 (1房)
 $688万
 $23,247/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -65828,7 +65828,7 @@
           <t>B3 | 296呎 (1房)
 $666万
 $22,497/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -65836,7 +65836,7 @@
           <t>B5 | 240呎 (开放式)
 $539万
 $22,478/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -65844,7 +65844,7 @@
           <t>B6 | 236呎 (开放式)
 $554万
 $23,463/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N27" s="22" t="inlineStr">
@@ -65852,7 +65852,7 @@
           <t>B8 | 477呎 (2房)
 $975万
 $20,430/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O27" s="20" t="inlineStr"/>
@@ -65878,7 +65878,7 @@
           <t>A1 | 497呎 (2房)
 $1242万
 $24,999/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -65886,7 +65886,7 @@
           <t>A2 | 298呎 (1房)
 $748万
 $25,105/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -65894,7 +65894,7 @@
           <t>A3 | 299呎 (1房)
 $725万
 $24,261/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -65902,7 +65902,7 @@
           <t>A5 | 300呎 (1房)
 $740万
 $24,665/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -65910,7 +65910,7 @@
           <t>A6 | 469呎 (2房)
 $1165万
 $24,849/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr"/>
@@ -65919,7 +65919,7 @@
           <t>B1 | 467呎 (2房)
 $924万
 $19,785/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -65927,7 +65927,7 @@
           <t>B2 | 296呎 (1房)
 $665万
 $22,452/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -65935,7 +65935,7 @@
           <t>B3 | 296呎 (1房)
 $686万
 $23,167/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -65943,7 +65943,7 @@
           <t>B5 | 240呎 (开放式)
 $538万
 $22,432/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -65951,7 +65951,7 @@
           <t>B6 | 237呎 (开放式)
 $535万
 $22,565/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="N28" s="22" t="inlineStr">
@@ -65959,7 +65959,7 @@
           <t>B8 | 477呎 (2房)
 $973万
 $20,390/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O28" s="20" t="inlineStr"/>
@@ -65985,7 +65985,7 @@
           <t>A1 | 497呎 (2房)
 $1290万
 $25,958/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -65993,7 +65993,7 @@
           <t>A2 | 298呎 (1房)
 $754万
 $25,289/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -66001,7 +66001,7 @@
           <t>A3 | 299呎 (1房)
 $724万
 $24,212/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -66009,7 +66009,7 @@
           <t>A5 | 300呎 (1房)
 $739万
 $24,649/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -66017,7 +66017,7 @@
           <t>A6 | 469呎 (2房)
 $1163万
 $24,800/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr"/>
@@ -66026,7 +66026,7 @@
           <t>B1 | 467呎 (2房)
 $922万
 $19,746/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -66034,7 +66034,7 @@
           <t>B2 | 296呎 (1房)
 $672万
 $22,713/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -66042,7 +66042,7 @@
           <t>B3 | 296呎 (1房)
 $663万
 $22,407/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -66050,7 +66050,7 @@
           <t>B5 | 240呎 (开放式)
 $537万
 $22,388/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -66058,7 +66058,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,573/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N29" s="22" t="inlineStr">
@@ -66066,7 +66066,7 @@
           <t>B8 | 477呎 (2房)
 $971万
 $20,349/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="O29" s="20" t="inlineStr"/>
@@ -66092,7 +66092,7 @@
           <t>A1 | 497呎 (2房)
 $1214万
 $24,420/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -66100,7 +66100,7 @@
           <t>A2 | 298呎 (1房)
 $752万
 $25,239/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -66108,7 +66108,7 @@
           <t>A3 | 299呎 (1房)
 $723万
 $24,164/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -66116,7 +66116,7 @@
           <t>A5 | 300呎 (1房)
 $738万
 $24,599/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -66124,7 +66124,7 @@
           <t>A6 | 469呎 (2房)
 $1161万
 $24,750/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr"/>
@@ -66133,7 +66133,7 @@
           <t>B1 | 467呎 (2房)
 $920万
 $19,706/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -66141,7 +66141,7 @@
           <t>B2 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -66149,7 +66149,7 @@
           <t>B3 | 296呎 (1房)
 $630万
 $21,297/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -66157,7 +66157,7 @@
           <t>B5 | 240呎 (开放式)
 $536万
 $22,343/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -66165,7 +66165,7 @@
           <t>B6 | 236呎 (开放式)
 $533万
 $22,571/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="N30" s="22" t="inlineStr">
@@ -66173,7 +66173,7 @@
           <t>B8 | 477呎 (2房)
 $969万
 $20,308/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O30" s="20" t="inlineStr"/>
@@ -66199,7 +66199,7 @@
           <t>A1 | 497呎 (2房)
 $1210万
 $24,346/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -66207,7 +66207,7 @@
           <t>A2 | 298呎 (1房)
 $736万
 $24,697/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -66215,7 +66215,7 @@
           <t>A3 | 299呎 (1房)
 $720万
 $24,092/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -66223,7 +66223,7 @@
           <t>A5 | 300呎 (1房)
 $736万
 $24,525/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -66231,7 +66231,7 @@
           <t>A6 | 469呎 (2房)
 $1157万
 $24,676/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr"/>
@@ -66240,7 +66240,7 @@
           <t>B1 | 467呎 (2房)
 $948万
 $20,302/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -66248,7 +66248,7 @@
           <t>B2 | 296呎 (1房)
 $649万
 $21,941/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -66256,7 +66256,7 @@
           <t>B3 | 296呎 (1房)
 $628万
 $21,233/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -66264,7 +66264,7 @@
           <t>B5 | 240呎 (开放式)
 $535万
 $22,277/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -66272,7 +66272,7 @@
           <t>B6 | 236呎 (开放式)
 $531万
 $22,503/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="N31" s="22" t="inlineStr">
@@ -66280,7 +66280,7 @@
           <t>B8 | 477呎 (2房)
 $966万
 $20,247/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O31" s="20" t="inlineStr"/>
@@ -66306,7 +66306,7 @@
           <t>A1 | 497呎 (2房)
 $1164万
 $23,429/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -66314,7 +66314,7 @@
           <t>A2 | 298呎 (1房)
 $720万
 $24,158/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -66322,7 +66322,7 @@
           <t>A3 | 299呎 (1房)
 $718万
 $24,019/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -66330,7 +66330,7 @@
           <t>A5 | 300呎 (1房)
 $734万
 $24,452/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -66338,7 +66338,7 @@
           <t>A6 | 469呎 (2房)
 $1154万
 $24,601/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr"/>
@@ -66347,7 +66347,7 @@
           <t>B1 | 467呎 (2房)
 $945万
 $20,241/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -66355,7 +66355,7 @@
           <t>B2 | 296呎 (1房)
 $648万
 $21,875/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -66363,7 +66363,7 @@
           <t>B3 | 296呎 (1房)
 $627万
 $21,170/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -66371,7 +66371,7 @@
           <t>B5 | 240呎 (开放式)
 $533万
 $22,210/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -66379,7 +66379,7 @@
           <t>B6 | 236呎 (开放式)
 $529万
 $22,436/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="N32" s="22" t="inlineStr">
@@ -66387,7 +66387,7 @@
           <t>B8 | 477呎 (2房)
 $963万
 $20,186/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O32" s="20" t="inlineStr"/>
@@ -66413,7 +66413,7 @@
           <t>A1 | 497呎 (2房)
 $1161万
 $23,359/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -66421,7 +66421,7 @@
           <t>A2 | 298呎 (1房)
 $711万
 $23,854/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -66429,7 +66429,7 @@
           <t>A3 | 299呎 (1房)
 $716万
 $23,947/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -66437,7 +66437,7 @@
           <t>A5 | 300呎 (1房)
 $731万
 $24,379/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -66445,7 +66445,7 @@
           <t>A6 | 469呎 (2房)
 $1150万
 $24,528/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr"/>
@@ -66454,7 +66454,7 @@
           <t>B1 | 467呎 (2房)
 $912万
 $19,530/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -66462,7 +66462,7 @@
           <t>B2 | 296呎 (1房)
 $646万
 $21,809/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -66470,7 +66470,7 @@
           <t>B3 | 296呎 (1房)
 $624万
 $21,072/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -66478,7 +66478,7 @@
           <t>B5 | 240呎 (开放式)
 $531万
 $22,144/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -66486,7 +66486,7 @@
           <t>B6 | 236呎 (开放式)
 $528万
 $22,369/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="N33" s="22" t="inlineStr">
@@ -66494,7 +66494,7 @@
           <t>B8 | 477呎 (2房)
 $960万
 $20,126/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O33" s="20" t="inlineStr"/>
@@ -66520,7 +66520,7 @@
           <t>A1 | 497呎 (2房)
 $1153万
 $23,202/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -66528,7 +66528,7 @@
           <t>A2 | 298呎 (1房)
 $688万
 $23,084/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -66536,7 +66536,7 @@
           <t>A3 | 299呎 (1房)
 $688万
 $22,998/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -66544,7 +66544,7 @@
           <t>A5 | 300呎 (1房)
 $689万
 $22,965/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -66552,7 +66552,7 @@
           <t>A6 | 469呎 (2房)
 $1131万
 $24,117/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr"/>
@@ -66561,7 +66561,7 @@
           <t>B1 | 467呎 (2房)
 $905万
 $19,381/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -66569,7 +66569,7 @@
           <t>B2 | 296呎 (1房)
 $641万
 $21,647/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -66577,7 +66577,7 @@
           <t>B3 | 296呎 (1房)
 $620万
 $20,949/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -66585,7 +66585,7 @@
           <t>B5 | 240呎 (开放式)
 $527万
 $21,943/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -66593,7 +66593,7 @@
           <t>B6 | 236呎 (开放式)
 $523万
 $22,168/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="N34" s="22" t="inlineStr">
@@ -66601,7 +66601,7 @@
           <t>B8 | 477呎 (2房)
 $953万
 $19,973/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="O34" s="20" t="inlineStr"/>
@@ -66627,7 +66627,7 @@
           <t>A1 | 497呎 (2房)
 $1183万
 $23,794/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -66635,7 +66635,7 @@
           <t>A2 | 298呎 (1房)
 $706万
 $23,679/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -66643,7 +66643,7 @@
           <t>A3 | 298呎 (1房)
 $683万
 $22,906/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -66651,7 +66651,7 @@
           <t>A5 | 300呎 (1房)
 $658万
 $21,941/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -66659,7 +66659,7 @@
           <t>A6 | 469呎 (2房)
 $1106万
 $23,574/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr"/>
@@ -66668,7 +66668,7 @@
           <t>B1 | 467呎 (2房)
 $897万
 $19,201/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -66676,7 +66676,7 @@
           <t>B2 | 296呎 (1房)
 $635万
 $21,452/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -66684,7 +66684,7 @@
           <t>B3 | 296呎 (1房)
 $614万
 $20,759/呎
-(24年-10月)</t>
+(24年-10月-24日)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -66692,7 +66692,7 @@
           <t>B5 | 240呎 (开放式)
 $523万
 $21,800/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -66700,7 +66700,7 @@
           <t>B6 | 236呎 (开放式)
 $520万
 $22,026/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="N35" s="22" t="inlineStr">
@@ -66708,7 +66708,7 @@
           <t>B8 | 477呎 (2房)
 $944万
 $19,787/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="O35" s="20" t="inlineStr"/>
@@ -66734,7 +66734,7 @@
           <t>A1 | 497呎 (2房)
 $1116万
 $22,451/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -66742,7 +66742,7 @@
           <t>A2 | 298呎 (1房)
 $664万
 $22,266/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -66750,7 +66750,7 @@
           <t>A3 | 299呎 (1房)
 $687万
 $22,967/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -66758,7 +66758,7 @@
           <t>A5 | 300呎 (1房)
 $668万
 $22,258/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -66766,7 +66766,7 @@
           <t>A6 | 469呎 (2房)
 $1095万
 $23,338/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="H36" s="20" t="inlineStr"/>
@@ -66775,7 +66775,7 @@
           <t>B1 | 467呎 (2房)
 $884万
 $18,931/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -66783,7 +66783,7 @@
           <t>B2 | 296呎 (1房)
 $626万
 $21,158/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -66791,7 +66791,7 @@
           <t>B3 | 296呎 (1房)
 $626万
 $21,158/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -66799,7 +66799,7 @@
           <t>B5 | 240呎 (开放式)
 $517万
 $21,524/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -66807,7 +66807,7 @@
           <t>B6 | 236呎 (开放式)
 $513万
 $21,749/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="N36" s="22" t="inlineStr">
@@ -66815,7 +66815,7 @@
           <t>B8 | 477呎 (2房)
 $931万
 $19,509/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="O36" s="20" t="inlineStr"/>
@@ -66841,7 +66841,7 @@
           <t>A1 | 497呎 (2房)
 $1049万
 $21,104/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -66849,7 +66849,7 @@
           <t>A2 | 298呎 (1房)
 $624万
 $20,930/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -66857,7 +66857,7 @@
           <t>A3 | 299呎 (1房)
 $632万
 $21,145/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -66865,7 +66865,7 @@
           <t>A5 | 300呎 (1房)
 $641万
 $21,368/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -66873,7 +66873,7 @@
           <t>A6 | 469呎 (2房)
 $1116万
 $23,787/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="H37" s="20" t="inlineStr"/>
@@ -66882,7 +66882,7 @@
           <t>B1 | 467呎 (2房)
 $858万
 $18,363/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -66890,7 +66890,7 @@
           <t>B2 | 296呎 (1房)
 $588万
 $19,861/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -66898,7 +66898,7 @@
           <t>B3 | 296呎 (1房)
 $606万
 $20,457/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -66906,7 +66906,7 @@
           <t>B5 | 240呎 (开放式)
 $501万
 $20,881/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -66914,7 +66914,7 @@
           <t>B6 | 236呎 (开放式)
 $497万
 $21,057/呎
-(24年-11月)</t>
+(24年-11月-05日)</t>
         </is>
       </c>
       <c r="N37" s="22" t="inlineStr">
@@ -66922,7 +66922,7 @@
           <t>B8 | 477呎 (2房)
 $903万
 $18,924/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="O37" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．天.xlsx
+++ b/files/九龙-启德-天玺．天.xlsx
@@ -36209,7 +36209,7 @@
         </is>
       </c>
       <c r="E573" s="4" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F573" s="3" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>6555000</v>
       </c>
       <c r="I573" s="5" t="n">
-        <v>21923</v>
+        <v>21997</v>
       </c>
       <c r="J573" s="3" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>6555000</v>
       </c>
       <c r="L573" s="5" t="n">
-        <v>21923</v>
+        <v>21997</v>
       </c>
       <c r="M573" s="3" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         </is>
       </c>
       <c r="E723" s="4" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F723" s="3" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>5439100</v>
       </c>
       <c r="I723" s="5" t="n">
-        <v>23047</v>
+        <v>22950</v>
       </c>
       <c r="J723" s="3" t="inlineStr">
         <is>
@@ -45568,7 +45568,7 @@
         <v>5439100</v>
       </c>
       <c r="L723" s="5" t="n">
-        <v>23047</v>
+        <v>22950</v>
       </c>
       <c r="M723" s="3" t="inlineStr">
         <is>
@@ -63259,9 +63259,9 @@
       </c>
       <c r="E36" s="22" t="inlineStr">
         <is>
-          <t>A3 | 299呎 (1房)
+          <t>A3 | 298呎 (1房)
 $656万
-$21,923/呎
+$21,997/呎
 (24年-10月-27日)</t>
         </is>
       </c>
@@ -65199,9 +65199,9 @@
       </c>
       <c r="M21" s="22" t="inlineStr">
         <is>
-          <t>B6 | 236呎 (开放式)
+          <t>B6 | 237呎 (开放式)
 $544万
-$23,047/呎
+$22,950/呎
 (24年-11月-04日)</t>
         </is>
       </c>
